--- a/www/LENS_INDICATORS_DB.xlsx
+++ b/www/LENS_INDICATORS_DB.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L231"/>
+  <dimension ref="A1:L239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -647,7 +647,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the volume or value of premiums written? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, type of insurance, and average premium. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the volume or value of premiums written associated with customer type, gender, age, income, location, FSP type, type of insurance, or average premium? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of MSMEs using digital payment tools? Variations in this indicator may be explored across MSME gender of owner, business sector, location, income, age, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator?</t>
+          <t>Are there disparities in the share of MSMEs using digital payment tools associated with MSME gender of owner, business sector, location, income, age, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of MSMEs using digital payment tools? Variations in this indicator may be explored across MSME gender of owner, business sector, age, location, income, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? This indicator can be analyzed alongside MSMEs accepting digital transactions and MSMEs using digital payments to explore whether participation in payment networks translates into active digital transaction acceptance and payment usage.</t>
+          <t>Are there disparities in the share of MSMEs using digital payment tools associated with MSME gender of owner, business sector, age, location, income, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? This indicator can be analyzed alongside MSMEs accepting digital transactions and MSMEs using digital payments to explore whether participation in payment networks translates into active digital transaction acceptance and payment usage.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of accounts registered in the instant payment system? Variations in this indicator may be explored across customer gender, age, income, location, customer type, and FSP type. This indicator can be analyzed alongside instant/fast payment transactions per account. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of accounts registered in the instant payment system associated with customer gender, age, income, location, customer type, or FSP type? This indicator can be analyzed alongside instant/fast payment transactions per account. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique current account holders? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of unique current account holders associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the average number of accounts held per person? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the average number of accounts held per person associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique deposit account holders? Variations in this indicator may be explored across customer gender, age, income, location, customer type, product type and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of unique deposit account holders associated with customer gender, age, income, location, customer type, product type or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the average number of accounts held per person? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside active deposit accounts (number) to explore whether socio-demographic gaps in total deposit account ownership are larger or smaller than gaps in active usage.</t>
+          <t>Are there disparities in the average number of accounts held per person associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside active deposit accounts (number) to explore whether socio-demographic gaps in total deposit account ownership are larger or smaller than gaps in active usage.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of e-money accounts? Variations in this indicator may be explored across customer gender, age, income, location, customer type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of e-money accounts associated with customer gender, age, income, location, customer type, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of e-money accounts? Variations in this indicator may be explored across customer gender, age, income, location, customer type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of e-money accounts associated with customer gender, age, income, location, customer type, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the unique holders of mobile money accounts? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, account average balance. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside active mobile money accounts (number) to explore whether socio-demographic gaps in mobile money account ownership translate into similar gaps in active usage.</t>
+          <t>Are there disparities in the unique holders of mobile money accounts associated with customer gender, age, income, location, customer type, FSP type, or account average balance? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside active mobile money accounts (number) to explore whether socio-demographic gaps in mobile money account ownership translate into similar gaps in active usage.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the accounts per person of mobile money accounts? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, average account balance. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside mobile money account holders to explore whether sociio-demographic disparities in accounts per person reflect patterns of multiple account use.</t>
+          <t>Are there disparities in the accounts per person of mobile money accounts associated with customer gender, age, income, location, customer type, FSP type, or average account balance? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside mobile money account holders to explore whether sociio-demographic disparities in accounts per person reflect patterns of multiple account use.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique payment account holders? Variations in this indicator may be explored across customer type, gender, age, income, location and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of unique payment account holders associated with customer type, gender, age, income, location or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the average number of accounts held per person,? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the average number of accounts held per person, associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique savings account holders? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of unique savings account holders associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the average number of accounts held per person? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the average number of accounts held per person associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique term deposit account holders? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of unique term deposit account holders associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the average number of term deposit accounts held per person? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the average number of term deposit accounts held per person associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of pension account holders? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, and pension type. Do FSPs with higher gender diversity show higher pension account ownership rates among women? This indicator can be analyzed alongside pension contributors to explore whether socio-demographic gaps in account holding are larger or smaller than gaps in active contribution.</t>
+          <t>Are there disparities in the number of pension account holders associated with customer type, gender, age, income, location, FSP type, or pension type? Do FSPs with higher gender diversity show higher pension account ownership rates among women? This indicator can be analyzed alongside pension contributors to explore whether socio-demographic gaps in account holding are larger or smaller than gaps in active contribution.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of pension account holders? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, and pension type. Do FSPs with higher gender diversity show higher pension account ownership rates among women?</t>
+          <t>Are there disparities in the number of pension account holders associated with customer type, gender, age, income, location, FSP type, or pension type? Do FSPs with higher gender diversity show higher pension account ownership rates among women?</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number or value of investment accounts held? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number or value of investment accounts held associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number or value of investment accounts held? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside investment account holders (retail investors) to explore whether socio-demographic gaps in the number of investment accounts reflect differences in account ownership or in the tendency to hold multiple accounts.</t>
+          <t>Are there disparities in the number or value of investment accounts held associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside investment account holders (retail investors) to explore whether socio-demographic gaps in the number of investment accounts reflect differences in account ownership or in the tendency to hold multiple accounts.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique debit card holders? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, product type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of unique debit card holders associated with customer gender, age, income, location, customer type, FSP type, or product type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of debit cards in circulation? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, product type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of debit cards in circulation associated with customer gender, age, income, location, customer type, FSP type, or product type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique credit card holders? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, average balance. Are FSPs with higher gender diversity more likely to issue credit cards to a more gender-diverse customer base? This indicator can be analyzed alongside credit cards (credit limit) to explore whether socio-demographic gaps in credit card access are compounded by lower credit limits assigned to differnt customer segments, suggesting a dual disadvantage in both access and credit depth.</t>
+          <t>Are there disparities in the number of unique credit card holders associated with customer gender, age, income, location, customer type, FSP type, or average balance? Are FSPs with higher gender diversity more likely to issue credit cards to a more gender-diverse customer base? This indicator can be analyzed alongside credit cards (credit limit) to explore whether socio-demographic gaps in credit card access are compounded by lower credit limits assigned to differnt customer segments, suggesting a dual disadvantage in both access and credit depth.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of credit cards in circulation? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside credit cards (credit limit) and credit cards (outstanding balance) to explore whether customer groups with fewer credit cards in circulation are also those with lower limits and lower balances.</t>
+          <t>Are there disparities in the number of credit cards in circulation associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside credit cards (credit limit) and credit cards (outstanding balance) to explore whether customer groups with fewer credit cards in circulation are also those with lower limits and lower balances.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique loan borrowers? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside loans (number) to explore whether socio-demographic gaps in unique borrowers are similar to gaps in the total number of loans.</t>
+          <t>Are there disparities in the number of unique loan borrowers associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside loans (number) to explore whether socio-demographic gaps in unique borrowers are similar to gaps in the total number of loans.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of loans? Variations in this indicator may be explored across customer gender, customer type, FSP type, product type, loan size, and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside loans (principal disbursed) to explore whether socio-demographic gaps in the number of loans are proportional to gaps in the value disbursed.</t>
+          <t>Are there disparities in the number of loans associated with customer gender, customer type, FSP type, product type, loan size, or loan term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside loans (principal disbursed) to explore whether socio-demographic gaps in the number of loans are proportional to gaps in the value disbursed.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique secured loan borrowers? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, loan type, term and size. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside collateral pledges on credit (borrowers) to explore whether socio-demographic gaps in secured loan access are associated with differences in the type or value of collateral pledged by each customer group.</t>
+          <t>Are there disparities in the number of unique secured loan borrowers associated with customer type, gender, age, income, location, FSP type, loan type, term or size? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside collateral pledges on credit (borrowers) to explore whether socio-demographic gaps in secured loan access are associated with differences in the type or value of collateral pledged by each customer group.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of secured loans? Variations in this indicator may be explored across customer type, gender, age, income, FSP type, loan type, size, term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of secured loans associated with customer type, gender, age, income, FSP type, loan type, size, or term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique unsecured loan borrowers? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, loan type, term and size. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside loans, secured (borrowers) to explore whether customer groups underrepresented among secured borrowers compensate through higher unsecured credit uptake.</t>
+          <t>Are there disparities in the number of unique unsecured loan borrowers associated with customer type, gender, age, income, location, FSP type, loan type, term or size? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside loans, secured (borrowers) to explore whether customer groups underrepresented among secured borrowers compensate through higher unsecured credit uptake.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unsecured loans? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, loan type, size, and term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of unsecured loans associated with customer type, gender, age, income, location, FSP type, loan type, size, or term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the volume of new loan originations? Variations in this indicator may be explored across customer type, gender, customer type, age, income, location, FSP type, loan type, size and term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the volume of new loan originations associated with customer type, gender, customer type, age, income, location, FSP type, loan type, size or term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique all insurance policies? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of unique all insurance policies associated with customer gender, age, income, location, customer type, FSP type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of retail borrowers holding multiple outstanding credit operations, as a potential indicator of over-indebtedness or some level of debt stress? Variations in this indicator may be explored across customer gender, age, income, location, FSP type, product type, loan size, and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside borrowers in risky indebtedness to explore whether customer segments with higher rates of multiple loans are also more frequently classified as at risk of over-indebtedness.</t>
+          <t>Are there disparities in the share of retail borrowers holding multiple outstanding credit operations, as a potential indicator of over-indebtedness or some level of debt stress associated with customer gender, age, income, location, FSP type, product type, loan size, or loan term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside borrowers in risky indebtedness to explore whether customer segments with higher rates of multiple loans are also more frequently classified as at risk of over-indebtedness.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique all insurance holders? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of unique all insurance holders associated with customer gender, age, income, location, customer type, FSP type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique life insurance holders? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of unique life insurance holders associated with customer type, gender, age, income, location, FSP type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique life insurance policies? Variations in this indicator may be explored across customer gender, age, income, location, customer type, insurer type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of unique life insurance policies associated with customer gender, age, income, location, customer type, insurer type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique non-life insurance policies? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of unique non-life insurance policies associated with customer type, gender, age, income, location, FSP type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique non-life insurance holders? Variations in this indicator may be explored across customer gender, age, income, location, customer type, insurer type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of unique non-life insurance holders associated with customer gender, age, income, location, customer type, insurer type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of adults receiving pension benefits? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, pension type average balance. Do FSPs or employers with higher gender diversity show more equitable coverage of pension beneficiaries across genders? This indicator can be analyzed alongside retirement income per pension beneficiary to explore whether socio-demographic gaps in the number of beneficiaries are accompanied by gaps in the average income received, compounding the overall pension inequality.</t>
+          <t>Are there disparities in the number of adults receiving pension benefits associated with customer gender, age, income, location, customer type, FSP type, or pension type average balance? Do FSPs or employers with higher gender diversity show more equitable coverage of pension beneficiaries across genders? This indicator can be analyzed alongside retirement income per pension beneficiary to explore whether socio-demographic gaps in the number of beneficiaries are accompanied by gaps in the average income received, compounding the overall pension inequality.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the proportion of adults contributing to a pension account? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, pension type, average balance. Do FSPs with higher gender diversity show higher gender balance in pension enrollment or contribution rates? This indicator can be analyzed alongside pension account holders to explore whether socio-demographic disparities in the number of pension accounts are driven primarily by gaps in active contributions.</t>
+          <t>Are there disparities in the proportion of adults contributing to a pension account associated with customer gender, age, income, location, customer type, FSP type, pension type, or average balance? Do FSPs with higher gender diversity show higher gender balance in pension enrollment or contribution rates? This indicator can be analyzed alongside pension account holders to explore whether socio-demographic disparities in the number of pension accounts are driven primarily by gaps in active contributions.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of MSMEs using digital payments? Variations in this indicator may be explored across MSME type, gender of owner, business sector, location, income, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator?</t>
+          <t>Are there disparities in the share of MSMEs using digital payments associated with MSME type, gender of owner, business sector, location, income, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the frequency of cash transactions? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, and transaction type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the frequency of cash transactions associated with customer type, gender, age, income, location, FSP type, or transaction type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of e-money transactions? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of e-money transactions associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the value of e-money transactions? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the value of e-money transactions associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the value of mobile money transactions per person? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the value of mobile money transactions per person associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the volume of mobile money transactions? Variations in this indicator may be explored across customer gender, age, income, location, customer type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside mobile money transactions (value) to explore whether customer groups conducting more frequent mobile money transactions also transact at lower average values.</t>
+          <t>Are there disparities in the volume of mobile money transactions associated with customer gender, age, income, location, customer type, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside mobile money transactions (value) to explore whether customer groups conducting more frequent mobile money transactions also transact at lower average values.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the value of international remittances, and is there a gender that is the predominant recipient? Variations in this indicator may be explored across customer gender, age, income, location, FSP type, channel type, and transaction type. Are remittances concentrated in specific geographic areas, FSP types, or channels associated with low-income or low-access communities? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside cost of remittances and speed of remittances to explore whether disparities in remittance value are compounded by higher costs or longer processing times.</t>
+          <t>Are there disparities in the value of international remittances, and is there a gender that is the predominant recipient associated with customer gender, age, income, location, FSP type, channel type, or transaction type? Are remittances concentrated in specific geographic areas, FSP types, or channels associated with low-income or low-access communities? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside cost of remittances and speed of remittances to explore whether disparities in remittance value are compounded by higher costs or longer processing times.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the volume of international remittances, and is there a gender that is the predominant recipient? Variations in this indicator may be explored across customer gender, age, income, location, FSP type, channel type, and transaction type. Are remittances concentrated in specific geographic areas, FSP types, or channels associated with low-income or low-access communities?Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside remittances, total (value) to explore whether disparities in the number and value of remittances point in the same direction, or whether different customer groups send or receive more frequent but smaller transfers.</t>
+          <t>Are there disparities in the volume of international remittances, and is there a gender that is the predominant recipient associated with customer gender, age, income, location, FSP type, channel type, or transaction type? Are remittances concentrated in specific geographic areas, FSP types, or channels associated with low-income or low-access communities?Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside remittances, total (value) to explore whether disparities in the number and value of remittances point in the same direction, or whether different customer groups send or receive more frequent but smaller transfers.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the value of transactions conducted through different channels (cash, ATM, digital, agents, mobile)? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, and transaction type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside financial transactions by channel (volume) to explore whether disparities in transaction value and frequency point in the same direction.</t>
+          <t>Are there disparities in the value of transactions conducted through different channels (cash, ATM, digital, agents, mobile) associated with customer gender, age, income, location, customer type, FSP type, or transaction type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside financial transactions by channel (volume) to explore whether disparities in transaction value and frequency point in the same direction.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the volume of transactions conducted through different channels (cash, ATM, digital, agents, mobile)? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, transaction type and average size. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the volume of transactions conducted through different channels (cash, ATM, digital, agents, mobile) associated with customer gender, age, income, location, customer type, FSP type, transaction type or average size? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the average number and value of transfers from mobile money or e-money accounts to savings accounts? Variations in this indicator may be explored across customer gender, age, income, location, and product type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside net savings account flows to explore whether customer groups that more frequently transfer from mobile wallets to savings accounts also show more positive net savings flows, indicating disciplined savings behavior.</t>
+          <t>Are there disparities in the average number and value of transfers from mobile money or e-money accounts to savings accounts associated with customer gender, age, income, location, or product type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside net savings account flows to explore whether customer groups that more frequently transfer from mobile wallets to savings accounts also show more positive net savings flows, indicating disciplined savings behavior.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the rate of early cash-out of G2P payments? Variations in this indicator may be explored across customer gender, age, income, location, and FSP type. This indicator can be analyzed alongside G2P payments received (value) and G2P accounts covered by deposit insurance. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the rate of early cash-out of G2P payments associated with customer gender, age, income, location, or FSP type? This indicator can be analyzed alongside G2P payments received (value) and G2P accounts covered by deposit insurance. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the value of G2P payments received? Variations in this indicator may be explored across customer gender, age, income, location, and FSP type. This indicator can be analyzed alongside G2P accounts covered by deposit insurance and G2P payment early cash-out rate. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the value of G2P payments received associated with customer gender, age, income, location, or FSP type? This indicator can be analyzed alongside G2P accounts covered by deposit insurance and G2P payment early cash-out rate. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the representation of P2P credit operations (borrowers)? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the representation of P2P credit operations (borrowers) associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the outstanding loan balance? Variations in this indicator may be explored across customer gender, customer type, FSP type, product type, loan size, and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside loans (number) to explore whether socio-demographic disparities in outstanding balances are explained by the number of loans held or by differences in the size and term of loans accessed by each customer segment.</t>
+          <t>Are there disparities in the outstanding loan balance associated with customer gender, customer type, FSP type, product type, loan size, or loan term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside loans (number) to explore whether socio-demographic disparities in outstanding balances are explained by the number of loans held or by differences in the size and term of loans accessed by each customer segment.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the principal disbursed? Variations in this indicator may be explored across customer gender, customer type, FSP type, product type, loan size, and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside new loans (number) to explore whether socio-demographic disparities in the value disbursed are driven by fewer loans or by systematically smaller loan sizes.</t>
+          <t>Are there disparities in the principal disbursed associated with customer gender, customer type, FSP type, product type, loan size, or loan term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside new loans (number) to explore whether socio-demographic disparities in the value disbursed are driven by fewer loans or by systematically smaller loan sizes.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the outstanding balance of secured loans? Variations in this indicator may be explored across customer type, age, gender, income, location, FSP type, product type, loan size, and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the outstanding balance of secured loans associated with customer type, age, gender, income, location, FSP type, product type, loan size, or loan term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the principal disbursed of secured loans? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, product type, loan size, and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the principal disbursed of secured loans associated with customer type, gender, age, income, location, FSP type, product type, loan size, or loan term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the outstanding balance of unsecured loans? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, loan type, size, and term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the outstanding balance of unsecured loans associated with customer type, gender, age, income, location, FSP type, loan type, size, or term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the principal disbursed of unsecured loans? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, loan type, size, and term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the principal disbursed of unsecured loans associated with customer type, gender, age, income, location, FSP type, loan type, size, or term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the balances held in active deposit accounts? Variations in this indicator may be explored across customer gender, age, income, location, customer type, pruduct type and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside active deposit accounts (number) to explore whether disparities in balances are proportional to gaps in account ownership.</t>
+          <t>Are there disparities in the balances held in active deposit accounts associated with customer gender, age, income, location, customer type, pruduct type or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside active deposit accounts (number) to explore whether disparities in balances are proportional to gaps in account ownership.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of active deposit accounts? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside deposit accounts (number) to explore whether socio-demographic gaps in total deposit account ownership translate into similar gaps in active usage.</t>
+          <t>Are there disparities in the number of active deposit accounts associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside deposit accounts (number) to explore whether socio-demographic gaps in total deposit account ownership translate into similar gaps in active usage.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of active e-money accounts? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of active e-money accounts associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of active mobile money accounts? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, account type and average balance. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside mobile money accounts (number) to explore whether socio-demographic disparities in total mobile money account ownership are wider or narrower than gaps in active usage.</t>
+          <t>Are there disparities in the number of active mobile money accounts associated with customer gender, age, income, location, customer type, FSP type, account type or average balance? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside mobile money accounts (number) to explore whether socio-demographic disparities in total mobile money account ownership are wider or narrower than gaps in active usage.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of active payment accounts? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number of active payment accounts associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the likelihood of holding dormant or inactive accounts? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, and account type. This indicator can be analyzed alongside inactive and dormant accounts (balance) and revenue from inactive/dormant accounts. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the likelihood of holding dormant or inactive accounts associated with customer gender, age, income, location, customer type, FSP type, or account type? This indicator can be analyzed alongside inactive and dormant accounts (balance) and revenue from inactive/dormant accounts. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number or value of investment accounts held? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the number or value of investment accounts held associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the adoption or registration of digital payment or banking channels? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the adoption or registration of digital payment or banking channels associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the active usage intensity of the instant payment system (IPS)? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, and account type. This indicator can be analyzed alongside access to the instant/fast payment system. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the active usage intensity of the instant payment system (IPS) associated with customer gender, age, income, location, customer type, FSP type, or account type? This indicator can be analyzed alongside access to the instant/fast payment system. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the adoption of POS for in-store or online purchases? Variations in this indicator may be explored across MSME types, size, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator?</t>
+          <t>Are there disparities in the adoption of POS for in-store or online purchases associated with MSME types, size, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the requirement to pledge collateral? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, product type, and collateral type. This indicator can be analyzed alongside the indicator on borrowers whose collateral was seized. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the requirement to pledge collateral associated with customer type, gender, age, income, location, FSP type, product type, or collateral type? This indicator can be analyzed alongside the indicator on borrowers whose collateral was seized. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the use of cooling-off periods for loans. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Variations in this indicator may be explored across customer gender, age, income, location, FSP type, credit type, loan size, and loan term. Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside grace period/payment leeway to explore whether FSPs offering cooling-off periods on loans are also more likely to offer grace periods on repayment, and whether these two consumer-protective features are correlated with FSP gender diversity.</t>
+          <t>Are there disparities in the use of cooling-off periods for loans. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator associated with customer gender, age, income, location, FSP type, credit type, loan size, or loan term? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside grace period/payment leeway to explore whether FSPs offering cooling-off periods on loans are also more likely to offer grace periods on repayment, and whether these two consumer-protective features are correlated with FSP gender diversity.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the cost of sending or receiving remittances across provider types and corridors? Variations in this indicator may be explored across customer gender, age, income, location, FSP type, channel type, and transaction type. Are costs higher in areas or channels predominantly used by low-income customers or women? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside speed of remittances to explore whether costlier remittance channels are also slower, and whether the channels most used by certain customer groups are doubly disadvantaged.</t>
+          <t>Are there disparities in the cost of sending or receiving remittances across provider types and corridors associated with customer gender, age, income, location, FSP type, channel type, or transaction type? Are costs higher in areas or channels predominantly used by low-income customers or women? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside speed of remittances to explore whether costlier remittance channels are also slower, and whether the channels most used by certain customer groups are doubly disadvantaged.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Consumer protection</t>
+          <t>Consumer protection; Market development</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Suitability</t>
+          <t>Suitability, Competition</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the likelihood of experiencing slow remittance processing, and do slower remittances tend to be more expensive? Variations in this indicator may be explored across customer gender, age, income, location, FSP type, channel type, and transaction type. Are low-income communities and women particularly affected by longer processing times? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the likelihood of experiencing slow remittance processing, and do slower remittances tend to be more expensive associated with customer gender, age, income, location, FSP type, channel type, or transaction type? Are low-income communities and women particularly affected by longer processing times? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the net pension replacement rate? Variations in this indicator may be explored across customer gender, age, income, location, FSP type, and pension type. Do FSPs or employers with higher gender diversity show higher or more equitable replacement rates among women? This indicator can be analyzed alongside pension contributors to explore whether customer groups with lower or shorter contribution histories also show lower replacement rates.</t>
+          <t>Are there disparities in the net pension replacement rate associated with customer gender, age, income, location, FSP type, or pension type? Do FSPs or employers with higher gender diversity show higher or more equitable replacement rates among women? This indicator can be analyzed alongside pension contributors to explore whether customer groups with lower or shorter contribution histories also show lower replacement rates.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Consumer protection</t>
+          <t>Consumer protection; Market development</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Fair treatment</t>
+          <t>Fair treatment, Competition</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the availability of complaints channels? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, and complaints filing channel. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside access to free complaints channels to explore whether socio-economic disparities in complaints channel availability are compounded by disparities in the cost of those channels.</t>
+          <t>Are there disparities in the availability of complaints channels associated with customer gender, age, income, location, customer type, FSP type, or complaints filing channel? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside access to free complaints channels to explore whether socio-economic disparities in complaints channel availability are compounded by disparities in the cost of those channels.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the likelihood of extracting term deposit savings before maturity? Variations in this indicator may be explored across customer gender, age, income, location, customer type, product type and FSP type. This indicator can be analyzed alongside the resumption of savings after early extraction from term deposits. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the likelihood of extracting term deposit savings before maturity associated with customer gender, age, income, location, customer type, product type or FSP type? This indicator can be analyzed alongside the resumption of savings after early extraction from term deposits. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the likelihood of resuming term deposit savings after an early withdrawal? Variations in this indicator may be explored across customer gender, age, income, location, customer type, product type and FSP type. This indicator can be analyzed alongside the early extraction of term deposits indicator. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the likelihood of resuming term deposit savings after an early withdrawal associated with customer gender, age, income, location, customer type, product type or FSP type? This indicator can be analyzed alongside the early extraction of term deposits indicator. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the proportion of account holders who also maintain term deposits (cross-selling)? Variations in this indicator may be explored across customer gender, age, income, location, customer type, product type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside tenure of deposit and payment accounts to explore whether customers with longer account tenure are more likely to also hold term deposits, and whether disparities in tenure explain disparities in term deposit cross-selling.</t>
+          <t>Are there disparities in the proportion of account holders who also maintain term deposits (cross-selling) associated with customer gender, age, income, location, customer type, product type, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside tenure of deposit and payment accounts to explore whether customers with longer account tenure are more likely to also hold term deposits, and whether disparities in tenure explain disparities in term deposit cross-selling.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the likelihood of unsecured borrowers also holding a deposit account? Variations in this indicator may be explored across customer gender, age, income, location, customer type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside savings to borrowings ratio to explore whether customer groups more likely to be stand-alone borrowers without deposit accounts are also those with lower savings-to-borrowings coverage ratios.</t>
+          <t>Are there disparities in the likelihood of unsecured borrowers also holding a deposit account associated with customer gender, age, income, location, customer type, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside savings to borrowings ratio to explore whether customer groups more likely to be stand-alone borrowers without deposit accounts are also those with lower savings-to-borrowings coverage ratios.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the ratio of savings to borrowings (likelihood of being a stand-alone borrower without savings coverage)? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. This indicator can be analyzed alongside the depositors-borrowers ratio. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the ratio of savings to borrowings (likelihood of being a stand-alone borrower without savings coverage) associated with customer type, gender, age, income, location, or FSP type? This indicator can be analyzed alongside the depositors-borrowers ratio. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the frequency of cash transactions across different channels and account types? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, transaction type and average size. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside cashless transactions (volume) to explore whether customer groups with higher cash transaction volumes show lower cashless adoption, and how this trade-off evolves over time and across regions.</t>
+          <t>Are there disparities in the frequency of cash transactions across different channels and account types associated with customer gender, age, income, location, customer type, FSP type, transaction type or average size? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside cashless transactions (volume) to explore whether customer groups with higher cash transaction volumes show lower cashless adoption, and how this trade-off evolves over time and across regions.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6259,6 +6259,11 @@
 !-Limitations and considerations: The meaningfulness of this indicator depends heavily on how inclusive insurance or microinsurance is defined in each jurisdiction. In countries without a dedicated regulatory framework or formal product classification, identifying which providers offer qualifying products may require subjective judgments or additional data collection efforts. The indicator captures the share of providers offering inclusive products but does not measure the depth, quality, or uptake of those products; a provider may offer a single inclusive product with very limited reach. Complementary indicators such as the number of inclusive insurance policies in force, premiums written, or claims settlement ratios for inclusive products would provide a fuller picture of market development. The indicator also does not distinguish between providers for whom inclusive insurance is a core business versus those for whom it is a marginal product line. Cross-country comparisons should be made cautiously due to differences in regulatory definitions, market structures, and the types of entities authorized to offer insurance. Finally, because this indicator focuses on the supply side, it should be interpreted alongside demand-side measures to understand whether available products are actually reaching and benefiting the intended populations.</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in customers' access to FSPs offering inclusive or micro insurance products? Variations in this indicator may be explored across customer gender, age, income, location, customer type, insurer type, and type of insurance. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance policies (number) and insurance policy holders to explore whether greater availability of inclusive or micro insurance products at the FSP level translates into higher uptake among underserved customer groups, particularly women and low-income customers.</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type</t>
@@ -6302,7 +6307,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Are there gender differences in the total number of lives covered by insurance, including across product types and providers? How do multiple insurance coverages and coverage amounts vary by gender, age, income, and location? To what extent do providers with higher gender diversity attract more gender-balanced portfolios of lives covered? Are gender disparities consistent or do they vary across life and non-life insurance within the overall market?</t>
+          <t>Are there disparities in the number of insured persons or lives covered by insurance associated with customer gender, age, income, location, customer type, insurer type, or type of insurance? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance policies (number) and insurance policy holders to explore whether gender gaps in the number of lives covered are proportional to gaps in the number of policies and policyholders, or whether certain customer groups are more likely to hold policies that cover multiple lives.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6352,7 +6357,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Do overdraft/NSF event rates differ between women and men? Are women more likely to incur repeated overdrafts due to income volatility or lower average balances? Do fee structures disproportionately burden lower-balance accounts, which may be more prevalent among women?</t>
+          <t>Are there disparities in the frequency of account overdrafts, bounced payments, or non-sufficient funds events associated with customer gender, age, income, location, customer type, FSP type, or product type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside liquid savings (cash) buffer and late penalty charges/fees on retail credit to explore whether customer groups with lower liquid savings buffers are also more likely to experience overdraft or NSF events, and whether these events in turn translate into higher penalty fee burdens for certain customer groups.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6412,7 +6417,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Do women maintain lower liquid savings buffers than men? Is the gender gap in savings buffers widening or narrowing over time? Are there differences in savings patterns by account type (e.g., mobile money vs. bank) that affect gendered buffer adequacy?</t>
+          <t>Are there disparities in the availability of liquid savings buffers among customers associated with customer gender, age, income, location, customer type, FSP type, or product type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6462,7 +6467,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Do women show lower rates of long-term savings and investment participation than men? At what age do women versus men begin accumulating long-term financial assets? Are gender gaps in long-term savings driven by income differences, access barriers, or product design?</t>
+          <t>Are there disparities in the likelihood of actively saving or accumulating financial assets for long-term purposes associated with customer gender, age, income, location, customer type, FSP type, or product type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6497,12 +6502,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Positive net cashflow</t>
+          <t>Positive net cash flow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Whether total income exceeds total expenses over a defined period, indicating ability to build savings and reduce debt</t>
+          <t>Total income minus total expenses over a defined period</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -6512,7 +6517,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Do women show systematically lower net cashflow than men? Is the gender gap in net cashflow driven by income differences, expense patterns, or both? How does net cashflow vary by household type (single vs. dual income) and how does this affect gendered financial health outcomes?</t>
+          <t>Are there disparities in the likelihood of achieving positive net cash flow associated with customer gender, age, income, location, customer type, FSP type, or product type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -6562,7 +6567,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the total principal amount of loans disbursed to individuals and MSMEs, disaggregated by borrower or business owner gender? Do women systematically receive smaller loan disbursements than men when controlling for loan type, income level, and sector? Are these disparities more pronounced in certain types of FSPs, geographic regions, or demographic groups? How does the share of total credit disbursed to women compare with their share of total loan applicants or potential borrowers? What does this reveal about credit allocation and approval processes? Are FSPs with higher gender diversity more likely to disburse a larger proportion of credit to women or women-owned MSMEs? How do disbursement patterns by gender relate to broader financial inclusion goals and barriers</t>
+          <t>Are there disparities in the value of new loans disbursed associated with customer gender, customer type, age, income, location, FSP type, loan type, size, or term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside new loans (number) to explore whether gender disparities in the value disbursed are driven by fewer loans or by systematically smaller loan sizes granted to certain customer groups.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6622,7 +6627,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of claims? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance claims paid to explore whether customer groups filing more claims also receive payment on a proportionally similar share.</t>
+          <t>Are there disparities in the number of claims associated with customer type, gender, age, income, location, FSP type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance claims paid to explore whether customer groups filing more claims also receive payment on a proportionally similar share.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6682,7 +6687,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the value of claims paid? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the value of claims paid associated with customer type, gender, age, income, location, FSP type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6742,7 +6747,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the proportion of fraud-related complaints? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, complaints resolution outcome and complaints resolution time (turnaround time). Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside frauds faced by customers to explore whether customer groups submitting more fraud-related complaints are also those with higher rates of actual fraud exposure.</t>
+          <t>Are there  disparities in the proportion of fraud-related complaints across customer groups? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, complaints resolution outcome and complaints resolution time (turnaround time). Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside frauds faced by customers to explore whether customer groups submitting more fraud-related complaints are also those with higher rates of actual fraud exposure.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6862,7 +6867,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of complaints? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, complaints issue category, complaints filing channel, and complaints resolution status. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside customer complaints resolved in the customer's favor to explore whether FSPs receiving more complaints per customer also resolve a higher or lower share in the customer's favor, and whether any customer group both complains more and achieves less favorable outcomes.</t>
+          <t>Are there disparities in the number of complaints associated with customer gender, age, income, location, customer type, FSP type, complaints issue category, complaints filing channel, or complaints resolution status? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside customer complaints resolved in the customer's favor to explore whether FSPs receiving more complaints per customer also resolve a higher or lower share in the customer's favor, and whether any customer group both complains more and achieves less favorable outcomes.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6922,7 +6927,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the rate of complaints resolved in favor of customers? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, product type, complaints issue category. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the rate of complaints resolved in favor of customers associated with customer gender, age, income, location, customer type, FSP type, product type, or complaints issue category? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7045,7 +7050,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the APR applied to loans disbursed? Variations in this indicator may be explored across customer gender, customer type, age, income, location, FSP type, credit type, and loan size and term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside processing and application fees (PAF) to explore whether customer groups facing higher APRs also pay higher upfront fees, pointing to a compounding cost disadvantage across the full borrowing lifecycle.</t>
+          <t>Are there disparities in the APR applied to loans disbursed associated with customer gender, customer type, age, income, location, FSP type, credit type, or loan size and term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside processing and application fees (PAF) to explore whether customer groups facing higher APRs also pay higher upfront fees, pointing to a compounding cost disadvantage across the full borrowing lifecycle.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7165,7 +7170,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of net interest income attributable to penalty charges? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, credit type, loan size and term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside grace period/payment leeway to explore whether customer groups that make more use of grace periods subsequently incur fewer penalty charges, or whether grace periods simply delay rather than prevent fees.</t>
+          <t>Are there disparities in the share of net interest income attributable to penalty charges associated with customer gender, age, income, location, customer type, FSP type, credit type, loan size or term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside grace period/payment leeway to explore whether customer groups that make more use of grace periods subsequently incur fewer penalty charges, or whether grace periods simply delay rather than prevent fees.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7227,7 +7232,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the origination fee percentages incurred as a share of loan principal? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, product type, and loan size and term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside annual percentage rate (APR) for retail credit to explore whether customer groups facing higher upfront fees also pay higher overall borrowing costs.</t>
+          <t>Are there disparities in the origination fee percentages incurred as a share of loan principal associated with customer gender, age, income, location, customer type, FSP type, product type, or loan size and term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside annual percentage rate (APR) for retail credit to explore whether customer groups facing higher upfront fees also pay higher overall borrowing costs.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7287,7 +7292,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of customers affected by data breaches? Variations in this indicator may be explored across customer gender, age, income, location, customer type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside consents for sharing data with third parties to explore whether FSPs where more customers have shared data with third parties also show higher rates of data breaches, and whether any customer group is disproportionately exposed.</t>
+          <t>Are there disparities in the share of customers affected by data breaches associated with customer gender, age, income, location, customer type, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside consents for sharing data with third parties to explore whether FSPs where more customers have shared data with third parties also show higher rates of data breaches, and whether any customer group is disproportionately exposed.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7347,7 +7352,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of deposit accounts covered by direct deposit insurance? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, and product type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside G2P accounts covered by deposit insurance to explore whether disparities in deposit insurance coverage are especially pronounced among G2P recipients, who are often predominantly women.</t>
+          <t>Are there disparities in the share of deposit accounts covered by direct deposit insurance associated with customer gender, age, income, location, customer type, FSP type, or product type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside G2P accounts covered by deposit insurance to explore whether disparities in deposit insurance coverage are especially pronounced among G2P recipients, who are often predominantly women.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7411,7 +7416,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of G2P recipient accounts covered by deposit insurance, given that women are often the primary recipients of G2P transfers? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, product type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the share of G2P recipient accounts covered by deposit insurance, given that women are often the primary recipients of G2P transfers associated with customer gender, age, income, location, customer type, FSP type, or product type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7472,17 +7477,17 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the effective cost of unsecured lending? Variations in this indicator may be explored across customer gender, age, income, location, FSP type, and credit type, size and term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside interest rate spreads (loans) to explore whether disparities in effective borrowing costs reflect broader pricing differences at the FSP level or differences in the specific products accessed by each customer group.</t>
+          <t>Are there disparities in the effective cost of unsecured lending associated with customer gender, age, income, location, FSP type, and credit type, size or term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside interest rate spreads (loans) to explore whether disparities in effective borrowing costs reflect broader pricing differences at the FSP level or differences in the specific products accessed by each customer group.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Financial inclusion; Market development</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Quality, Competition</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -7529,7 +7534,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the distribution of revenue from unsecured credit operations? Variations in this indicator may be explored across customer gender, customer type, age, income, location, FSP type, and loan type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside average cost-to-borrower for unsecured retail lending to explore whether FSPs generating a higher share of revenue from unsecured credit also charge higher effective costs to borrowers.</t>
+          <t>Are there disparities in the distribution of revenue from unsecured credit operations associated with customer gender, customer type, age, income, location, FSP type, or loan type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside average cost-to-borrower for unsecured retail lending to explore whether FSPs generating a higher share of revenue from unsecured credit also charge higher effective costs to borrowers.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7589,7 +7594,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the average value of outstanding approved but unpaid insurance claims? Variations in this indicator may be explored across customer gender, age, income, location, customer type, insurer type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance claims settlement ratio to explore whether customer groups with higher outstanding approved-but-unpaid claims also show lower overall settlement ratios, indicating systemic delays rather than isolated cases.</t>
+          <t>Are there disparities in the average value of outstanding approved but unpaid insurance claims associated with customer gender, age, income, location, customer type, insurer type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance claims settlement ratio to explore whether customer groups with higher outstanding approved-but-unpaid claims also show lower overall settlement ratios, indicating systemic delays rather than isolated cases.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7650,7 +7655,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of insurance claims declined at intake? Variations in this indicator may be explored across customer gender, age, income, location, customer type, insurer type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the share of insurance claims declined at intake associated with customer gender, age, income, location, customer type, insurer type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7946,17 +7951,17 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the cost of holding and using transaction accounts? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, and product type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside average cost-to-borrower for unsecured retail lending to explore whether customer groups that face higher transaction account costs also face higher credit costs, suggesting a compounding pricing disadvantage.</t>
+          <t>Are there disparities in the cost of holding and using transaction accounts associated with customer gender, age, income, location, customer type, FSP type, or product type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside average cost-to-borrower for unsecured retail lending to explore whether customer groups that face higher transaction account costs also face higher credit costs, suggesting a compounding pricing disadvantage.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Financial inclusion; Market development</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Quality, Competition</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8061,7 +8066,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the average number and value of outstanding unsecured credit facilities per borrower? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, product type, loan term and average size. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside borrowers with multiple outstanding loans to explore whether customer groups with higher average credit facilities per borrower are also more likely to hold loans across multiple FSPs.</t>
+          <t>Are there disparities in the average number and value of outstanding unsecured credit facilities per borrower associated with customer gender, age, income, location, customer type, FSP type, product type, loan term or average size? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside borrowers with multiple outstanding loans to explore whether customer groups with higher average credit facilities per borrower are also more likely to hold loans across multiple FSPs.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8106,7 +8111,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Frauds faced by customers</t>
+          <t>Confirmed fraud incidents faced by customers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -8121,7 +8126,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the prevalence or financial impact of fraud? Variations in this indicator may be explored across customer gender, age, income, location, customer type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside frauds resulting in customer losses to explore whether customer groups exposed to more fraud incidents also suffer higher financial losses per incident.</t>
+          <t>Are there disparities in the prevalence of fraud across customer groups? Variations in this indicator may be explored across customer gender, age, income, location, customer type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside frauds resulting in customer losses to explore whether customer groups exposed to more fraud incidents also suffer higher financial losses per incident.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8136,7 +8141,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Quality, AML/CFT</t>
+          <t>Outcomes, AML/CFT</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -8181,7 +8186,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the prevalence or financial impact of fraud? Variations in this indicator may be explored across customer gender, age, income, location, customer type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the financial impact of fraud across customer groups? Variations in this indicator may be explored across customer gender, age, income, location, customer type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8242,7 +8247,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of physical security incidents affecting customers? Variations in this indicator may be explored across customer gender, age, income, location, customer type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside physical access points to explore whether socio-demographic disparities in physical safety incidents are concentrated in areas or access point types with lower infrastructure quality or fewer alternative channels.</t>
+          <t>Are there disparities in the number of physical security incidents affecting customers associated with customer gender, age, income, location, customer type, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside physical access points to explore whether socio-demographic disparities in physical safety incidents are concentrated in areas or access point types with lower infrastructure quality or fewer alternative channels.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8357,7 +8362,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the likelihood of making early loan repayments? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, credit type, loan size and term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside annual percentage rate (APR) for retail credit to explore whether customer groups facing higher APRs are more motivated to repay early, or whether higher costs instead reduce their capacity to do so.</t>
+          <t>Are there disparities in the likelihood of making early loan repayments associated with customer gender, age, income, location, customer type, FSP type, credit type, loan size or term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside annual percentage rate (APR) for retail credit to explore whether customer groups facing higher APRs are more motivated to repay early, or whether higher costs instead reduce their capacity to do so.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -8417,7 +8422,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the use of payment grace periods or leeways? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, and credit type, size and term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside borrowers in debt counselling and rehabilitation to explore whether access to grace periods reduces the likelihood of entering debt counseling, and whether oscio-demographic differences in grace period use correspond to differences in debt distress rates.</t>
+          <t>Are there disparities in the use of payment grace periods or leeways associated with customer gender, age, income, location, customer type, FSP type, and credit type, size or term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside borrowers in debt counselling and rehabilitation to explore whether access to grace periods reduces the likelihood of entering debt counseling, and whether oscio-demographic differences in grace period use correspond to differences in debt distress rates.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8538,7 +8543,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the classification of borrowers as being in risky indebtedness? Variations in this indicator may be explored across customer gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside borrowers with multiple outstanding loans to explore whether holding loans across multiple FSPs is the primary driver of risky indebtedness classification, and whether this concentration risk falls disproportionately on a particular cusomter group.</t>
+          <t>Are there disparities in the classification of borrowers as being in risky indebtedness associated with customer gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside borrowers with multiple outstanding loans to explore whether holding loans across multiple FSPs is the primary driver of risky indebtedness classification, and whether this concentration risk falls disproportionately on a particular cusomter group.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -8718,7 +8723,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the rate of reinstating lapsed insurance policies after back-payments? Variations in this indicator may be explored across customer gender, age, income, location, customer type, insurer type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance lapse rates and risk of insurance coverage lapse to explore whether FSPs with higher lapse rates also show higher reinstatement rates, and whether socio-demographic differences in financial resilience predict reinstatement behavior.</t>
+          <t>Are there disparities in the rate of reinstating lapsed insurance policies after back-payments associated with customer gender, age, income, location, customer type, insurer type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance lapse rates and risk of insurance coverage lapse to explore whether FSPs with higher lapse rates also show higher reinstatement rates, and whether socio-demographic differences in financial resilience predict reinstatement behavior.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -8778,7 +8783,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of policies at risk of lapse? Variations in this indicator may be explored across customer gender, age, income, location, customer type, insurer type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance lapse rates to explore whether customer groups with higher shares of policies at risk of lapse also have higher realized lapse rates, or whether interventions during the grace period prevent them from lapsing.</t>
+          <t>Are there disparities in the share of policies at risk of lapse associated with customer gender, age, income, location, customer type, insurer type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance lapse rates to explore whether customer groups with higher shares of policies at risk of lapse also have higher realized lapse rates, or whether interventions during the grace period prevent them from lapsing.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -8963,7 +8968,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the rate at which insurance policies are downgraded? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance lapse rates to explore whether policy downgrades serve as a step before full lapse for vulnerable policyholders, and whether customer groups with higher downgrade rates subsequently show higher lapse rates.</t>
+          <t>Are there disparities in the rate at which insurance policies are downgraded associated with customer type, gender, age, income, location, FSP type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance lapse rates to explore whether policy downgrades serve as a step before full lapse for vulnerable policyholders, and whether customer groups with higher downgrade rates subsequently show higher lapse rates.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9018,7 +9023,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of unpaid matured long-term investments? Variations in this indicator may be explored across customer gender, age, income, location, customer type, product type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside net rate of return on investments to explore whether FSPs with higher rates of unpaid matured investments also deliver lower net returns to customers, and whether some customer groups are disproportionately exposed to both risks.</t>
+          <t>Are there disparities in the share of unpaid matured long-term investments associated with customer gender, age, income, location, customer type, product type, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside net rate of return on investments to explore whether FSPs with higher rates of unpaid matured investments also deliver lower net returns to customers, and whether some customer groups are disproportionately exposed to both risks.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9199,7 +9204,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of total balances held in inactive or dormant accounts? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, and product type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the share of total balances held in inactive or dormant accounts associated with customer gender, age, income, location, customer type, FSP type, or product type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9259,7 +9264,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the average revenue earned from inactive or dormant accounts which could reflect discrimination via pricing? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, and product type. This indicator can be analyzed alongside the inactive and dormant accounts (number and balance) indicators. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there disparities in the average revenue earned from inactive or dormant accounts which could reflect discrimination via pricing associated with customer gender, age, income, location, customer type, FSP type, or product type? This indicator can be analyzed alongside the inactive and dormant accounts (number and balance) indicators. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9406,12 +9411,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>AML/CFT</t>
+          <t>Safety and security</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9420,31 +9425,38 @@
         </is>
       </c>
       <c r="D166">
-        <v>64</v>
+        <v>404</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Suspicious transaction reports</t>
+          <t>Fraud attempt success rate</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Number of suspicious transaction reports</t>
+          <t>% of all fraud attempts that were completed, resulting in customer exposure to losses</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>The indicator tallies the suspicious transaction reports (STRs)  financial service providers file with the Financial Intelligence Unit (FIU) when they suspect financial crimes such as money-laundering and terrorism financing. A rising count can signal stronger transaction monitoring systems or higher level of potentially criminal activities. Policymakers use STR volumes, in combination with other data (e.g., investigations), to allocate investigative resources. !- Definitions and concepts: Suspicious Transaction Report (STR): a mandatory report filed when a transaction is known, suspected, or has reasonable grounds to be suspected of involving criminal proceeds or terrorist funds (FATF Rec. 20). Reporting entities: broadly, all institutions covered by the AML/CFT law, including all finacial financial service providers. !- Data requirements: FIU registry of incoming STRs, ideally tagged by date, reporting institution, sector, transaction channel, predicate crime category, and outcome (e.g., disseminated to law-enforcement), and customer gender. Data quality: Duplicate submissions, incomplete narratives, or vague suspicion reasons hamper analysis and inflate reported numbers without real value. Confidentiality constraints: Detailed STR data including customer gender may be restricted.</t>
+          <t>This indicator measures the proportion of identified fraud attempts that resulted in a completed fraudulent transaction causing actual or potential customer loss, as distinct from attempts that were blocked before execution. Not all fraud attempts succeed. Institutions and payment systems deploy multiple layers of controls (eg automated blocking, step-up authentication, human review) that intercept attempts before they result in losses. Tracking the share of attempts that succeed captures the real-world effectiveness of the overall fraud control framework, not just individual components. A rising success rate despite stable or growing detection volumes indicates that controls are being outpaced by attacker sophistication or volume. Sociodemographic data enables identifying whether success rates signficantly vary by customer segment.
+Definitions and concepts: A fraud attempt is any event identified as an effort to execute a fraudulent transaction, regardless of outcome. Outcomes should be classified into three mutually exclusive categories: (1) Blocked automatically: the attempt was prevented by an automated system (e.g., rule engine, machine-learning model) without human intervention; (2) Blocked through human intervention: the attempt was flagged and subsequently stopped following manual review or customer verification; (3) Successfully completed: the attempt was not blocked and resulted in a transaction causing customer exposure to loss. Fraud attempt success rate = [# of completed fraud attempts / # of all identified fraud attempts] × 100%. Institutions should report all three outcome categories to enable a complete picture of control effectiveness.
+Data requirements: Total number of identified fraud attempts during the reporting period, classified by outcome (automatically blocked, blocked through human intervention, successfully completed); where possible, corresponding transaction values for each outcome category.</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Are there gender patterns in the customer segments most often associated with suspicious transaction reports? Variations in this indicator may be explored across FSP type and transaction type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Are fraud attempts more likely to succeed against certain customer groups than others, suggesting vulnerabilities linked to digital literacy, product design, or institutional controls? Variations in this indicator may be explored across customer gender, age, income, location, type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base show different performance in this indicator? This indicator can be analyzed alongside fraud detection lag to examine whether higher success rates for particular groups are associated with slower detection, and alongside fraud reimbursement rate to assess whether groups that suffer more completed fraud attempts are also less likely to recover their losses.</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness; Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Operational risk, Quality</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -9456,12 +9468,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>AML/CFT</t>
+          <t>Safety and security</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9470,216 +9482,216 @@
         </is>
       </c>
       <c r="D167">
-        <v>65</v>
+        <v>405</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Systematic reporting to financial intelligence unit/office (FIU)</t>
+          <t>Fraud reimbursement rate</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Number of transactions reported (excluding suspicious transaction reports) to FIU</t>
+          <t>% of confirmed customer fraud losses that were reimbursed by the FSP</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>This indicator counts all objective anti-money-laundering (AML) disclosures that reporting institutions file with the FIU other than Suspicious Transaction Reports (STRs)—for example Cash / Large-Value Transaction Reports (CTRs/LCTRs), Cross-Border Currency Reports (CBCRs), Electronic Funds Transfer Reports (EFTIs), and threshold-based filings. Tracking the volume highlights how much potentially risky activity flows through the regulated system, tests the reach and effectiveness of automated monitoring engines, and helps the FIU size analytical workloads and allocate investigative resources. When combined with STR counts and outcome statistics, this indicator offers a comprehensive perspective on the preventive arm of the AML/CFT framework. !- Definitions and concepts: Objective reports: filings triggered automatically when a transaction exceeds a statutory threshold or meets a predefined typology—irrespective of suspicion. Thresholds are set at national level and vary across countries. Reporting entities: all AML-obliged financial institutions. Optional denominator metrics to enable intensity ratios: total transactions processed or number of active customers. !- Data requirements: FIU registry of objective-report filings with unique identifiers. Data-quality variance: Missing customer identifiers or incorrect codes hinder FIU analytics; robust validation routines are essential.</t>
+          <t>This indicator measures the share of confirmed customer fraud losses by volume and value, for which the FSP provided full or partial reimbursement within a specified period. Reimbursement outcomes determine whether the cost of fraud is borne by customers or absorbed by FSPs. Disaggregation by fraud type and customer segment reveals whether certain groups systematically bear higher uncompensated losses.
+!- Definitions and concepts: Reimbursement outcomes classified into mutually exclusive categories: (1) Full reimbursement: the customer was compensated for 100% of the confirmed loss; (2) Partial reimbursement: the customer was compensated for a portion of the confirmed loss; (3) Under investigation: the claim has been submitted but reimbursement has not yet been determined; (4) No reimbursement: the FSP determined that the customer is not eligible for compensation. The reimbursement rate should be reported by number of cases and by value of losses. An advanced companion metric is the average and median time from fraud confirmation to reimbursement decision and payment, which captures operational responsiveness and is often a source of consumer complaints in its own right.
+!- Data requirements: Total number and value of confirmed customer fraud loss cases during the reporting period; number and value of cases reimbursed in full; number and value of cases reimbursed in part; number and value of cases under investigation at period end; number and value of cases closed without reimbursement; date of fraud confirmation and date of reimbursement payment for each case (to compute time-to-reimbursement).</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Are there disparities in whether, and how fully, customers are reimbursed following a confirmed fraud event? Variations in this indicator may be explored across customer gender, age, income, location, type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base show different performance in this indicator? This indicator warrants special attention from an equity perspective: if certain customer groups are systematically less likely to receive full reimbursement, the fraud burden would be falling disproportionately on already-vulnerable groups. Time-to-reimbursement should also be examined across segments, as delays impose liquidity costs that are more severe for customers with limited financial buffers. This indicator can be analyzed alongside fraud loss rate to assess the net financial impact borne by different customer groups after reimbursement.</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness; Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Operational risk, Quality</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Transaction type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>Safety and security</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D168">
-        <v>26</v>
+        <v>406</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Gender composition of loan guarantors</t>
+          <t>Fraud loss rate</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Gender composition of guarantors in the retail loan portfolio</t>
+          <t>Total volume and value of confirmed customer losses from fraud as a share of total transaction volume and value</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Measures the representation of different genders among the individuals who act as loan guarantors--pledge to repay a loan if the borrower defaults. It offers a sophisticated lens through which to view credit risk, gender-based economic disparities, and the social dynamics that underpin a loan portfolio. It can reveal hidden concentration risks. For example, if a large portion of a bank's small business loans are guaranteed by the male spouses of female entrepreneurs, the portfolio's risk profile becomes heavily correlated with the financial health and stability of that specific demographic.  This metric also provides insights into the structural barriers different genders face when seeking credit. If the data shows that female borrowers disproportionately require male guarantors (while the reverse is not true), it can signal underlying biases in credit assessment or a disparity in asset ownership. Prudential supervisors may also be interested in finding out whether the different permutations of borrower's and guarantor's gender could relate to loan performance. Conduct supervisors would use it to scrutinize lending practices for fairness and equity.</t>
+          <t>Fraud loss rate translates the incidence of successful fraud into a systemic risk metric calibrated to the size of the payments and financial services ecosystem. Unlike absolute loss figures, which grow mechanically with transaction volumes, loss rate normalises losses against activity, enabling meaningful comparisons across institutions, markets, and time. It is a key input into cost-benefit analysis of fraud controls and into assessments of whether financial system resilience is improving or deteriorating.
+This indicator measures fraud losses in two complementary dimensions: (1) volume rate = [# of confirmed fraudulent transactions / # of all transactions] × 100%; and (2) value rate = [total value of confirmed fraud losses / total value of all transactions] × 100%. Both dimensions should be reported to capture whether fraud is concentrated in high-value transactions or spread across high volumes of low-value ones.
+!- Definitions and concepts: Fraud loss refers to the net financial loss incurred by customers as a result of confirmed fraud events, after any reimbursements received from the institution. Gross loss (before reimbursement) and net loss (after reimbursement) should be reported separately where possible, as the difference reflects the allocation of risk between customers and institutions. Losses should be recorded in local currency and, for cross-country comparability, also expressed as a share of total transaction value in the same currency. Transaction scope should be clearly defined (e.g., payment transactions only, or all financial transactions including deposits and withdrawals).
+!- Data requirements: Total number and value of all transactions executed during the reporting period; total number and value of transactions confirmed as fraudulent resulting in customer loss; gross customer losses and net customer losses (after reimbursement) by volume and value.</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the representation of loan guarantors? Variations in this indicator may be explored across customer type, gender, income, location, FSP type, product type, and loan term and size. Do female borrowers disproportionately require male guarantors compared to the reverse? Is there a relationship between the gender pairing of borrower and guarantor and loan performance (delinquency, NPL)? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside borrowers whose collateral was seized to explore whether loan portfolios relying more heavily on guarantors of a particular customer group show different collateral seizure rates, and what this implies about risk allocation by customer groups.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Are there significant disparities across customer groups in terms of financial losses resulting from fraud? Variations in this indicator may be explored across customer gender, age, income, location, type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base show different performance in this indicator? Because this indicator captures net losses after reimbursement, it reflects the combined effect of fraud exposure, institutional control quality, and reimbursement outcomes across customer segments. It may be analyzed alongside confirmed fraud incidents faced by customers and fraud reimbursement rate to identify whether disparate losses correlate with high fraud incidence, large individual loss amounts, or low reimbursement rates — or a combination of all three. Where losses are concentrated among lower-income or financially excluded customers, this indicator functions as a direct measure of fraud as a driver of negative financial inclusion outcomes.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Consumer protection; Financial inclusion</t>
+          <t>Stability, safety and soundness; Financial inclusion</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Fair treatment, Quality</t>
+          <t>Operational risk, Outcomes</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Product type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>Safety and security</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D169">
-        <v>24</v>
+        <v>407</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Delinquency rate in the loan portfolio</t>
+          <t>Fraud recurrence rate</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Volume and value of delinquent retail loans as a proportion of total retail portfolio</t>
+          <t>% of customers who experienced more than one confirmed fraud event within the same a reporting period</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>The delinquency rate tracks the share of consumer loans—mortgages, credit-cards, instalment loans, auto, buy-now-pay-later, qualifying MSMEs—that have fallen past due but have not yet crossed the “non-performing” threshold or been written off. Rising early-stage arrears are an early-warning signal of household stress and of future spikes in non-performing loans (NPLs), provisions and write-offs. Paired with NPL, restructuring and write-off metrics, the delinquency rate provides a forward-looking barometer of retail credit health. Supervisors and risk managers use the metric to test the effectiveness of underwriting standards, consumer disclosure, customer interfaces (for digital loans), and pricing for credit risk. !- Definitions and concepts: Loan delinquency refers to a situation in which borrowed money is not paid back as agreed. A loan becomes delinquent when a borrower misses a regular installment payment. A delinquent loan is any kind of loan that has past due payments but has yet to go into default. On a value basis, this indicator measures the total outstanding balances past due (for example greater than 1 day past due) as a share of gross retail loan balances at the end of a specified period. Operational cut-offs: Inconsistent days past due calculation (calendar days vs. business days, partial payments) hinders cross-lender comparability.</t>
+          <t>This indicator measures the share of customers who experienced at least two confirmed fraud events during the reporting period, as a proportion of all customers who experienced at least one confirmed fraud event in the same period. A customer who is defrauded once may have been an incidental target. A customer who is defrauded repeatedly within a short period is likely exposed to a systemic vulnerability — whether in the institution's controls, in the customer's own authentication practices, or in an ongoing attack campaign targeting a particular segment. Fraud recurrence is therefore a diagnostic indicator: high recurrence points to inadequate post-incident remediation, insufficient account hardening, or persistent targeting of specific customer profiles. 
+Definitions and concepts: Fraud recurrence rate = [# of customers with 2 or more confirmed fraud events in the period / # of customers with at least 1 confirmed fraud event in the period] × 100%. A confirmed fraud event is defined consistently with other indicators. Recurrence should be measured at the individual customer level using unique customer identifiers. The indicator should be distinguished from repeat fraud attempts: a customer may face multiple attempts but only one successful event, or multiple successful events. Where data permits, institutions should also report the average number of fraud events among customers who experienced recurrence, and whether recurrence involved the same fraud type or different types (which would suggest either targeted exploitation or a broad vulnerability).
+Data requirements: Customer-level fraud event records during the reporting period, linked by unique customer identifier; count of confirmed fraud events per customer; classification of fraud events by type.</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Are there gender disparities in delinquency rates? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, product type, and loan size and term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside loan loss provisions to explore whether FSPs provisioning more heavily against certain loan segments also show higher delinquency rates in those segments, and whether socio-demographic disparities in provisioning reflects actual differences in credit risk.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Are certain customer groups more likely to experience repeated fraud events, suggesting persistent vulnerabilities or inadequate post-incident remediation for those segments? Variations in this indicator may be explored across customer gender, age, income, location, type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base show different performance in this indicator? High recurrence within a customer segment may indicate that post-fraud measures such as credential resets, step-up authentication, or customer outreach are not being applied equitably, or that certain groups are persistently targeted by organised fraud networks. This indicator may be analyzed alongside fraud detection lag to assess whether slower detection among certain groups contributes to higher recurrence, and alongside fraud reporting rate to explore whether customers who do not report their first fraud event are more likely to be victimised again.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection</t>
+          <t>Stability, safety and soundness; Financial inclusion</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Quality, Outcomes, Suitability</t>
+          <t>AML/CFT, Operational risk, Quality</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Product type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>Safety and security</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D170">
-        <v>22</v>
+        <v>409</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Non performing loans (NPLs)</t>
+          <t>Fraud reporting rate by customers</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Non performing loans rate in the retail loan portfolio</t>
+          <t>% of customers who experienced confirmed fraud and subsequently reported it through a formal channel</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>The NPL indicator for the retail loan portfolio quantifies the share (or absolute value) of consumer and MSME loans that are unlikely to be fully repaid. Because retail credit typically involves high volumes of granular, often unsecured exposures, a build-up of NPLs signals mounting credit risk costs, pressure on provisioning, and potential stress. Supervisors track this metric to assess lenders' underwriting standards, resilience to economic shocks, and the effectiveness of arrears management. !- Definitions and concepts: An NPL is defined as a loan that is past-due for a minimum amount of days (e.g., 90 days). The definition can vary across countries but the Basel Committee has set common standards. The retail portfolio encompasses exposures to individuals and qualifying MSMEs treated under the retail asset class. The most common ratio is Gross NPLs ÷ Gross retail loans. Aggressive charge-offs or “evergreening” can temporarily lower the NPL ratio without improving underlying asset quality. Seasonality and relief measures: Payment holidays or pandemic moratoria may defer delinquencies, masking latent credit risk.</t>
+          <t>Most fraud indicators in this catalog are constructed from data generated by FSPs, but a substantial share of fraud victims never formally notify their FSP, regulator, or any authority. The fraud reporting rate is the only supply-side indicator that directly measures whether the institutional fraud-reporting infrastructure is reaching customers and how much of the true fraud burden remains invisible to supervisors and policymakers. This indicator is distinct from fraud-related complaints. A complaint is an expression of dissatisfaction — typically filed when a customer believes the institution has acted inadequately, for example by failing to reimburse a loss or resolve a dispute. A fraud report is a factual notification that a fraud event occurred, filed at or near the time of the event, and does not presuppose dissatisfaction with the institution's response. Many customers who report fraud are entirely satisfied with how their institution subsequently handles the matter and never file a complaint. Conflating the two conflates different stages of the customer journey and different supervisory signals. This indicator measures the share of customers who experienced at least one confirmed fraud event during the reporting period and  filed a formal report of that event through at least one designated channel. The denominator is the number of customers with at least one confirmed fraud event in the period; the numerator is the subset of those customers who filed a formal report.
+!- Definitions and concepts: A formal fraud report is a structured notification submitted through a designated channel maintained by an FSP, supervisory authority, ADR, or law enforcement body, with a recorded timestamp and case reference. It is distinct from: (a) a fraud-related complaint, which alleges inadequate institutional response rather than simply notifying of a fraud event; (b) an informal mention to a bank agent or call centre representative that does not generate a case record; and (c) a dispute or chargeback request, which is a financial remedy mechanism rather than a fraud notification per se. Reporting channels should be classified into at least three categories: (1) institution-level (reported directly to the FSP); (2) regulatory or ADR-level (reported to a supervisory or independent redress body); (3) law enforcement or national fraud registry. Customers who reported through more than one channel should be counted once in the numerator but their multi-channel behaviour noted separately, as it may reflect either institutional non-response or heightened victim engagement. Where possible, reporting rates should be disaggregated by customer segment (gender, age, income tier, urban/rural) to identify whether systemic under-reporting is concentrated among specific groups — a finding with direct implications for inclusive consumer protection policy.
+!- Limitations and considerations: The fundamental challenge of this indicator is that the true denominator (all customers who experienced fraud) is unobservable: it includes customers whose fraud went undetected by the institution and who also did not report it. The denominator used here (confirmed fraud events known to the institution) therefore understates the true fraud-affected population, which means the reporting rate computed from institutional records likely overstates the true population-level reporting rate. This is an important caveat for interpretation. Triangulation with demand-side survey data is recommended to develop a fuller picture of the gap between actual fraud incidence and reported incidence. Additionally, reporting rates are sensitive to the accessibility and awareness of reporting channels: institutions that actively publicise fraud reporting mechanisms will mechanically observe higher rates, which should be interpreted as a positive policy outcome rather than a sign of higher fraud incidence.
+!- Data requirements: Number of customers with at least one confirmed fraud event during the reporting period (drawn from institution fraud records); number of those customers who filed a formal fraud report through at least one designated channel, with channel category recorded; where available, report timestamp relative to fraud event timestamp (to compute time-to-report as a companion metric); customer-level demographic identifiers for disaggregation by gender, age, income tier, and geography.</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Are there gender disparities in NPL rates? Variations in this indicator may be explored across customer gender, customer type, FSP type, product type, loan size, and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside delinquency rates in the retail loan portfolio to explore whether socio-demographic patterns in early-stage delinquency are a reliable leading indicator of NPL outcomes by customer grouop.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Are certain customer groups less likely to formally report fraud events, and do reporting barriers (eg awareness of channels, trust in institutions, or access challenges) fall disproportionately on particular segments? Variations in this indicator may be explored across customer gender, age, income, location, type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base show different performance in this indicator? Because under-reporting means that fraud affecting specific groups remains invisible to authorities, disparities in this indicator affect the quality and representativeness of other fraud indicators. For example, if women, rural, or low-income clients systematically under-report, their fraud burden will be underestimated overall. This indicator should be analyzed alongside fraud prevalence in complaints to distinguish between customers who do not report fraud at all and those who report but then escalate to a formal complaint.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection</t>
+          <t>Stability, safety and soundness; Financial inclusion</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Quality, Suitability</t>
+          <t>AML/CFT, Operational risk, Outcomes</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -9691,35 +9703,35 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>AML/CFT</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D171">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Restructured loans</t>
+          <t>Suspicious transaction reports</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Volume and value of restructured loans as a proportion of total retail/MSME portfolio</t>
+          <t>Number of suspicious transaction reports</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>The restructured loans indicator tracks the portion of a lender's credit portfolio whose contractual terms have been modified to relieve a borrower in financial difficulty—by lowering the interest rate, extending maturity, granting grace periods, converting currency, or partially forgiving principal, or a mix of these. A rising stock signals mounting credit stress, latent loss risk, or even internal frauds or mismagement. While restructurings can help viable borrowers bridge a temporary shock, they may defer recognition of non-performing loans (NPLs). Supervisors watch both the level and the flow of restructurings to detect “ever-greening”. !- Definitions and concepts: Restructured (or renegotiated / forborne) loan: an exposure whose cash-flow terms have been modified for credit risk reasons and would not have been granted under comparable market conditions. Local definitions vary, while standard setting bodies such as the Basel Committe and IFRS have provided common standards. Indicator formula: Restructured loans ÷ Gross loans (stock measure). !- Limitations and considerations: Regulatory divergence: Some jurisdictions treat any concession as a restructuring; others exclude purely administrative changes, hampering cross-country comparisons. Forbearance episodes: Crisis-era moratoria or government-mandated payment holidays may inflate restructuring volumes temporarily, masking true borrower weakness. Portfolio mix effects: High-yield consumer portfolios often show higher restructuring rates than collateralised mortgages; segment analysis is essential.</t>
+          <t>The indicator tallies the suspicious transaction reports (STRs)  financial service providers file with the Financial Intelligence Unit (FIU) when they suspect financial crimes such as money-laundering and terrorism financing. A rising count can signal stronger transaction monitoring systems or higher level of potentially criminal activities. Policymakers use STR volumes, in combination with other data (e.g., investigations), to allocate investigative resources. !- Definitions and concepts: Suspicious Transaction Report (STR): a mandatory report filed when a transaction is known, suspected, or has reasonable grounds to be suspected of involving criminal proceeds or terrorist funds (FATF Rec. 20). Reporting entities: broadly, all institutions covered by the AML/CFT law, including all finacial financial service providers. !- Data requirements: FIU registry of incoming STRs, ideally tagged by date, reporting institution, sector, transaction channel, predicate crime category, and outcome (e.g., disseminated to law-enforcement), and customer gender. Data quality: Duplicate submissions, incomplete narratives, or vague suspicion reasons hamper analysis and inflate reported numbers without real value. Confidentiality constraints: Detailed STR data including customer gender may be restricted.</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of restructured loans? Variations in this indicator may be explored across customer gender, customer type, customer income, FSP type, credit type, loan size, and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside delinquency rates and NPLs to explore whether customer groups with higher restructuring rates also show elevated delinquency or NPL ratios, or whether restructuring successfully prevents default.</t>
+          <t>Are there gender patterns in the customer segments most often associated with suspicious transaction reports? Variations in this indicator may be explored across FSP type and transaction type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -9727,19 +9739,9 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Quality, Suitability</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -9751,50 +9753,45 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>AML/CFT</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D172">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Large exposures</t>
+          <t>Systematic reporting to financial intelligence unit/office (FIU)</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Large exposures as % of total capital</t>
+          <t>Number of transactions reported (excluding suspicious transaction reports) to FIU</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tracks a lender's credit exposures to single counterparties or groups that exceed a threshold (e.g., a % of capital) and ensures none breach the regulatory cap. !- Definitions and concepts: Exposure includes on- and off-balance-sheet items. !- Data requirements: Counterparty-level exposure data, eligible capital base.</t>
+          <t>This indicator counts all objective anti-money-laundering (AML) disclosures that reporting institutions file with the FIU other than Suspicious Transaction Reports (STRs)—for example Cash / Large-Value Transaction Reports (CTRs/LCTRs), Cross-Border Currency Reports (CBCRs), Electronic Funds Transfer Reports (EFTIs), and threshold-based filings. Tracking the volume highlights how much potentially risky activity flows through the regulated system, tests the reach and effectiveness of automated monitoring engines, and helps the FIU size analytical workloads and allocate investigative resources. When combined with STR counts and outcome statistics, this indicator offers a comprehensive perspective on the preventive arm of the AML/CFT framework. !- Definitions and concepts: Objective reports: filings triggered automatically when a transaction exceeds a statutory threshold or meets a predefined typology—irrespective of suspicion. Thresholds are set at national level and vary across countries. Reporting entities: all AML-obliged financial institutions. Optional denominator metrics to enable intensity ratios: total transactions processed or number of active customers. !- Data requirements: FIU registry of objective-report filings with unique identifiers. Data-quality variance: Missing customer identifiers or incorrect codes hinder FIU analytics; robust validation routines are essential.</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>How are large exposures distributed by product type and customer socio-demographics? This indicator may be analyzed alongside NPLs and delinquency indicators. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type, product type, customer gender, age, income, and location.</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>Competition</t>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type</t>
+          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Transaction type</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9803,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Credit risk, Soundness</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9815,41 +9812,46 @@
         </is>
       </c>
       <c r="D173">
-        <v>262</v>
+        <v>26</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Write-offs ratio</t>
+          <t>Gender composition of loan guarantors</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Volume and value of written off retail loans as a proportion of retail/MSME portfolio</t>
+          <t>Gender composition of guarantors in the retail loan portfolio</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>The write-offs ratio tracks the portion of the retail loan portfolio that a lender permanently removes from its balance sheet within a period because collection is deemed impossible or uneconomic. It is a forward-looking credit-risk barometer: rising write-offs shrink the loan book, erode earnings through higher impairment charges, and may reveal weaknesses in underwriting or collections. Supervisors examine the indicator alongside NPL and provisioning coverage to judge whether lenders are recognising losses promptly or postponing them through restructurings. !- Definitions and concepts: Write-offs ratio is usually expressed as (Gross retail loan write-offs during period ÷ Average gross retail loans outstanding). Write-off: an accounting action that derecognises the unrecoverable portion of a loan’s amortised cost. It does not preclude further collections, which are recognised as recoveries. !- Limitations and considerations:  Timing disparities: Institutions with aggressive 180-day charge-off policies show higher ratios than peers that delay write-offs until legal exhaustion, complicating comparisons..</t>
+          <t>Measures the representation of different genders among the individuals who act as loan guarantors--pledge to repay a loan if the borrower defaults. It offers a sophisticated lens through which to view credit risk, gender-based economic disparities, and the social dynamics that underpin a loan portfolio. It can reveal hidden concentration risks. For example, if a large portion of a bank's small business loans are guaranteed by the male spouses of female entrepreneurs, the portfolio's risk profile becomes heavily correlated with the financial health and stability of that specific demographic.  This metric also provides insights into the structural barriers different genders face when seeking credit. If the data shows that female borrowers disproportionately require male guarantors (while the reverse is not true), it can signal underlying biases in credit assessment or a disparity in asset ownership. Prudential supervisors may also be interested in finding out whether the different permutations of borrower's and guarantor's gender could relate to loan performance. Conduct supervisors would use it to scrutinize lending practices for fairness and equity.</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Are there gender disparities in loan write-off rates? Variations in this indicator may be explored across customer gender, customer type, FSP type, credit type, loan size, and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside NPLs in the retail portfolio to explore whether socio-demographic patterns in non-performing loans translate predictably into write-offs.</t>
+          <t>Are there disparities in the representation of loan guarantors associated with customer type, gender, income, location, FSP type, product type, or loan term and size? Do female borrowers disproportionately require male guarantors compared to the reverse? Is there a relationship between the gender pairing of borrower and guarantor and loan performance (delinquency, NPL)? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside borrowers whose collateral was seized to explore whether loan portfolios relying more heavily on guarantors of a particular customer group show different collateral seizure rates, and what this implies about risk allocation by customer groups.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection</t>
+          <t>Consumer protection; Financial inclusion</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Quality, Outcomes, Suitability</t>
+          <t>Fair treatment, Quality</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer type; Customer gender; Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Product type</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9863,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Credit risk, Soundness</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9870,26 +9872,26 @@
         </is>
       </c>
       <c r="D174">
-        <v>263</v>
+        <v>24</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Loan loss provisions</t>
+          <t>Delinquency rate in the loan portfolio</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>% of the outstanding loan portfolio set aside as provisions for expected credit losses</t>
+          <t>Volume and value of delinquent retail loans as a proportion of total retail portfolio</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Loan loss provisions (LLPs) are the expenses a lender records to cover expected credit losses on its loan portfolio. They represent management’s best estimate of future cash shortfalls arising from borrower defaults or deteriorating credit quality. Adequate provisioning is critical for portraying true earnings, maintaining solvency, and sustaining market confidence. Monitoring LLP trends alongside non-performing loan inflows, write-offs, and capital ratios provides a holistic view of a bank’s credit-risk resilience and earnings quality. Definitions &amp; concepts: Loan Loss Provision (expense) – the profit-and-loss charge that increases the Allowance for Expected Credit Losses (ECL) on the balance sheet. !- Data requirements: LLP expenses segmented by product, geography, collateral type. Total loan portfolio value.</t>
+          <t>The delinquency rate tracks the share of consumer loans—mortgages, credit-cards, instalment loans, auto, buy-now-pay-later, qualifying MSMEs—that have fallen past due but have not yet crossed the “non-performing” threshold or been written off. Rising early-stage arrears are an early-warning signal of household stress and of future spikes in non-performing loans (NPLs), provisions and write-offs. Paired with NPL, restructuring and write-off metrics, the delinquency rate provides a forward-looking barometer of retail credit health. Supervisors and risk managers use the metric to test the effectiveness of underwriting standards, consumer disclosure, customer interfaces (for digital loans), and pricing for credit risk. !- Definitions and concepts: Loan delinquency refers to a situation in which borrowed money is not paid back as agreed. A loan becomes delinquent when a borrower misses a regular installment payment. A delinquent loan is any kind of loan that has past due payments but has yet to go into default. On a value basis, this indicator measures the total outstanding balances past due (for example greater than 1 day past due) as a share of gross retail loan balances at the end of a specified period. Operational cut-offs: Inconsistent days past due calculation (calendar days vs. business days, partial payments) hinders cross-lender comparability.</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Are there gender disparities in provisioning levels? Variations in this indicator may be explored across customer gender, age, income and location, FSP type, product type, and average loan size and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside write-offs ratio to explore whether customer groups with higher provisioning levels also experience higher write-off rates, helping assess whether provisioning accurately anticipates credit losses by customer segment.</t>
+          <t>Are there gender disparities in delinquency rates? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, product type, and loan size and term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside loan loss provisions to explore whether FSPs provisioning more heavily against certain loan segments also show higher delinquency rates in those segments, and whether socio-demographic disparities in provisioning reflects actual differences in credit risk.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -9904,12 +9906,12 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Quality, Suitability</t>
+          <t>Quality, Outcomes, Suitability</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Loan size; Product type</t>
+          <t>Customer type; Customer gender; Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Product type</t>
         </is>
       </c>
     </row>
@@ -9930,26 +9932,26 @@
         </is>
       </c>
       <c r="D175">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Physical risk in the credit portfolio</t>
+          <t>Non performing loans (NPLs)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Exposure of the credit portfolio to customers/industries with high physical risk related to climate change</t>
+          <t>Non performing loans rate in the retail loan portfolio</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>This indicator quantifies how much of the loan book is exposed to climate-related physical risks, specifically. These risks materialize through direct damage to assets, disruptions in business operations, or negative impacts on local economies, all of which can lead to higher rates of loan defaults and losses for the lender. This indicator should complement the all-encompassing indicator that measures climate-related risks (both physical and transition risks). Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, including physical risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
+          <t>The NPL indicator for the retail loan portfolio quantifies the share (or absolute value) of consumer and MSME loans that are unlikely to be fully repaid. Because retail credit typically involves high volumes of granular, often unsecured exposures, a build-up of NPLs signals mounting credit risk costs, pressure on provisioning, and potential stress. Supervisors track this metric to assess lenders' underwriting standards, resilience to economic shocks, and the effectiveness of arrears management. !- Definitions and concepts: An NPL is defined as a loan that is past-due for a minimum amount of days (e.g., 90 days). The definition can vary across countries but the Basel Committee has set common standards. The retail portfolio encompasses exposures to individuals and qualifying MSMEs treated under the retail asset class. The most common ratio is Gross NPLs ÷ Gross retail loans. Aggressive charge-offs or “evergreening” can temporarily lower the NPL ratio without improving underlying asset quality. Seasonality and relief measures: Payment holidays or pandemic moratoria may defer delinquencies, masking latent credit risk.</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Are there gender disparities in customer exposure to climate-related physical risks, particularly for women-led MSMEs in vulnerable sectors or regions? Variations in this indicator may be explored across customer gender, customer type, FSP type, and product type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside physical risk in the insurance portfolio to explore whether FSPs operating across both lending and insurance lines show consistent socio-demographic patterns in their exposure to climate-related physical risks.</t>
+          <t>Are there gender disparities in NPL rates? Variations in this indicator may be explored across customer gender, customer type, FSP type, product type, loan size, and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside delinquency rates in the retail loan portfolio to explore whether socio-demographic patterns in early-stage delinquency are a reliable leading indicator of NPL outcomes by customer grouop.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -9957,9 +9959,19 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Quality, Suitability</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Customer gender; Customer type; Financial service provider (FSP) type; Product type; Loan size; Loan term</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -9971,40 +9983,55 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Liquidity risk</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D176">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Liquidity ratio</t>
+          <t>Restructured loans</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Liquidity ratio</t>
+          <t>Volume and value of restructured loans as a proportion of total retail/MSME portfolio</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>The liquidity ratio tests whether an entity holds enough high quality liquid assets to survive a 30-day stress scenario. !- Definitions and concepts: definition of liquidity ratios can vary across countries. The Basel Committee has provided definitions for the Liquidity Coverage Ratio and the Net Stable Funding, but many countries use simpler liquidity ratio definitions. For the insurance sector, the International Association of Insurance Supervisors has also proposed liquidity metrics using an exposure approach (Insurance Liquidity Ratio) and a company projection approach (based on cash flows).</t>
+          <t>The restructured loans indicator tracks the portion of a lender's credit portfolio whose contractual terms have been modified to relieve a borrower in financial difficulty—by lowering the interest rate, extending maturity, granting grace periods, converting currency, or partially forgiving principal, or a mix of these. A rising stock signals mounting credit stress, latent loss risk, or even internal frauds or mismagement. While restructurings can help viable borrowers bridge a temporary shock, they may defer recognition of non-performing loans (NPLs). Supervisors watch both the level and the flow of restructurings to detect “ever-greening”. !- Definitions and concepts: Restructured (or renegotiated / forborne) loan: an exposure whose cash-flow terms have been modified for credit risk reasons and would not have been granted under comparable market conditions. Local definitions vary, while standard setting bodies such as the Basel Committe and IFRS have provided common standards. Indicator formula: Restructured loans ÷ Gross loans (stock measure). !- Limitations and considerations: Regulatory divergence: Some jurisdictions treat any concession as a restructuring; others exclude purely administrative changes, hampering cross-country comparisons. Forbearance episodes: Crisis-era moratoria or government-mandated payment holidays may inflate restructuring volumes temporarily, masking true borrower weakness. Portfolio mix effects: High-yield consumer portfolios often show higher restructuring rates than collateralised mortgages; segment analysis is essential.</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside liquid asset ratio to explore whether disparities are consistent across both flow-based and stock-based measures of liquidity. Variations in this indicator may be explored across FSP type.</t>
+          <t>Are there disparities in the share of restructured loans associated with customer gender, customer type, customer income, FSP type, credit type, loan size, or loan term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside delinquency rates and NPLs to explore whether customer groups with higher restructuring rates also show elevated delinquency or NPL ratios, or whether restructuring successfully prevents default.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Quality, Suitability</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -10016,40 +10043,50 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Market risk</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D177">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Value at Risk (VaR)</t>
+          <t>Large exposures</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Exposure to market risk (value volatility in the trading book)</t>
+          <t>Large exposures as % of total capital</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>VaR estimates the maximum potential trading-book loss over a specified horizon at a given confidence level (e.g., one-day 99%). It informs market risk limits and capital requirements for market risk. !- Definitions and concepts: market risk definition and standardized calculations vary across jurisdictions. Standards are provided by international standard setting bodies such as the Basel Committee.</t>
+          <t>Tracks a lender's credit exposures to single counterparties or groups that exceed a threshold (e.g., a % of capital) and ensures none breach the regulatory cap. !- Definitions and concepts: Exposure includes on- and off-balance-sheet items. !- Data requirements: Counterparty-level exposure data, eligible capital base.</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type and product type.</t>
+          <t>How are large exposures distributed by product type and customer socio-demographics? This indicator may be analyzed alongside NPLs and delinquency indicators. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type, product type, customer gender, age, income, and location.</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Competition</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+          <t>Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -10061,35 +10098,35 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Operational risk</t>
+          <t>Credit risk, Soundness</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Payments, Savings</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D178">
-        <v>31</v>
+        <v>262</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Balance of suspense accounts</t>
+          <t>Write-offs ratio</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Value of balances of suspense accounts</t>
+          <t>Volume and value of written off retail loans as a proportion of retail/MSME portfolio</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Suspense accounts are temporary holding ledgers used when a transaction cannot be posted to its final customer account because critical details are missing or disputed or due to any technical issues. The balance of suspense accounts aggregates the outstanding debit or credit amounts awaiting resolution. Persistently high or growing balances signal weaknesses in reconciliation, client on-boarding, Know-Your-Customer (KYC) data quality, payment-processing controls, or even internal fraud. Ageing buckets: some regulators require ageing of reported balances (0-30, 31-90, 91-180, &gt;180 days) to identify balances that exceed tolerance windows. !- Limitations and considerations: Accounting practices vary: some institutions clear items by moving them to internal “parking” accounts that may not be labelled suspense, understating the indicator. Standardization is needed to ensure reporting of balances in similar accounts that are not labelled "suspense accounts". Regulatory treatment: in certain jurisdictions, long-dated unresolved credits are treated as unclaimed funds.</t>
+          <t>The write-offs ratio tracks the portion of the retail loan portfolio that a lender permanently removes from its balance sheet within a period because collection is deemed impossible or uneconomic. It is a forward-looking credit-risk barometer: rising write-offs shrink the loan book, erode earnings through higher impairment charges, and may reveal weaknesses in underwriting or collections. Supervisors examine the indicator alongside NPL and provisioning coverage to judge whether lenders are recognising losses promptly or postponing them through restructurings. !- Definitions and concepts: Write-offs ratio is usually expressed as (Gross retail loan write-offs during period ÷ Average gross retail loans outstanding). Write-off: an accounting action that derecognises the unrecoverable portion of a loan’s amortised cost. It does not preclude further collections, which are recognised as recoveries. !- Limitations and considerations:  Timing disparities: Institutions with aggressive 180-day charge-off policies show higher ratios than peers that delay write-offs until legal exhaustion, complicating comparisons..</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the average amount of funds held in suspense accounts? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type. This indicator can be compared with failed transaction rates by gender. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there gender disparities in loan write-off rates? Variations in this indicator may be explored across customer gender, customer type, FSP type, credit type, loan size, and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside NPLs in the retail portfolio to explore whether socio-demographic patterns in non-performing loans translate predictably into write-offs.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10099,12 +10136,12 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Quality, Suitability</t>
+          <t>Quality, Outcomes, Suitability</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -10116,35 +10153,40 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Operational risk</t>
+          <t>Credit risk, Soundness</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D179">
-        <v>29</v>
+        <v>263</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Incomplete/failed transactions</t>
+          <t>Loan loss provisions</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>% of all initiated transactions that are incomplete or failed</t>
+          <t>% of the outstanding loan portfolio set aside as provisions for expected credit losses</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Measures the percentage of transactions that users initiate but that do not successfully complete as intended. It's a metric for assessing the reliability, usability, and accessibility of a digital financial service. A high rate of incomplete or failed transactions points to a poor user experience, and may lead to financial loss if funds are temporarily held and not returned. A sudden spike in this indicator can be an early warning of technical problems, cybersecurity attacks, or capacity issues. Incomplete transactions: transactions that are started by the user but are never fully processed to a conclusion. They are often "timed out" or abandoned. Failed transactions: transactions that are fully processed by the system but are ultimately rejected. The system actively returns an error message confirming the failure.</t>
+          <t>Loan loss provisions (LLPs) are the expenses a lender records to cover expected credit losses on its loan portfolio. They represent management’s best estimate of future cash shortfalls arising from borrower defaults or deteriorating credit quality. Adequate provisioning is critical for portraying true earnings, maintaining solvency, and sustaining market confidence. Monitoring LLP trends alongside non-performing loan inflows, write-offs, and capital ratios provides a holistic view of a bank’s credit-risk resilience and earnings quality. Definitions &amp; concepts: Loan Loss Provision (expense) – the profit-and-loss charge that increases the Allowance for Expected Credit Losses (ECL) on the balance sheet. !- Data requirements: LLP expenses segmented by product, geography, collateral type. Total loan portfolio value.</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the impact of failed transactions? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, transaction type and average size. This indicator can be analyzed alonside the indicator on financial loss due to failed transaction, and be compared with the indicator on balances in suspense accounts. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+          <t>Are there gender disparities in provisioning levels? Variations in this indicator may be explored across customer gender, age, income and location, FSP type, product type, and average loan size and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside write-offs ratio to explore whether customer groups with higher provisioning levels also experience higher write-off rates, helping assess whether provisioning accurately anticipates credit losses by customer segment.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10159,7 +10201,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Transaction type</t>
+          <t>Customer type; Customer gender; Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Loan size; Product type</t>
         </is>
       </c>
     </row>
@@ -10171,553 +10213,578 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
+          <t>Credit risk</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D180">
+        <v>125</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Physical risk in the credit portfolio</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Exposure of the credit portfolio to customers/industries with high physical risk related to climate change</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>This indicator quantifies how much of the loan book is exposed to climate-related physical risks, specifically. These risks materialize through direct damage to assets, disruptions in business operations, or negative impacts on local economies, all of which can lead to higher rates of loan defaults and losses for the lender. This indicator should complement the all-encompassing indicator that measures climate-related risks (both physical and transition risks). Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, including physical risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in customer exposure to climate-related physical risks, particularly for women-led MSMEs in vulnerable sectors or regions? Variations in this indicator may be explored across customer gender, customer type, FSP type, and product type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside physical risk in the insurance portfolio to explore whether FSPs operating across both lending and insurance lines show consistent socio-demographic patterns in their exposure to climate-related physical risks.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Customer gender; Customer type; Financial service provider (FSP) type; Product type; Loan size; Loan term</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Liquidity risk</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Investments</t>
+        </is>
+      </c>
+      <c r="D181">
+        <v>110</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Liquidity ratio</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Liquidity ratio</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>The liquidity ratio tests whether an entity holds enough high quality liquid assets to survive a 30-day stress scenario. !- Definitions and concepts: definition of liquidity ratios can vary across countries. The Basel Committee has provided definitions for the Liquidity Coverage Ratio and the Net Stable Funding, but many countries use simpler liquidity ratio definitions. For the insurance sector, the International Association of Insurance Supervisors has also proposed liquidity metrics using an exposure approach (Insurance Liquidity Ratio) and a company projection approach (based on cash flows).</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside liquid asset ratio to explore whether disparities are consistent across both flow-based and stock-based measures of liquidity. Variations in this indicator may be explored across FSP type.</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Market risk</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D182">
+        <v>52</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Value at Risk (VaR)</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Exposure to market risk (value volatility in the trading book)</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>VaR estimates the maximum potential trading-book loss over a specified horizon at a given confidence level (e.g., one-day 99%). It informs market risk limits and capital requirements for market risk. !- Definitions and concepts: market risk definition and standardized calculations vary across jurisdictions. Standards are provided by international standard setting bodies such as the Basel Committee.</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type and product type.</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
           <t>Operational risk</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Payments, Savings</t>
+        </is>
+      </c>
+      <c r="D183">
+        <v>31</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Balance of suspense accounts</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Value of balances of suspense accounts</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Suspense accounts are temporary holding ledgers used when a transaction cannot be posted to its final customer account because critical details are missing or disputed or due to any technical issues. The balance of suspense accounts aggregates the outstanding debit or credit amounts awaiting resolution. Persistently high or growing balances signal weaknesses in reconciliation, client on-boarding, Know-Your-Customer (KYC) data quality, payment-processing controls, or even internal fraud. Ageing buckets: some regulators require ageing of reported balances (0-30, 31-90, 91-180, &gt;180 days) to identify balances that exceed tolerance windows. !- Limitations and considerations: Accounting practices vary: some institutions clear items by moving them to internal “parking” accounts that may not be labelled suspense, understating the indicator. Standardization is needed to ensure reporting of balances in similar accounts that are not labelled "suspense accounts". Regulatory treatment: in certain jurisdictions, long-dated unresolved credits are treated as unclaimed funds.</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Are there disparities in the average amount of funds held in suspense accounts associated with customer gender, age, income, location, customer type, or FSP type? This indicator can be compared with failed transaction rates by gender. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Quality, Suitability</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
         <is>
           <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D180">
+      <c r="D184">
+        <v>29</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Incomplete/failed transactions</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>% of all initiated transactions that are incomplete or failed</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Measures the percentage of transactions that users initiate but that do not successfully complete as intended. It's a metric for assessing the reliability, usability, and accessibility of a digital financial service. A high rate of incomplete or failed transactions points to a poor user experience, and may lead to financial loss if funds are temporarily held and not returned. A sudden spike in this indicator can be an early warning of technical problems, cybersecurity attacks, or capacity issues. Incomplete transactions: transactions that are started by the user but are never fully processed to a conclusion. They are often "timed out" or abandoned. Failed transactions: transactions that are fully processed by the system but are ultimately rejected. The system actively returns an error message confirming the failure.</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Are there disparities in the impact of failed transactions associated with customer gender, age, income, location, customer type, FSP type, transaction type or average size? This indicator can be analyzed alonside the indicator on financial loss due to failed transaction, and be compared with the indicator on balances in suspense accounts. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Quality, Suitability</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Transaction type</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D185">
         <v>106</v>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E185" t="inlineStr">
         <is>
           <t>Operational disruption incidents</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>Number of operational disruption incidents</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>This indicator counts and classifies events that interrupt an institution’s ability to deliver financial services—whether due to IT failures, cyber-attacks, power outages, third-party breakdowns, or physical events (e.g., fire, pandemic lockdowns). Regulators track both the frequency and severity (e.g., service-unavailable minutes, customers affected, monetary losses) to judge the resilience of regulated services. A rising trend can erode confidence and expose the system to contagion if multiple firms rely on the same outsourced providers or infrastructure.
 !- Definitions and concepts: Operational disruption incident: an unplanned event that prevents or materially degrades the delivery of a critical business service beyond a defined tolerance. Definitions, including of critical services, vary across countries. Standard setting bodies including the Basel Committee provide standardized definitions that can be used. 
 Impact metrics: duration, peak concurrent users affected, transaction backlog, financial loss, data-integrity impact, customer detriment, others. Root-cause categories: hardware/software failure, cyber-intrusion, third-party outage, human error, environmental event, others. !- Limitations and considerations: Firms may fear reputational damage so there is a risk of under-reporting. Heterogeneous critical-service definitions may be used across firm, so regulatory standardization is needed.</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
+      <c r="H185" t="inlineStr">
         <is>
           <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside successful cyber attacks to explore whether FSPs with higher rates of one type of operational failure also tend to show higher rates of the other, and whether this varies by customer groups. Variations in this indicator may be explored across FSP type and types of incidents.</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr">
+      <c r="J185" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="K185" t="inlineStr">
         <is>
           <t>Quality, Data privacy and protection</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="L185" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Transaction type</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+    <row r="186">
+      <c r="A186" t="inlineStr">
         <is>
           <t>Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>Operational risk</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D181">
+      <c r="D186">
         <v>107</v>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="E186" t="inlineStr">
         <is>
           <t>Successful cyber attacks</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>Number of successful cyber attacks</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
+      <c r="G186" t="inlineStr">
         <is>
           <t>A measure of the frequency of cyberattacks on regulated financial institutions over a specified period. !- Definitions and concepts: A cyberattack is any intentional effort to steal, expose, alter, disable, or destroy data, applications, or other assets through unauthorized access to a network, computer system or digital device. Cyberattacks can disrupt and damage businesses and often carry high costs, including the costs of discovering and responding to the violation, downtime and lost revenue, and the long-term reputational damage to a business and its brand. Data requirement: Self-reporting of the number of successful cyberattacks by FSPs or data from other parties that track the incidence and severity of cyberattacks.</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
+      <c r="H186" t="inlineStr">
         <is>
           <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type and type of cyber attacks.</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr">
+      <c r="J186" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="K186" t="inlineStr">
         <is>
           <t>Outcomes, Safety and security</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
+      <c r="L186" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type; Transaction type</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>Soundness</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D182">
+      <c r="D187">
         <v>122</v>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="E187" t="inlineStr">
         <is>
           <t>Cost of reinsurance</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
+      <c r="F187" t="inlineStr">
         <is>
           <t>Premiums ceded to reinsurers as % of gross premium written</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="G187" t="inlineStr">
         <is>
           <t>The cost of reinsurance indicator quantifies the price an insurer pays to transfer part of its underwriting risk to reinsurers. Tracked as either an absolute expense or as a ratio—most often Reinsurance premium ceded ÷ Gross premiums written (GPW)—it shows how much earnings capacity the insurer surrenders for balance-sheet protection. Rising costs may stem from hardening global reinsurance markets, high catastrophe exposures, deteriorating loss experience or weakened credit quality of the insurer. Supervisors and rating agencies watch for excessive reliance on expensive reinsurance cover which can compress margins, while under-spending may leave the insurer over-exposed to shocks. Evaluated over time and in tandem with retention ratios, claims ratio and solvency coverage, the cost of reinsurance reveals whether an insurer’s risk transfer strategy is adequate. !- Definitions and concepts: Reinsurance premium ceded: contractual payments (net of commissions) made to reinsurers for proportional (quota-share, surplus) or non-proportional (excess-of-loss, stop-loss) treaties, booked at treaty inception. Net cost of reinsurance: ceded premium minus ceding commission plus profit-commission adjustments and reinstatement premiums. Timing mismatches: Premiums are typically paid up-front, while recoveries occur post-loss, so annual cost ratios can spike in growth years and dip after large events.</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
+      <c r="H187" t="inlineStr">
         <is>
           <t>Do insurers with greater gender diversity in their workforce, management, or board, incur different reinsurance costs? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across insurer type, and type of reinsurance.</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr">
+      <c r="J187" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="K187" t="inlineStr">
         <is>
           <t>Quality, Suitability</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
+      <c r="L187" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
+    <row r="188">
+      <c r="A188" t="inlineStr">
         <is>
           <t>Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>Soundness</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D183">
+      <c r="D188">
         <v>56</v>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="E188" t="inlineStr">
         <is>
           <t>Insurance claims (loss) ratio</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>% of total premium income paid out as claims</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
+      <c r="G188" t="inlineStr">
         <is>
           <t>The claims paid ratio compares the amount of benefits and claims an insurer actually disburses during a period with the premium income it records for the same portfolio. It answers a basic question for supervisors, policy-holders, and analysts: How much of each premium dollar flows back to customers in the form of claims? Persistently low ratios may flag overly aggressive pricing, onerous exclusions, or servicing bottlenecks, while very high ratios can foreshadow reserve inadequacy, under-pricing, or a spike in catastrophe losses. In combination with the expense ratio, the indicator feeds into the overall loss or combined ratio that underpins solvency and profitability assessments. !- Definitions and concepts: Claims paid: cash actually settled with policy-holders and claimants in the accounting period, including partial payments and salvage recoveries netted where local GAAP allows. It excludes outstanding claims reserves and IBNR, which are captured by “claims incurred.” Gross vs. net basis: gross claims ignore reinsurance recoveries; net claims deduct them, better reflecting the insurer’s retained risk. Segmented ratios (e.g., motor, health, property) pinpoint product-level profitability. !- Data requirements: Extracts from the claims-management system showing paid amounts, dates, line of business, and reinsurance cessions. Premium registers (written or earned, depending on supervisory preference) reconciled to the general ledger. Catastrophe tags, legal-settlement flags, and large-loss registers to isolate one-off distortions. Limitations &amp; considerations: Timing mismatch: annual premiums are often received up-front, whereas claim payments can lag; using earned premiums mitigates, but does not eliminate, this distortion. Claims-handling practices: delayed settlement or dispute escalation depresses the ratio without improving true risk experience. Reinsurance structure: quota-share vs. excess-of-loss treaties change the net ratio dramatically; analysts should review both gross and net perspectives. Regulatory definitions: some jurisdictions fold surrenders of savings-type contracts into claims, inflating comparability. Trend analysis should therefore pair the claims paid ratio with claims-incurred and reserve-adequacy metrics, catastrophe-loss disclosures, and expense dynamics to obtain a holistic view of underwriting performance and solvency resilience.</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
+      <c r="H188" t="inlineStr">
         <is>
           <t>Are there gender differences in loss ratios? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance claims settlement ratio to explore whether insurers with higher loss ratios also show lower settlement ratios. Variations in this indicator may be explored across customer type, gender, income, age, location, FSP type, ype of insurance and average premium.</t>
         </is>
       </c>
-      <c r="J183" t="inlineStr">
+      <c r="J188" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
+      <c r="K188" t="inlineStr">
         <is>
           <t>Usage, Quality, Suitability</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
+      <c r="L188" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
+    <row r="189">
+      <c r="A189" t="inlineStr">
         <is>
           <t>Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>Soundness</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C189" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D184">
+      <c r="D189">
         <v>8</v>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="E189" t="inlineStr">
         <is>
           <t>Insurance claims incurred</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F189" t="inlineStr">
         <is>
           <t>Value of insurance claims incurred</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
+      <c r="G189" t="inlineStr">
         <is>
           <t>“Claims incurred” represents the total cost an insurer recognises for claims events during a reporting period, regardless of whether they have been paid yet. Tracking the level and trend of incurred claims helps supervisors monitor the financial health of insurers such as by detecting emerging risk clusters (e.g., climate-driven catastrophes). !- Definitions and concepts: Claims incurred = Claims paid + Change in outstanding claims reserves + Change in IBNR (incurred-but-not-reported) reserves ± Claims-handling expense reserve movements. !- Data requirements: Total claims incurred.  !- Limitations and considerations: Catastrophe volatility: Single severe events cause spikes. Used alongside premium growth, claims-ratio components, and reserve-adequacy studies, “claims incurred” provides a cornerstone view of underwriting performance and balance-sheet resilience.</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in the volume or value of claims incurred? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance claims paid to explore whether socio-demographic disparities in claims incurred translate into equivalent disparities in claims paid.</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Are there disparities in the volume or value of claims incurred associated with customer type, gender, age, income, location, FSP type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance claims paid to explore whether socio-demographic disparities in claims incurred translate into equivalent disparities in claims paid.</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="K189" t="inlineStr">
         <is>
           <t>Usage, Quality, Suitability</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
+      <c r="L189" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
+    <row r="190">
+      <c r="A190" t="inlineStr">
         <is>
           <t>Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>Soundness</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C190" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D185">
+      <c r="D190">
         <v>57</v>
       </c>
-      <c r="E185" t="inlineStr">
+      <c r="E190" t="inlineStr">
         <is>
           <t>Insurance policy renewal (persistency) ratio</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="F190" t="inlineStr">
         <is>
           <t>% of all policies up for renewal that are renewed</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
+      <c r="G190" t="inlineStr">
         <is>
           <t>The renewal- or persistency-ratio gauges the proportion of in-force insurance policies (or premium) that remain active after a specified period—typically the 13th, 25th, or 61st month following issuance. High persistency signals strong customer satisfaction, effective servicing, and accurate underwriting assumptions; it underpins stable cash-flow projections, lowers acquisition-cost amortisation strain, and enhances embedded value. Conversely, rapid lapses may expose product-design weaknesses or mis-selling. Supervisors review persistency alongside surrender-value payouts and complaint levels to detect conduct risk and solvency concerns. !- Definitions and concepts: Persistency ratio (policy-count basis) = Policies renewed at month t / Policies eligible for renewal at month t
 Premium-weighted persistency uses renewal premium divided by original premium to capture face-amount shifts. Cohort vs. calendar method: Cohort traces a single issue-year block through time; calendar aggregates all cohorts renewing in a given period. !- Limitations and considerations: Measurement horizon: 13-month persistency suits annual-premium life products; short-tailed general-insurance policies need annual or shorter retention ratios. Channel mix: Bancassurance and digital pathways often show different lapse behaviours—segment analysis is essential.</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
+      <c r="H190" t="inlineStr">
         <is>
           <t>Are there gender disparities in insurance policy renewal rates? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, and type of insurance and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance lapse rates to explore whether socio-demographic patterns in renewal and lapse are mirror images of each other.</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr">
+      <c r="J190" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="K190" t="inlineStr">
         <is>
           <t>Quality, Suitability</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
+      <c r="L190" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Soundness</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D186">
-        <v>114</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Risk retention ratio (dependency on reinsurance)</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>% of gross written premium that is net (as a measure of the level of dependency on reinsurance)</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Also known as the net retention ratio, this indicator shows the proportion of insurance risk an insurer keeps on its own balance sheet after ceding portions to reinsurers. It is usually expressed as Net premiums written ÷ Gross premiums written. A high ratio signals greater self-reliance (and potentially higher earnings volatility), while a low ratio points to heavy dependence on reinsurance, which may reduce earnings swings but create counter-party risks. Supervisors monitor the metric to ensure that ceded volumes are commensurate with the insurer’s capital strength, product mix, and risk appetite. !- Definitions and concepts: Gross premiums written (GPW): Total premium income before reinsurance ceded. Net premiums written (NPW): GPW minus premiums ceded plus reinsurance recoveries on ceded unearned premiums. !- Data requirements: Line-of-business breakdown of GPW and NPW for the period. Details of outward reinsurance treaties. Counter-party concentration: high concentration risk may offset the benefits of resinsurance.</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside cost of reinsurance to explore whether insurers with lower risk retention also face higher reinsurance costs, and whether the gender composition of the portfolio influences both. Variations in this indicator may be explored across product type, customer type, and insurer type.</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Soundness</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D187">
-        <v>115</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Technical provisions</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>Level of technical provisions to cover actuarial liabilities</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Technical provisions represent the present-value estimate of all future cash outflows that an insurer expects to incur on written policies, including claims not yet reported (IBNR), claims reported but not settled, and future policyholder benefits. Adequate provisions are the cornerstone of insurance solvency and a key indicator for prudential supervisors. Definitions &amp; concepts: Technical provisions comprise two main blocks: Best-Estimate Liabilities (BEL), the probability-weighted expected value of future cash flows (claims, benefits, expenses) discounted using risk-free or prescribed curves; and Risk Margins, an additional amount reflecting the cost of holding capital to run off the liabilities (Solvency II) or a prudential margin (IFRS 17, LAT).</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside the insurance claims (loss) ratio to explore whether insurers that maintain higher technical provisions also show lower or more stable loss ratios, and whether this relationship varies across customer groups. Variations in this indicator may be explored across insurer type.</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Soundness</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D188">
-        <v>127</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Physical risk in the insurance portfolio</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>Exposure of the insurance portfolio to written policies to physical risk related to climate change</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>Metric used to quantify an insurer's financial exposure to losses caused by the direct physical impacts of climate change. This includes both event-driven acute risks and longer-term chronic risks. This indicator is essential for measuring an insurer's vulnerability to climate-related claims, which can impact its profitability, solvency, and ability to provide affordable coverage. Hence, it is an important metric for prudential supervisors from the perspective of capital adequacy, solvency and risk management. Definitions and concepts of climate-related risks vary across countries. The NGFS provides a range of additional defintions, including nature-related financial risks.</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in financial risk exposure to climate-related physical risks? Variations in this indicator may be explored across customer gender, customer type, age, income, location, and insurer type. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Soundness</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Investments</t>
-        </is>
-      </c>
-      <c r="D189">
-        <v>108</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Capital adequacy ratio (CAR)</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Total regulatory capital relative as % of risk weighted assets (RWAs)</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>Capital Adequacy Rario (CAR) shows the total qualifying capital relative to risk-weighted assets (RWA). It captures the full loss-absorbing cushion. !-Definitions and concepts: Capital tiers to include in the CAR formula are provided by the Basel Capital Accords and adapted in each jurisdiction. !- Data requirements: Full breakdown of regulatory capital components, and total RWA. For the insurance sector, the equivalent is the Solvency Ratio calculated as own funds divided by the minimum capital that insurers are required to hold to cover unexpected losses.</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside Tier 1 capital ratio to explore whether any differences by FSP gender diversity are consistent across both measures. Variations in this indicator may be explored across FSP type.</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Soundness</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D190">
-        <v>109</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Tier 1 capital ratio</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Tier 1 regulatory capital as % of risk weighted assets (RWAs)</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>The Tier 1 ratio shows the core loss-absorbing capital relative to risk-weighted assets (RWA). It is a cornerstone of the Basel Capital Accords and a trigger point for supervisory intervention. !- Definitions and concepts: Tier 1 capital comprises common equity tier 1 (CET1) plus additional tier 1 (perpetual, non-cumulative instruments). RWA adjust asset values for credit, market, and operational risk weights. Local definitions vary, but the Basel Committee has provided common standards.</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type.</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -10734,35 +10801,35 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D191">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Interest margin ratio</t>
+          <t>Risk retention ratio (dependency on reinsurance)</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Net interest income as % of total earning assets</t>
+          <t>% of gross written premium that is net (as a measure of the level of dependency on reinsurance)</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Also known as Net Interest Margin (NIM), is a metric that measures a lender's profitability by calculating difference between the interest it earns on its assets (like loans) and the interest it pays on liabilities, divided by the total earning assets. !- Definitions and concepts: NIM = (Net Interest income – Interest expense) ÷ Average earning assets. !- Data requirements: Total interest income, total interest expenses, total earning assets.</t>
+          <t>Also known as the net retention ratio, this indicator shows the proportion of insurance risk an insurer keeps on its own balance sheet after ceding portions to reinsurers. It is usually expressed as Net premiums written ÷ Gross premiums written. A high ratio signals greater self-reliance (and potentially higher earnings volatility), while a low ratio points to heavy dependence on reinsurance, which may reduce earnings swings but create counter-party risks. Supervisors monitor the metric to ensure that ceded volumes are commensurate with the insurer’s capital strength, product mix, and risk appetite. !- Definitions and concepts: Gross premiums written (GPW): Total premium income before reinsurance ceded. Net premiums written (NPW): GPW minus premiums ceded plus reinsurance recoveries on ceded unearned premiums. !- Data requirements: Line-of-business breakdown of GPW and NPW for the period. Details of outward reinsurance treaties. Counter-party concentration: high concentration risk may offset the benefits of resinsurance.</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside indicators of costs faced by borrowers, to explore correlations between gender disparities in pricing and performance in interest margin ratios. Variations in this indicator may be explored across FSP type.</t>
+          <t>Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside cost of reinsurance to explore whether insurers with lower risk retention also face higher reinsurance costs, and whether the gender composition of the portfolio influences both. Variations in this indicator may be explored across product type, customer type, and insurer type.</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -10783,41 +10850,31 @@
         </is>
       </c>
       <c r="D192">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Insurance premiums written</t>
+          <t>Technical provisions</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Value of insurance premiums writen in the insurance sector</t>
+          <t>Level of technical provisions to cover actuarial liabilities</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Premiums written represent the contractual revenue an insurer books when it underwrites new or renewal policies during a given period, irrespective of when coverage is provided or cash is received. Rising written-premium volumes can indicate growth, improved pricing power, or inflation-driven sum-assured increases; declining volumes may flag competitive pressures or tighter underwriting standards. !- Definitions and concepts: Gross premiums written (GPW): All premiums on policies incepted or renewed during the period before ceding to reinsurers. Net premiums written (NPW): GPW minus premiums ceded plus any reinsurance assumed—reflects the risk the insurer retains. Earned premiums: Portion of written premiums recognised as revenue in proportion to expired coverage—crucial for claims-ratio analysis. !- Data requirements: total premium written. For granular data: Policy-level underwriting feeds: issue/renewal dates, premium amounts, payment mode, product line, distribution channel, currency.</t>
+          <t>Technical provisions represent the present-value estimate of all future cash outflows that an insurer expects to incur on written policies, including claims not yet reported (IBNR), claims reported but not settled, and future policyholder benefits. Adequate provisions are the cornerstone of insurance solvency and a key indicator for prudential supervisors. Definitions &amp; concepts: Technical provisions comprise two main blocks: Best-Estimate Liabilities (BEL), the probability-weighted expected value of future cash flows (claims, benefits, expenses) discounted using risk-free or prescribed curves; and Risk Margins, an additional amount reflecting the cost of holding capital to run off the liabilities (Solvency II) or a prudential margin (IFRS 17, LAT).</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the volume or value of premiums written? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance claims incurred to explore whether socio-demographic disparities in the volume or value of premiums written are mirrored by corresponding disparities in claims incurred.</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>Usage, Outcomes</t>
+          <t>Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside the insurance claims (loss) ratio to explore whether insurers that maintain higher technical provisions also show lower or more stable loss ratios, and whether this relationship varies across customer groups. Variations in this indicator may be explored across insurer type.</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -10834,35 +10891,35 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D193">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Efficiency ratio</t>
+          <t>Physical risk in the insurance portfolio</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Effciency ratio</t>
+          <t>Exposure of the insurance portfolio to written policies to physical risk related to climate change</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Indicates operating efficiency by comparing non-interest expenses to operating income. Lower ratios signal better cost control, a key driver of sustainable profitability, especially in low-margin environments. Definitions &amp; concepts – Efficiency Ratio = Operating expenses ÷ (Net interest income + Non-interest income). Some variants exclude litigation or restructuring charges. !- Data requirements: Detailed income statement with breakdowns of personnel, IT, and occupancy costs; segment reporting helps pinpoint inefficiencies. !- Limitations and considerations: Cost cuts that impair risk management or customer service may improve the ratio temporarily but raise long-run risks. Cross-country comparisons should adjust for labour cost levels and digitalisation stages. One-off income (e.g., asset sales) can distort the denominator.</t>
+          <t>Metric used to quantify an insurer's financial exposure to losses caused by the direct physical impacts of climate change. This includes both event-driven acute risks and longer-term chronic risks. This indicator is essential for measuring an insurer's vulnerability to climate-related claims, which can impact its profitability, solvency, and ability to provide affordable coverage. Hence, it is an important metric for prudential supervisors from the perspective of capital adequacy, solvency and risk management. Definitions and concepts of climate-related risks vary across countries. The NGFS provides a range of additional defintions, including nature-related financial risks.</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside personnel expenses per customer/contract to explore whether disparities are driven in part by differences in the cost of serving different customer segments. Variations in this indicator may be explored across FSP type.</t>
+          <t>Are there gender disparities in financial risk exposure to climate-related physical risks? Variations in this indicator may be explored across customer gender, customer type, age, income, location, and insurer type. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -10879,35 +10936,35 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Payments, Savings, Credit, Insurance, Investments</t>
         </is>
       </c>
       <c r="D194">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Personnel expenses per customer/contract</t>
+          <t>Capital adequacy ratio (CAR)</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Total personnel expenses per customer or contract</t>
+          <t>Total regulatory capital relative as % of risk weighted assets (RWAs)</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>This indicator measures the total cost of personnel (wages, salaries, benefits, etc.) divided by the total number of customers a financial service provider serves, revealing how much is spent on staff to support each individual customer. This metric helps assess a company's operational efficiency and cost-effectiveness in managing its customer base, with a lower figure typically indicating better efficiency.</t>
+          <t>Capital Adequacy Rario (CAR) shows the total qualifying capital relative to risk-weighted assets (RWA). It captures the full loss-absorbing cushion. !-Definitions and concepts: Capital tiers to include in the CAR formula are provided by the Basel Capital Accords and adapted in each jurisdiction. !- Data requirements: Full breakdown of regulatory capital components, and total RWA. For the insurance sector, the equivalent is the Solvency Ratio calculated as own funds divided by the minimum capital that insurers are required to hold to cover unexpected losses.</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Do FSPs serving a higher proportion of women customers incur different per-customer personnel costs? Do FSPs with greater gender diversity at board, management, and staff levels show better performance on this indicator? This indicator can be analyzed alongside efficiency ratio to explore whether FSPs with higher per-customer personnel costs also show weaker overall efficiency ratios, and whether serving a more gender-diverse customer base correlates with different cost structures. Variations in this indicator may be explored across FSP type.</t>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside Tier 1 capital ratio to explore whether any differences by FSP gender diversity are consistent across both measures. Variations in this indicator may be explored across FSP type.</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
         </is>
       </c>
     </row>
@@ -10928,31 +10985,31 @@
         </is>
       </c>
       <c r="D195">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>ROA</t>
+          <t>Tier 1 capital ratio</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Return on assets</t>
+          <t>Tier 1 regulatory capital as % of risk weighted assets (RWAs)</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>ROA gauges how efficiently a financial service provider turns every unit of assets under its control into net profit. !- Definitions and concepts: ROA = Net income after tax ÷ Average total assets (opening + closing assets ÷ 2). !- Data requirements: net income and total assets at two balance-sheet dates, preferably quarterly to smooth seasonality. !- Limitations and considerations: ROA ignores off-balance-sheet exposures such as guarantees or derivatives.</t>
+          <t>The Tier 1 ratio shows the core loss-absorbing capital relative to risk-weighted assets (RWA). It is a cornerstone of the Basel Capital Accords and a trigger point for supervisory intervention. !- Definitions and concepts: Tier 1 capital comprises common equity tier 1 (CET1) plus additional tier 1 (perpetual, non-cumulative instruments). RWA adjust asset values for credit, market, and operational risk weights. Local definitions vary, but the Basel Committee has provided common standards.</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside efficiency ratio and NPLs to explore whether FSPs with stronger risk management and operational efficiency also show higher asset returns, and whether these relationships are consistent across FSPs with different gender diversity profiles. Variations in this indicator may be explored across FSP type.</t>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type.</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -10964,40 +11021,40 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Soundness, Credit risk</t>
+          <t>Soundness</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D196">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>ROE</t>
+          <t>Interest margin ratio</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Return on equity</t>
+          <t>Net interest income as % of total earning assets</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>ROE indicates the earnings available to common shareholders per unit of book equity. !- Definitions and concepts: ROE = Net income ÷ Average shareholders’ equity. !- Data requirements: Consolidated net income and shareholders’ equity.</t>
+          <t>Also known as Net Interest Margin (NIM), is a metric that measures a lender's profitability by calculating difference between the interest it earns on its assets (like loans) and the interest it pays on liabilities, divided by the total earning assets. !- Definitions and concepts: NIM = (Net Interest income – Interest expense) ÷ Average earning assets. !- Data requirements: Total interest income, total interest expenses, total earning assets.</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside ROA to explore whether disparities in ROE reflect differences in leverage as well as asset returns, helping distinguish between financial strategy and operational performance. Variations in this indicator may be explored across FSP type.</t>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside indicators of costs faced by borrowers, to explore correlations between gender disparities in pricing and performance in interest margin ratios. Variations in this indicator may be explored across FSP type.</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -11009,35 +11066,35 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>Soundness</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Financial system credit operations</t>
+          <t>Insurance premiums written</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Volume and value of credit operations in the total financial sector portfolio</t>
+          <t>Value of insurance premiums writen in the insurance sector</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>This indicator captures the breadth of formal lending with two perspectives: the number of credit contracts (volume) and their aggregate outstanding balance (value) across all regulated lenders. Tracking it offers a panoramic view of credit provision, enabling supervisors to (i) gauge financial deepening, (ii) assess systemic leverage of the banking sector, (iii) monitor shifts in portfolio composition (e.g., rise of consumer or MSME lending), and (iv) feed macro-prudential stress tests and monetary policy models. Sharp expansions may indicate rapid financial inclusion or overheating; contractions can herald credit crunches that dampen growth. !- Definitions and concepts: Credit operation – any legally binding loan, line of credit, hire-purchase, lease, or other. Off-balance-sheet commitments (e.g., undrawn credit lines, guarantees) are usually excluded or reported separately. Volume (count): unique credit contracts outstanding at the reporting date; renewals/extensions count as new operations if a fresh contract is signed. Segmentation by sector (household, corporate, government), product type, currency, and residual maturity enriches analysis. !- Data requirements: Supervisory returns or call-reports detailing credit operations contract count by institution and product. Standardised product and sector taxononies to avoid double counting.</t>
+          <t>Premiums written represent the contractual revenue an insurer books when it underwrites new or renewal policies during a given period, irrespective of when coverage is provided or cash is received. Rising written-premium volumes can indicate growth, improved pricing power, or inflation-driven sum-assured increases; declining volumes may flag competitive pressures or tighter underwriting standards. !- Definitions and concepts: Gross premiums written (GPW): All premiums on policies incepted or renewed during the period before ceding to reinsurers. Net premiums written (NPW): GPW minus premiums ceded plus any reinsurance assumed—reflects the risk the insurer retains. Earned premiums: Portion of written premiums recognised as revenue in proportion to expired coverage—crucial for claims-ratio analysis. !- Data requirements: total premium written. For granular data: Policy-level underwriting feeds: issue/renewal dates, premium amounts, payment mode, product line, distribution channel, currency.</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the distribution of credit operations? Variations in this indicator may be explored across customer type, gender, FSP type, and product type.</t>
+          <t>Are there disparities in the volume or value of premiums written associated with customer type, gender, age, income, location, FSP type, type of insurance, or average premium? Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside insurance claims incurred to explore whether socio-demographic disparities in the volume or value of premiums written are mirrored by corresponding disparities in claims incurred.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11047,12 +11104,12 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Usage, Outcomes</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -11064,74 +11121,309 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
+          <t>Soundness</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D198">
+        <v>112</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Efficiency ratio</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Effciency ratio</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Indicates operating efficiency by comparing non-interest expenses to operating income. Lower ratios signal better cost control, a key driver of sustainable profitability, especially in low-margin environments. Definitions &amp; concepts – Efficiency Ratio = Operating expenses ÷ (Net interest income + Non-interest income). Some variants exclude litigation or restructuring charges. !- Data requirements: Detailed income statement with breakdowns of personnel, IT, and occupancy costs; segment reporting helps pinpoint inefficiencies. !- Limitations and considerations: Cost cuts that impair risk management or customer service may improve the ratio temporarily but raise long-run risks. Cross-country comparisons should adjust for labour cost levels and digitalisation stages. One-off income (e.g., asset sales) can distort the denominator.</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside personnel expenses per customer/contract to explore whether disparities are driven in part by differences in the cost of serving different customer segments. Variations in this indicator may be explored across FSP type.</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Soundness</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D199">
+        <v>123</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Personnel expenses per customer/contract</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Total personnel expenses per customer or contract</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>This indicator measures the total cost of personnel (wages, salaries, benefits, etc.) divided by the total number of customers a financial service provider serves, revealing how much is spent on staff to support each individual customer. This metric helps assess a company's operational efficiency and cost-effectiveness in managing its customer base, with a lower figure typically indicating better efficiency.</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Do FSPs serving a higher proportion of women customers incur different per-customer personnel costs? Do FSPs with greater gender diversity at board, management, and staff levels show better performance on this indicator? This indicator can be analyzed alongside efficiency ratio to explore whether FSPs with higher per-customer personnel costs also show weaker overall efficiency ratios, and whether serving a more gender-diverse customer base correlates with different cost structures. Variations in this indicator may be explored across FSP type.</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Soundness</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D200">
+        <v>117</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Return on assets</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>ROA gauges how efficiently a financial service provider turns every unit of assets under its control into net profit. !- Definitions and concepts: ROA = Net income after tax ÷ Average total assets (opening + closing assets ÷ 2). !- Data requirements: net income and total assets at two balance-sheet dates, preferably quarterly to smooth seasonality. !- Limitations and considerations: ROA ignores off-balance-sheet exposures such as guarantees or derivatives.</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside efficiency ratio and NPLs to explore whether FSPs with stronger risk management and operational efficiency also show higher asset returns, and whether these relationships are consistent across FSPs with different gender diversity profiles. Variations in this indicator may be explored across FSP type.</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Soundness, Credit risk</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D201">
+        <v>116</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Return on equity</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>ROE indicates the earnings available to common shareholders per unit of book equity. !- Definitions and concepts: ROE = Net income ÷ Average shareholders’ equity. !- Data requirements: Consolidated net income and shareholders’ equity.</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside ROA to explore whether disparities in ROE reflect differences in leverage as well as asset returns, helping distinguish between financial strategy and operational performance. Variations in this indicator may be explored across FSP type.</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Credit risk</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D202">
+        <v>6</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Financial system credit operations</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Volume and value of credit operations in the total financial sector portfolio</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>This indicator captures the breadth of formal lending with two perspectives: the number of credit contracts (volume) and their aggregate outstanding balance (value) across all regulated lenders. Tracking it offers a panoramic view of credit provision, enabling supervisors to (i) gauge financial deepening, (ii) assess systemic leverage of the banking sector, (iii) monitor shifts in portfolio composition (e.g., rise of consumer or MSME lending), and (iv) feed macro-prudential stress tests and monetary policy models. Sharp expansions may indicate rapid financial inclusion or overheating; contractions can herald credit crunches that dampen growth. !- Definitions and concepts: Credit operation – any legally binding loan, line of credit, hire-purchase, lease, or other. Off-balance-sheet commitments (e.g., undrawn credit lines, guarantees) are usually excluded or reported separately. Volume (count): unique credit contracts outstanding at the reporting date; renewals/extensions count as new operations if a fresh contract is signed. Segmentation by sector (household, corporate, government), product type, currency, and residual maturity enriches analysis. !- Data requirements: Supervisory returns or call-reports detailing credit operations contract count by institution and product. Standardised product and sector taxononies to avoid double counting.</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Are there disparities in the distribution of credit operations associated with customer type, gender, FSP type, or product type?</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
           <t>Liquidity risk</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
+      <c r="C203" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="D198">
+      <c r="D203">
         <v>17</v>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E203" t="inlineStr">
         <is>
           <t>Deposit stability/volatility</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
+      <c r="F203" t="inlineStr">
         <is>
           <t>Stability/volatility of retail deposits (deposit stickness, deposit stability, deposit flows)</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
+      <c r="G203" t="inlineStr">
         <is>
           <t>The deposit stability (or deposit-volatility) indicator assesses how predictable an FSP's funding base is by tracking the fluctuation and “stickiness” of customer deposits over time. Sudden, correlated outflows—whether triggered by market rumours, rate competition or digital bank runs—can force a bank to liquidate assets at fire-sale prices or draw on emergency facilities. Prudential supervisors monitor deposit volatility alongside liquidity ratios to judge an institution’s ability to withstand funding shocks and to calibrate run-off assumptions in stress tests and the Liquidity Coverage Ratio (LCR). Definitions &amp; concepts: Core / stable deposits: retail balances judged unlikely to flee under stress; often defined by balance size, relationship depth, and whether the account is transactional rather than rate-sensitive. Volatility metrics: standard deviation of daily balances divided by the mean (coefficient of variation), maximum one-day net outflow over a look-back window, or elasticity (beta) to market rates. Calculation methods vary across countries. !- Data requirements: High-frequency (daily or intraday) deposit-balance time series, tagged by customer type, product, and currency. Interest-rate history to estimate betas. Customer identifiers for relationship tenure, cross-selling, and concentration analysis. 
 Digital channel dynamics: mobile app withdrawals can accelerate run speed beyond historical norms; backward-looking volatility measures may understate future risk.</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
+      <c r="H203" t="inlineStr">
         <is>
           <t>Do accounts held by different gender groups show distinct patterns in deposit stability or volatility? Variations in this indicator may be explored across FSP type, product type, customer type, customer gender, age, income, location. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside net savings account flows to explore whether accounts with more volatile balances also show lower average net savings, and whether socio-demographic disparities in savings volatility are consistent with patterns in net savings behavior.</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
+      <c r="L203" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
+    <row r="204">
+      <c r="A204" t="inlineStr">
         <is>
           <t>Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>Soundness</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
+      <c r="C204" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D199">
+      <c r="D204">
         <v>392</v>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="E204" t="inlineStr">
         <is>
           <t>Combined ratio</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="F204" t="inlineStr">
         <is>
           <t>% of total premium income used in paying expenses and claims</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
+      <c r="G204" t="inlineStr">
         <is>
           <t>The combined ratio is a key measure of underwriting profitability in the insurance industry. It indicates the proportion of each unit of premium earned that an insurer uses to cover claims-related losses and operating expenses. A combined ratio below 100% signals an underwriting profit, meaning the insurer is collecting more in premiums than it pays out in claims and expenses, while a ratio above 100% indicates an underwriting loss. This indicator is widely used by insurance supervisors as an early warning signal for assessing the financial health and operational efficiency of insurers, and it supports prudential oversight by helping to identify companies that may be underpricing risk or operating with excessive costs. Monitoring this indicator over time and across different types of insurers can reveal structural patterns in the sustainability of insurance business models and inform supervisory responses.
 !-Definitions and concepts: The combined ratio is calculated as the sum of two components: the loss ratio and the expense ratio. The loss ratio measures claims-related costs (incurred losses plus loss adjustment expenses) as a proportion of earned premiums. The expense ratio measures underwriting and administrative expenses (such as commissions, salaries, and other operational costs) as a proportion of earned or written premiums. The general formula is: Combined Ratio = Loss Ratio + Expense Ratio, or equivalently, Combined Ratio = (Incurred Losses + Loss Adjustment Expenses + Underwriting Expenses) / Earned Premiums. Earned premiums refer to the portion of written premiums corresponding to the coverage period that has elapsed, ensuring proper matching between income recognized and associated claims obligations. A combined ratio of exactly 100% represents the break-even point for underwriting operations.
@@ -11139,37 +11431,47 @@
 !-Limitations and considerations: The combined ratio captures only underwriting performance and does not account for investment income, which is a significant source of revenue for many insurers. As a result, an insurer with a combined ratio above 100% may still be profitable overall due to returns on invested premiums and reserves. Changes in loss reserve estimates can materially affect the ratio, and reserve strengthening or releases in a given period may distort comparisons over time. The ratio is most commonly applied to non-life (property and casualty) insurance and may be less meaningful for life insurance products where long-term investment returns play a more central role. Additionally, the use of written premiums versus earned premiums in the expense ratio denominator can vary across jurisdictions and accounting standards, requiring care when making cross-country or cross-insurer comparisons. The combined ratio should be interpreted alongside other indicators of insurer financial health, including solvency ratios and investment performance metrics.</t>
         </is>
       </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside the insurance claims (loss) ratio and cost of reinsurance to explore whether insurers with higher combined ratios are also those with less favorable loss and reinsurance cost profiles, and whether insurer gender diversity is associated with more disciplined underwriting and expense management. Variations in this indicator may be explored across insurer type, and type of insurance.</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Financial service provider (FSP) gender diversity</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
         <is>
           <t>Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B205" t="inlineStr">
         <is>
           <t>Soundness</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D200">
+      <c r="D205">
         <v>394</v>
       </c>
-      <c r="E200" t="inlineStr">
+      <c r="E205" t="inlineStr">
         <is>
           <t>Expense ratio</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
+      <c r="F205" t="inlineStr">
         <is>
           <t>% of earned premiums that an insurance company spends on underwriting and administrative expenses (excluding claims)</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
+      <c r="G205" t="inlineStr">
         <is>
           <t>The expense ratio measures the proportion of earned premiums that an insurance company spends on underwriting and administrative expenses, excluding claims-related costs. It is a key indicator of operational efficiency, reflecting how effectively an insurer manages the costs associated with acquiring, underwriting, and servicing insurance policies. Financial sector authorities use this indicator to assess whether insurers are operating within sustainable cost structures and to identify potential inefficiencies that could affect policyholder value or long-term solvency. Together with the loss ratio, the expense ratio is one of the two components of the combined ratio, providing a complementary view that isolates operational cost management from claims experience. Monitoring the expense ratio across providers and over time can help supervisors detect trends in market competitiveness, evaluate the impact of new distribution models (such as digital or agent-based channels) on cost structures, and assess whether high acquisition or administrative costs may be eroding the value delivered to policyholders.
 !-Definitions and concepts: The expense ratio is calculated by dividing total underwriting and administrative expenses by premiums for a given reporting period. The formula is: Expense Ratio (%) = (Underwriting and Administrative Expenses / Premiums) × 100. Underwriting and administrative expenses typically include acquisition costs (such as agent and broker commissions, marketing expenses, and premium taxes), as well as operational costs associated with policy administration, underwriting staff salaries, technology, licensing fees, and general overhead. These expenses exclude claims payments and loss adjustment expenses, which are captured separately in the loss ratio. An important distinction exists in the choice of denominator: under statutory accounting conventions, the expense ratio often uses written premiums, since acquisition costs are recognized at the time a policy is written rather than spread over its duration. Under other accounting frameworks, earned premiums may be used. This difference can affect comparability across jurisdictions and should be noted when interpreting the ratio.
@@ -11177,454 +11479,181 @@
 !-Limitations and considerations: The expense ratio captures only the cost dimension of underwriting operations and does not reflect claims performance or investment returns. An insurer with a low expense ratio may still be unprofitable if its loss ratio is high, and conversely, a higher expense ratio may be justified if it reflects investment in distribution channels that expand access or improve policyholder service. Differences in business models significantly affect expense ratios: insurers relying on intermediary-based distribution typically report higher acquisition costs than those using direct or digital channels, without this necessarily indicating inefficiency. Similarly, insurers writing complex commercial lines may have higher underwriting expenses than those focused on standardized personal lines products. The use of written premiums versus earned premiums in the denominator can lead to meaningful differences in the reported ratio, particularly for insurers experiencing rapid premium growth or contraction, so care is needed when comparing across entities or jurisdictions using different accounting bases. Reinsurance arrangements can also affect the ratio, as ceding commissions received from reinsurers may offset reported expenses. The expense ratio should be interpreted alongside the loss ratio and combined ratio for a comprehensive view of underwriting performance.</t>
         </is>
       </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Sustainability (ESG)</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Climate and environmental objectives</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D201">
-        <v>330</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Rural credit (volume)</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>Number of loans in the retail loan portfolio designated as rural credit</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector, such as the volume of loans disbursed as a % of the total loan portfolio. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis.</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in access to rural credit by volume? Variations in this indicator may be explored across customer type, gender, age, location, income, FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Sustainability (ESG)</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Climate and environmental objectives</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D202">
-        <v>124</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>Climate and other environmental risk in the credit portfolio</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>Exposure of the credit portfolio to customers or industries with high climate (physical and transition risks) and other environmental risk</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>This indicator quantifies how much of the loan book is exposed to climate-related risks (physical and transition) and broader environmental risks (e.g., water stress, biodiversity loss, pollution). It helps firms and supervisors judge vulnerability to asset impairment, collateral devaluation, cash-flow shocks, and regulatory change. It also informs pricing, sector limits, and strategic portfolio alignment. Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type, product type, customer type and gender.</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>Credit risk</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Sustainability (ESG)</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Climate and environmental objectives</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D203">
-        <v>130</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Exposure to polluting firms/industries</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>Number of loans and total exposure of the credit portfolio to pollutting firms/industries</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>This indicator quantifies how much of the loan book is exposed to borrowers classified as big polluters (e.g., fossil fuel industry). The definition of polluting borrowers or activity varies widely across countries and the indicator should be aligned with national definitions. The EU uses a range of similar indicators: https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside financed emissions to explore whether FSPs with high polluting-sector exposures also show higher overall financed emissions, and whether both indicators are correlated with FSP gender diversity. Variations in this indicator may be explored across FSP type.</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>Credit risk</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Sustainability (ESG)</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Climate and environmental objectives</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D204">
-        <v>129</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Financed emissions (Carbon footprint of credit portfolio)</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Contribution of the financial sector to emissions (debtor's emissions financed by the financial sector via loan and securities portfolios)</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>This indicator, also known as carbon footprint, quantifies how much carbon emission the loan book is financing, by estimating the carbon emissions of financed activities and clients. The standardized calculations of emissions vary across countries and the indicator should align with national practices. In the EU, ther financed emissions (FE) indicator provides information on the financing of high-emitting economic activities. It tracks the amount of total carbon emissions from non-financial corporations (borrowers) that can be linked to funding from financial institutions, based on a set of identifiable securities and loan portfolios. See https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside green/sustainable loans to explore whether FSPs with a higher share of green lending also show lower financed emissions overall, and whether gender-diverse FSPs lead on both dimensions. Variations in this indicator may be explored across FSP type, customer type, gender, and product type.</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>Credit risk</t>
-        </is>
-      </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Sustainability (ESG)</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Climate and environmental objectives</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D205">
-        <v>21</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>Green/sustainable loans</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>% of all loans labelled as green or sustainable</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>This indicator shows the share of a regulated lender’s aggregate loan book that is formally designated green, social, or sustainable in an official taxonomy. A higher percentage signals that credit is being channelled toward activities aligned with climate-transition and inclusive-growth objectives, helping regulators gauge progress against national or international sustainable-finance targets and identify institutions with elevated exposure to taxonomy-related reputation or compliance risks. The indicator is an input for green-asset-ratio disclosures and climate-stress-testing frameworks. !- Definitions and concepts: The definition of green or sustainable loan varies widely across countries and should align with local frameworks. Whether a loan qualifies as green is determined by the regulatory taxonomy in force in the jurisdiction — such as the EU Taxonomy Regulation, which requires that a financed activity substantially contribute to at least one environmental objective (e.g., climate change mitigation or adaptation), do no significant harm to the others, and meet minimum social safeguards. Where no mandatory national taxonomy exists, classification may draw on voluntary international standards such as the UN Principles for Sustainable Insurance, the Green Bond Principles, or sector-specific guidelines, though these carry greater greenwashing risk in the absence of mandatory third-party verification. !- Data requirements: Loan-level tagging for use-of-proceeds or sustainability-performance targets, mapped to the applicable taxonomy code. Up-to-date balances to build the numerator and denominator. Dynamic criteria: Ongoing revisions to reference taxonomies may reclassify loans ex-post, creating series breaks.</t>
-        </is>
-      </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Are there gender disparities in access to green or sustainable loans? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, credit type, loan size, and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>Uptake (account ownership)</t>
+          <t>Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do insurers with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside the combined ratio to explore whether insurers with higher expense ratios are also those with higher combined ratios overall, and whether insurer gender diversity is associated with leaner operational and administrative cost structures. Variations in this indicator may be explored across insurer type, and type of insurance.</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Financial service provider (FSP) gender diversity; Insurance type</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Sustainability (ESG)</t>
+          <t>Stability, safety and soundness</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Climate and environmental objectives</t>
+          <t>Operational risk</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D206">
-        <v>331</v>
+        <v>402</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Rural credit (outstanding balance)</t>
+          <t>Suspected fraudulent transactions</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>% of the total retail loan portfolio that is rural credit based on outstanding balance</t>
+          <t>% of customer transactions flagged as suspected fraud</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis. !- Data requirements: Loan account level data, with details on date of disbursements, size of loan, payment schedule and repayments to date. Loan-level detail should have an existing agricultural classification or description of loan to enable classification.</t>
+          <t>Fraud detection systems generate alerts that may or may not correspond to genuine fraud events. Tracking the share of transactions flagged as suspected fraud before confirmation, gives supervisors and institutions a signal of attack volume, detection system sensitivity, and operational load on fraud teams. A rising flagging rate can indicate a surge in fraud attempts or a deterioration in model precision. When disaggregated by customer segment, this indicator exposes whether certain groups (e.g., women, youth, rural clients, low-income customers) are disproportionately targeted. This indicator measures the share of transactions initiated during a reporting period that are flagged by automated or manual systems as potentially fraudulent, prior to confirmation of actual fraud.  
+!- Definitions and concepts: A suspected fraud transaction is one flagged by a financial institution's detection system (eg rule-based, machine-learning, human review) as potentially fraudulent, regardless of whether the suspicion is subsequently confirmed. False positives (flagged transactions later confirmed as legitimate) are included in the numerator at the point of flagging and should be tracked separately to compute the fraud precision rate (see related indicator). Disaggregation by customer demographics requires linking transaction-level data to customer profiles with appropriate privacy safeguards.
+!- Data requirements: Total number of transactions initiated during the reporting period; number of transactions flagged as suspected fraud during the same period; where available, customer-level identifiers enabling sociodemographic disaggregation.</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Are there gender disparities in access to rural credit by outstanding balance? Variations in this indicator may be explored across customer type, gender, age, location, income, FSP type. This indicator can be analyzed alongside green/sustainable loans to explore the intersection of gender, climate, and rural finance. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Are certain customer groups disproportionately targeted by fraud attempts? Variations in this indicator may be explored across customer gender, age, income, location, type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base show different performance in this indicator? This indicator can be analyzed alongside confirmed fraud incidents faced by customers, to explore whether groups that face more confirmed fraud events are also subject to higher rates of flagging, or whether flagging patterns diverge from confirmed outcomes, which may signal detection bias affecting particular customer segments.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Consumer protection; Stability, safety and soundness; Financial inclusion</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Uptake (account ownership)</t>
+          <t>Safety and security, AML/CFT, Quality</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Sustainability (ESG)</t>
+          <t>Stability, safety and soundness</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Climate and environmental objectives</t>
+          <t>Operational risk</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D207">
-        <v>332</v>
+        <v>403</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Rural credit (principal disbursed)</t>
+          <t>Fraud precision rate</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>% of the total retail loan portfolio that is rural credit based on principal disbursed</t>
+          <t>% of flagged transactions that were confirmed as genuinely fraudulent</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis. !- Data requirements: Loan account level data, with details on date of disbursements, size of loan, payment schedule and repayments to date. Loan-level detail should have an existing agricultural classification or description of loan to enable classification.</t>
+          <t>A fraud detection system that flags too many legitimate transactions generates false positives that impose costs on customers (eg declined transactions, friction, distrust) and on institutions (eg manual review load, customer complaints). Conversely, a system with low precision may signal under-investment in detection quality. Monitoring precision rate alongside detection volume allows assessing whether fraud controls are well-calibrated and to benchmark across peers and over time. This indicator measures the proportion of transactions flagged as suspected fraud that are subsequently confirmed as genuinely fraudulent following investigation or adjudication. When disaggregated by customer segment, this indicator exposes whether precision is higher for certain groups, thus making them more exposed to risks. 
+!- Definitions and concepts: Precision rate = [# confirmed fraudulent transactions / # flagged transactions] × 100%. A confirmed fraudulent transaction is one where investigation has finished, determining that fraud occurred. Transactions still under investigation should be excluded from the denominator or reported separately to avoid distortion. The complement indicator (false positive rate) is equally important and should be reported alongside this indicator. Precision rates vary by detection channel (automated rules, machine-learning models, manual review) and by fraud type; institutions should be encouraged to report by detection channel where data permits.
+!- Data requirements: Total number of transactions flagged as suspected fraud during the reporting period; number of those flagged transactions subsequently confirmed as fraudulent following completed investigation; number of flagged transactions confirmed as legitimate (false positives); number of flagged transactions still under review at period end.</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Are there gender disparities in access to rural credit by principal disbursed? Variations in this indicator may be explored across customer gender, age, type, location, income, FSP type. This indicator can be analyzed alongside green/sustainable loans to explore the intersection of gender, climate, and rural finance. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Do fraud detection systems perform differently for different customer groups, and do false positives fall disproportionately on particular segments? Variations in this indicator may be explored across customer gender, age, income, location, type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base show different performance in this indicator? This indicator is important for sociodemographic analysis because low precision (high false positive rate) can result in the systematic blocking or friction of legitimate transactions for specific customer groups, constituting a form of bias with direct financial inclusion implications. It can be analyzed alongside the suspected fraudulent transaction rate to assess whether high flagging rates for a segment reflect genuine exposure or detection miscalibration.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Consumer protection; Financial inclusion</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Safety and security, Quality</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Sustainability (ESG)</t>
+          <t>Stability, safety and soundness</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Climate and environmental objectives</t>
+          <t>Operational risk</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D208">
-        <v>58</v>
+        <v>408</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Green/sustainable insurance</t>
+          <t>Fraud detection lag</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>% of all insurance policies that are green or sustainable</t>
+          <t>Average time elapsed between the execution of a fraudulent transaction and its detection</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>This indicator shows the share of an insurer's aggregate policy portfolio that is formally designated green, social, or sustainable. A higher percentage signals that insurance being channelled toward activities aligned with climate-transition and inclusive-growth objectives (e.g., crop insurance for agroforestry), helping regulators gauge progress against national or international sustainable-finance targets. !- Definitions and concepts: The definition of a green insurance product varies widely across countries and should align with local frameworks. Whether a product qualifies as green is determined by the regulatory taxonomy in force in the jurisdiction — such as the EU Taxonomy Regulation, which requires that a covered activity substantially contribute to at least one environmental objective (e.g., climate change mitigation or adaptation), do no significant harm to the others, and meet minimum social safeguards. For non-life insurance specifically, this typically means the product incorporates advanced climate risk modeling, prices climate risks accurately, rewards policyholders for preventive or environmentally responsible behavior, or provides coverage for green activities such as renewable energy, energy-efficient buildings, or low-emission vehicles. Where no mandatory national taxonomy exists, classification may draw on voluntary international standards such as the UN Principles for Sustainable Insurance or sector-specific industry guidelines, though these carry greater greenwashing risk in the absence of mandatory third-party verification. !- Data requirements: Policy-level tagging for sustainability-performance targets, mapped to the applicable taxonomy code.</t>
+          <t>This indicator measures the average time elapsed between the moment a fraudulent transaction was executed and the moment it was first detected (whether by the institution's own systems, by a third-party processor, or through customer notification) during a specified reporting period. The speed of fraud detection is a critical determinant of loss severity: the longer a fraudulent transaction goes undetected, the less likely it is that funds can be recovered, accounts hardened, or cascading damage (eg further unauthorised withdrawals or identity exploitation) prevented. Fraud detection lag captures the operational responsiveness of an institution's fraud control framework, complementing indicators that measure detection accuracy (fraud precision rate) and control effectiveness (fraud attempt success rate). A reduction in detection lag over time signals improving surveillance capabilities; persistently high lag may indicate over-reliance on customer self-reporting, inadequate real-time monitoring, or gaps in transaction data integration across channels. 
+!- Definitions and concepts: Detection is defined as the first formal identification of a transaction as suspected or confirmed fraud, recorded in the institution's fraud management system with a timestamp. The point of execution is the transaction settlement timestamp or, where settlement is delayed, the authorisation timestamp. Detection lag = [detection timestamp − execution timestamp], expressed in hours. The average should be computed across all confirmed fraud events in the reporting period. Because the distribution of detection lags is typically right-skewed (most fraud is detected quickly, but a tail of late-detected cases can be severe), FSPs should report both the mean and the median detection lag, and ideally the 90th percentile, to capture the worst-case tail. Detection lag should also be disaggregated by detection source: (1) institution-initiated detection (automated systems or manual review); (2) customer-initiated detection (customer reports the event before the institution identifies it); and (3) third-party notification (e.g., card network alerts, correspondent bank notices). This disaggregation is important because high reliance on customer-initiated detection signals a passive surveillance posture and understates the institution's monitoring capability. 
+!- Limitations and considerations: Detection lag is sensitive to how institutions define and timestamp the detection event. Inconsistent logging practices (for example, recording the date a case was formally opened rather than the date a system alert was generated) can artificially inflate or deflate reported lag. Supervisors should specify a standardised definition of the detection moment for reporting purposes. Detection lag also varies significantly by fraud type: card-not-present fraud and account takeover are often detected faster than social-engineering scams (e.g., authorised push payment fraud), where the customer may not recognise the loss for days or weeks. Reporting by fraud type alongside aggregate figures is therefore strongly encouraged.
+!- Data requirements: Confirmed fraud events during the reporting period, each with: transaction execution timestamp; detection timestamp; detection source (institution-automated, institution-manual, customer-reported, third-party); fraud type classification. From these: mean, median, and 90th-percentile detection lag overall and by detection source; share of fraud events detected by each source category.</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Are there gender disparities in access to and uptake of green or sustainable insurance products? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside green/sustainable loans to explore whether customer groups with lower access to green credit also show lower uptake of green insurance products.</t>
+          <t>Are fraud events affecting certain customer groups detected more slowly than those affecting others, and does detection speed vary depending on whether the customer or the institution initiates detection? Variations in this indicator may be explored across customer gender, age, income, location, type, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base show different performance in this indicator? Detection lag has an important sociodemographic dimension because customers with lower digital literacy or limited access to real-time account monitoring (eg elderly, rural, clients using feature phones) may be less able to identify and self-report fraud promptly, leading to systematically longer lags and larger losses for them. This indicator may be analyzed alongside fraud attempt success and fraud loss to examine whether longer detection lags translate into higher loss severity for specific segments.</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Consumer protection; Stability, safety and soundness; Financial inclusion</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Safety and security, AML/CFT, Quality</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -11646,35 +11675,50 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D209">
-        <v>41</v>
+        <v>330</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Holdings of green/sustainable bonds</t>
+          <t>Rural credit (volume)</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Volume (holdings) and value (amount outstanding) of sustainable/green bonds</t>
+          <t>Number of loans in the retail loan portfolio designated as rural credit</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>The indicator measures the aggregate value and volume of green and/or sustainability bonds held by investors, reflecting capital directed towards projects and activities with positive environmental or social impacts. It is a measure of sustainable finance. The definition of a green, social, or sustainable bond varies widely across countries and should align with local frameworks. Whether a bond qualifies as green or sustainable is determined by the regulatory taxonomy in force in the jurisdiction — such as the EU Taxonomy Regulation, which requires that the proceeds finance activities that substantially contribute to at least one environmental objective (e.g., climate change mitigation or adaptation), do no significant harm to the others, and meet minimum social safeguards. Where no mandatory national taxonomy exists, classification may draw on voluntary international standards such as the ICMA Green Bond Principles, the ICMA Social Bond Principles, the Climate Bonds Standard, or the UN SDG framework, though these carry greater greenwashing risk in the absence of mandatory second-party opinions or third-party verification.</t>
+          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector, such as the volume of loans disbursed as a % of the total loan portfolio. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis.</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Are there gender disparities in access to and participation in holding green or sustainable bonds? Variations in this indicator may be explored across customer type, gender, age, income, location. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? FSP type, and main activity.</t>
+          <t>Are there gender disparities in access to rural credit by volume? Variations in this indicator may be explored across customer type, gender, age, location, income, FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Usage</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -11691,45 +11735,45 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D210">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Issuances of green/sustainable bonds</t>
+          <t>Climate and other environmental risk in the credit portfolio</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Volume (issuances) and value (amount outstanding) of sustainable/green bonds</t>
+          <t>Exposure of the credit portfolio to customers or industries with high climate (physical and transition risks) and other environmental risk</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>This indicator tracks the number and, more commonly, the face value (in USD, EUR or local currency) of bonds labelled green, social, sustainability or sustainability-linked that reach primary markets in a given period. By capturing how much fresh capital is being channelled explicitly toward environmentally and/or socially beneficial projects, it offers a tangible gauge of the financial sector’s contribution to the transition to a low-carbon, inclusive economy. Policymakers use the series to monitor progress against climate-finance targets, assess the effectiveness of incentives such as tax exemptions or regulatory relief, and spot market slow-downs that could jeopardise net-zero pathways. The definition of a green, social, or sustainable bond varies widely across countries and should align with local frameworks. Whether a bond qualifies as green or sustainable is determined by the regulatory taxonomy in force in the jurisdiction — such as the EU Taxonomy Regulation, which requires that the proceeds finance activities that substantially contribute to at least one environmental objective (e.g., climate change mitigation or adaptation), do no significant harm to the others, and meet minimum social safeguards. Where no mandatory national taxonomy exists, classification may draw on voluntary international standards such as the ICMA Green Bond Principles, the ICMA Social Bond Principles, the Climate Bonds Standard, or the UN SDG framework, though these carry greater greenwashing risk in the absence of mandatory second-party opinions or third-party verification.</t>
+          <t>This indicator quantifies how much of the loan book is exposed to climate-related risks (physical and transition) and broader environmental risks (e.g., water stress, biodiversity loss, pollution). It helps firms and supervisors judge vulnerability to asset impairment, collateral devaluation, cash-flow shocks, and regulatory change. It also informs pricing, sector limits, and strategic portfolio alignment. Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Are there gender disparities in access to and participation in issuing green or sustainable bonds? Variations in this indicator may be explored across customer type, gender, FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside holdings of green/sustainable bonds to explore whether socio-demographic disparities in green bond issuance participation are mirrored by disparities in holding.</t>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type, product type, customer type and gender.</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -11746,30 +11790,30 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Savings, Credit, Insurance, Pensions</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D211">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Climate and other environmental risks in the investment portoflio</t>
+          <t>Exposure to polluting firms/industries</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Exposure of the investment portfolio to industries with high climate and other environmental risks</t>
+          <t>Number of loans and total exposure of the credit portfolio to pollutting firms/industries</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>This indicator quantifies how much of the investment book is exposed to climate-related risks (physical and transition) and broader environmental risks (e.g., water stress, biodiversity loss, pollution). It helps firms and supervisors judge vulnerability to asset impairment and regulatory change. Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, while the NGFS provides a range of additional definitions, including nature-related financial risks.</t>
+          <t>This indicator quantifies how much of the loan book is exposed to borrowers classified as big polluters (e.g., fossil fuel industry). The definition of polluting borrowers or activity varies widely across countries and the indicator should be aligned with national definitions. The EU uses a range of similar indicators: https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? This indicator can be analyzed alongside climate and other environmental risk in the credit portfolio to explore whether FSPs show consistent socio-demographic patterns in environmental risk exposure across both their lending and investment activities. Variations in this indicator may be explored across FSP type.</t>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside financed emissions to explore whether FSPs with high polluting-sector exposures also show higher overall financed emissions, and whether both indicators are correlated with FSP gender diversity. Variations in this indicator may be explored across FSP type.</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -11779,7 +11823,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Market risk, Credit risk</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -11796,35 +11840,45 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Diversity and inclusion</t>
+          <t>Climate and environmental objectives</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D212">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Gender diversity of FSP employees (by reference group)</t>
+          <t>Financed emissions (Carbon footprint of credit portfolio)</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Gender composition of FSP employee group, by level of responsibility (Board, management, staff)</t>
+          <t>Contribution of the financial sector to emissions (debtor's emissions financed by the financial sector via loan and securities portfolios)</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Measure used to assess the representation of different genders within a financial institution. It serves as a critical tool for evaluating a firm's commitment to inclusivity and is increasingly correlated with enhanced financial performance, risk management, and innovation. This indicator is not a single metric but a suite of measurements that can be applied across various levels of an organization. Ideally, it would be calculated at the board level, the senior management level (C suite), and the staff level. In some occasions, it can also be useful to calculate it for specific roles within the financial institution, such as branch managers, or agents, when analyzing differences in performance related to specific issues, such as consumer protection and conduct issues. In addition to being useful to monitor diversity at the system level, and its alignment with national gender equality policies, this indicator can also be used by prudential and conduct supervisors, as a growing body of knowledge points to improved financial and conduct performance of financial institutions that have a greater level of diversity. For prudential supervisors, this indicator serves as a valuable proxy for assessing a firm's health, as greater gender diversity is often correlated with stronger corporate governance, more prudent risk management, and enhanced financial stability.</t>
+          <t>This indicator, also known as carbon footprint, quantifies how much carbon emission the loan book is financing, by estimating the carbon emissions of financed activities and clients. The standardized calculations of emissions vary across countries and the indicator should align with national practices. In the EU, ther financed emissions (FE) indicator provides information on the financing of high-emitting economic activities. It tracks the amount of total carbon emissions from non-financial corporations (borrowers) that can be linked to funding from financial institutions, based on a set of identifiable securities and loan portfolios. See https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Are there gender disparities in FSP workforce participation across different levels of responsibility (board, management, staff)? Variations in this indicator may be explored across FSP type. By analyzing gender diversity with performance indicators and prudential rartios, how does gender diversity in FSP leadership correlate with key indicators such as ROE, ROA, capital adequacy ratio, efficiency ratio, liquidity ratio, interest margin ratio (for lenders), technical provisions (for insurers)? If gender equity requirements exist for FSPs, are they being met? Does gender diversity correlate with overall supervisory risk scores of risk-based prudential and conduct superivision, or enforcement actions?</t>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside green/sustainable loans to explore whether FSPs with a higher share of green lending also show lower financed emissions overall, and whether gender-diverse FSPs lead on both dimensions. Variations in this indicator may be explored across FSP type, customer type, gender, and product type.</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -11841,40 +11895,50 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Diversity and inclusion</t>
+          <t>Climate and environmental objectives</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D213">
-        <v>341</v>
+        <v>21</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Gender diversity of customer base</t>
+          <t>Green/sustainable loans</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Gender composition of FSP customer base</t>
+          <t>% of all loans labelled as green or sustainable</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Measures the representation of different genders—women, men, and non-binary individuals—among a financial institution's clients. This metric provides insights into a firm's market reach, product inclusiveness, and potential exposure to social and economic trends. This indicator can be used to monitor implementaton of gender equality targets and national policies, but also by prudential and conduct supervisors, to compare performance in other metrics, such as basic consumer risk indicators and prudential risk indicators, with the level of gender diversity of the customer base, with the purpose of finding any possible correlation.</t>
+          <t>This indicator shows the share of a regulated lender’s aggregate loan book that is formally designated green, social, or sustainable in an official taxonomy. A higher percentage signals that credit is being channelled toward activities aligned with climate-transition and inclusive-growth objectives, helping regulators gauge progress against national or international sustainable-finance targets and identify institutions with elevated exposure to taxonomy-related reputation or compliance risks. The indicator is an input for green-asset-ratio disclosures and climate-stress-testing frameworks. !- Definitions and concepts: The definition of green or sustainable loan varies widely across countries and should align with local frameworks. Whether a loan qualifies as green is determined by the regulatory taxonomy in force in the jurisdiction — such as the EU Taxonomy Regulation, which requires that a financed activity substantially contribute to at least one environmental objective (e.g., climate change mitigation or adaptation), do no significant harm to the others, and meet minimum social safeguards. Where no mandatory national taxonomy exists, classification may draw on voluntary international standards such as the UN Principles for Sustainable Insurance, the Green Bond Principles, or sector-specific guidelines, though these carry greater greenwashing risk in the absence of mandatory third-party verification. !- Data requirements: Loan-level tagging for use-of-proceeds or sustainability-performance targets, mapped to the applicable taxonomy code. Up-to-date balances to build the numerator and denominator. Dynamic criteria: Ongoing revisions to reference taxonomies may reclassify loans ex-post, creating series breaks.</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>What is the gender composition of each FSP's customer base across product types, and how has it evolved over time? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Variations in this indicator may be explored across FSP type, FSP location, product type, customer gender, age, income, and location. This indicator can be analyzed alongside gender diversity at FSP (by reference workforce group) to explore whether FSPs with greater internal gender diversity in their workforce also tend to serve a more gender-balanced customer base.</t>
+          <t>Are there gender disparities in access to green or sustainable loans? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, credit type, loan size, and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -11886,40 +11950,55 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Diversity and inclusion</t>
+          <t>Climate and environmental objectives</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D214">
-        <v>131</v>
+        <v>331</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Gender pay gap at FSPs</t>
+          <t>Rural credit (outstanding balance)</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Gender pay gap at FSPs</t>
+          <t>% of the total retail loan portfolio that is rural credit based on outstanding balance</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Metric that measures the difference in average (or median) earnings between genders across similar functions and roles at financial institutions. Typically calculated to spot differences across men and women, but it could be expanded to include other genders. It's typically expressed as a percentage of the higher earner gender (usually men's earnings), for a given role or hierarchical level at the financial institution. Prudential supervisors can use this indicator with a focus on the safety and soundness of financial institutions. A significant gender pay gap can be an indicator of underlying governance and operational risks. for conduct supervisors, a significant gender pay gap could be an indication of potential misconduct and unfairness that could affect customers. The gender pay gap is most commonly calculated as the mean or median difference in gross earnings between all male and female employees, expressed as a percentage of the male earnings.</t>
+          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis. !- Data requirements: Loan account level data, with details on date of disbursements, size of loan, payment schedule and repayments to date. Loan-level detail should have an existing agricultural classification or description of loan to enable classification.</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Are there gender pay gaps for similar roles and responsibility levels (board, management, staff) at FSPs? Variations in this indicator may be explored across FSP type. Do FSPs with greater board-level gender diversity tend to have smaller gender pay gaps? How do pay gap levels correlate with FSP performance indicators such as ROW, ROE, efficiency ratio, NPL, and delinquency? This indicator can be analyzed alongside the Human Resources Gender Index (HRGI) to explore whether FSPs with better overall gender HR policies, as captured in the HRGI, also show smaller gender pay gaps.</t>
+          <t>Are there gender disparities in access to rural credit by outstanding balance? Variations in this indicator may be explored across customer type, gender, age, location, income, FSP type. This indicator can be analyzed alongside green/sustainable loans to explore the intersection of gender, climate, and rural finance. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -11931,458 +12010,458 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
+          <t>Climate and environmental objectives</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D215">
+        <v>332</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Rural credit (principal disbursed)</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>% of the total retail loan portfolio that is rural credit based on principal disbursed</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis. !- Data requirements: Loan account level data, with details on date of disbursements, size of loan, payment schedule and repayments to date. Loan-level detail should have an existing agricultural classification or description of loan to enable classification.</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in access to rural credit by principal disbursed? Variations in this indicator may be explored across customer gender, age, type, location, income, FSP type. This indicator can be analyzed alongside green/sustainable loans to explore the intersection of gender, climate, and rural finance. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Sustainability (ESG)</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Climate and environmental objectives</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D216">
+        <v>58</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Green/sustainable insurance</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>% of all insurance policies that are green or sustainable</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>This indicator shows the share of an insurer's aggregate policy portfolio that is formally designated green, social, or sustainable. A higher percentage signals that insurance being channelled toward activities aligned with climate-transition and inclusive-growth objectives (e.g., crop insurance for agroforestry), helping regulators gauge progress against national or international sustainable-finance targets. !- Definitions and concepts: The definition of a green insurance product varies widely across countries and should align with local frameworks. Whether a product qualifies as green is determined by the regulatory taxonomy in force in the jurisdiction — such as the EU Taxonomy Regulation, which requires that a covered activity substantially contribute to at least one environmental objective (e.g., climate change mitigation or adaptation), do no significant harm to the others, and meet minimum social safeguards. For non-life insurance specifically, this typically means the product incorporates advanced climate risk modeling, prices climate risks accurately, rewards policyholders for preventive or environmentally responsible behavior, or provides coverage for green activities such as renewable energy, energy-efficient buildings, or low-emission vehicles. Where no mandatory national taxonomy exists, classification may draw on voluntary international standards such as the UN Principles for Sustainable Insurance or sector-specific industry guidelines, though these carry greater greenwashing risk in the absence of mandatory third-party verification. !- Data requirements: Policy-level tagging for sustainability-performance targets, mapped to the applicable taxonomy code.</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in access to and uptake of green or sustainable insurance products? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, type of insurance, and average premium. Do insurers with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside green/sustainable loans to explore whether customer groups with lower access to green credit also show lower uptake of green insurance products.</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Sustainability (ESG)</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Climate and environmental objectives</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="D217">
+        <v>41</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Holdings of green/sustainable bonds</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Volume (holdings) and value (amount outstanding) of sustainable/green bonds</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>The indicator measures the aggregate value and volume of green and/or sustainability bonds held by investors, reflecting capital directed towards projects and activities with positive environmental or social impacts. It is a measure of sustainable finance. The definition of a green, social, or sustainable bond varies widely across countries and should align with local frameworks. Whether a bond qualifies as green or sustainable is determined by the regulatory taxonomy in force in the jurisdiction — such as the EU Taxonomy Regulation, which requires that the proceeds finance activities that substantially contribute to at least one environmental objective (e.g., climate change mitigation or adaptation), do no significant harm to the others, and meet minimum social safeguards. Where no mandatory national taxonomy exists, classification may draw on voluntary international standards such as the ICMA Green Bond Principles, the ICMA Social Bond Principles, the Climate Bonds Standard, or the UN SDG framework, though these carry greater greenwashing risk in the absence of mandatory second-party opinions or third-party verification.</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in access to and participation in holding green or sustainable bonds? Variations in this indicator may be explored across customer type, gender, age, income, location. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? FSP type, and main activity.</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Sustainability (ESG)</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Climate and environmental objectives</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="D218">
+        <v>40</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Issuances of green/sustainable bonds</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Volume (issuances) and value (amount outstanding) of sustainable/green bonds</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>This indicator tracks the number and, more commonly, the face value (in USD, EUR or local currency) of bonds labelled green, social, sustainability or sustainability-linked that reach primary markets in a given period. By capturing how much fresh capital is being channelled explicitly toward environmentally and/or socially beneficial projects, it offers a tangible gauge of the financial sector’s contribution to the transition to a low-carbon, inclusive economy. Policymakers use the series to monitor progress against climate-finance targets, assess the effectiveness of incentives such as tax exemptions or regulatory relief, and spot market slow-downs that could jeopardise net-zero pathways. The definition of a green, social, or sustainable bond varies widely across countries and should align with local frameworks. Whether a bond qualifies as green or sustainable is determined by the regulatory taxonomy in force in the jurisdiction — such as the EU Taxonomy Regulation, which requires that the proceeds finance activities that substantially contribute to at least one environmental objective (e.g., climate change mitigation or adaptation), do no significant harm to the others, and meet minimum social safeguards. Where no mandatory national taxonomy exists, classification may draw on voluntary international standards such as the ICMA Green Bond Principles, the ICMA Social Bond Principles, the Climate Bonds Standard, or the UN SDG framework, though these carry greater greenwashing risk in the absence of mandatory second-party opinions or third-party verification.</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in access to and participation in issuing green or sustainable bonds? Variations in this indicator may be explored across customer type, gender, FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside holdings of green/sustainable bonds to explore whether socio-demographic disparities in green bond issuance participation are mirrored by disparities in holding.</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Sustainability (ESG)</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Climate and environmental objectives</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Savings, Credit, Insurance, Pensions</t>
+        </is>
+      </c>
+      <c r="D219">
+        <v>126</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Climate and other environmental risks in the investment portoflio</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Exposure of the investment portfolio to industries with high climate and other environmental risks</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>This indicator quantifies how much of the investment book is exposed to climate-related risks (physical and transition) and broader environmental risks (e.g., water stress, biodiversity loss, pollution). It helps firms and supervisors judge vulnerability to asset impairment and regulatory change. Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, while the NGFS provides a range of additional definitions, including nature-related financial risks.</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? This indicator can be analyzed alongside climate and other environmental risk in the credit portfolio to explore whether FSPs show consistent socio-demographic patterns in environmental risk exposure across both their lending and investment activities. Variations in this indicator may be explored across FSP type.</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Market risk, Credit risk</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Sustainability (ESG)</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
           <t>Diversity and inclusion</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D215">
+      <c r="D220">
+        <v>11</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Gender diversity of FSP employees (by reference group)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Gender composition of FSP employee group, by level of responsibility (Board, management, staff)</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Measure used to assess the representation of different genders within a financial institution. It serves as a critical tool for evaluating a firm's commitment to inclusivity and is increasingly correlated with enhanced financial performance, risk management, and innovation. This indicator is not a single metric but a suite of measurements that can be applied across various levels of an organization. Ideally, it would be calculated at the board level, the senior management level (C suite), and the staff level. In some occasions, it can also be useful to calculate it for specific roles within the financial institution, such as branch managers, or agents, when analyzing differences in performance related to specific issues, such as consumer protection and conduct issues. In addition to being useful to monitor diversity at the system level, and its alignment with national gender equality policies, this indicator can also be used by prudential and conduct supervisors, as a growing body of knowledge points to improved financial and conduct performance of financial institutions that have a greater level of diversity. For prudential supervisors, this indicator serves as a valuable proxy for assessing a firm's health, as greater gender diversity is often correlated with stronger corporate governance, more prudent risk management, and enhanced financial stability.</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in FSP workforce participation across different levels of responsibility (board, management, staff)? Variations in this indicator may be explored across FSP type. By analyzing gender diversity with performance indicators and prudential rartios, how does gender diversity in FSP leadership correlate with key indicators such as ROE, ROA, capital adequacy ratio, efficiency ratio, liquidity ratio, interest margin ratio (for lenders), technical provisions (for insurers)? If gender equity requirements exist for FSPs, are they being met? Does gender diversity correlate with overall supervisory risk scores of risk-based prudential and conduct superivision, or enforcement actions?</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Sustainability (ESG)</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Diversity and inclusion</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D221">
+        <v>341</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Gender diversity of customer base</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Gender composition of FSP customer base</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Measures the representation of different genders—women, men, and non-binary individuals—among a financial institution's clients. This metric provides insights into a firm's market reach, product inclusiveness, and potential exposure to social and economic trends. This indicator can be used to monitor implementaton of gender equality targets and national policies, but also by prudential and conduct supervisors, to compare performance in other metrics, such as basic consumer risk indicators and prudential risk indicators, with the level of gender diversity of the customer base, with the purpose of finding any possible correlation.</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>What is the gender composition of each FSP's customer base across product types, and how has it evolved over time? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Variations in this indicator may be explored across FSP type, FSP location, product type, customer gender, age, income, and location. This indicator can be analyzed alongside gender diversity at FSP (by reference workforce group) to explore whether FSPs with greater internal gender diversity in their workforce also tend to serve a more gender-balanced customer base.</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Sustainability (ESG)</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Diversity and inclusion</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D222">
+        <v>131</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Gender pay gap at FSPs</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Gender pay gap at FSPs</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Metric that measures the difference in average (or median) earnings between genders across similar functions and roles at financial institutions. Typically calculated to spot differences across men and women, but it could be expanded to include other genders. It's typically expressed as a percentage of the higher earner gender (usually men's earnings), for a given role or hierarchical level at the financial institution. Prudential supervisors can use this indicator with a focus on the safety and soundness of financial institutions. A significant gender pay gap can be an indicator of underlying governance and operational risks. for conduct supervisors, a significant gender pay gap could be an indication of potential misconduct and unfairness that could affect customers. The gender pay gap is most commonly calculated as the mean or median difference in gross earnings between all male and female employees, expressed as a percentage of the male earnings.</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Are there gender pay gaps for similar roles and responsibility levels (board, management, staff) at FSPs? Variations in this indicator may be explored across FSP type. Do FSPs with greater board-level gender diversity tend to have smaller gender pay gaps? How do pay gap levels correlate with FSP performance indicators such as ROW, ROE, efficiency ratio, NPL, and delinquency? This indicator can be analyzed alongside the Human Resources Gender Index (HRGI) to explore whether FSPs with better overall gender HR policies, as captured in the HRGI, also show smaller gender pay gaps.</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Sustainability (ESG)</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Diversity and inclusion</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D223">
         <v>18</v>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="E223" t="inlineStr">
         <is>
           <t>Human Resources Gender Index (HRGI)</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
+      <c r="F223" t="inlineStr">
         <is>
           <t>Index based on FSPs' gender diversity policies, covering gender and employment, gender earnings, leave and work arrangements, childcare, and other benefits</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
+      <c r="G223" t="inlineStr">
         <is>
           <t>The Human Resources Gender Index (HRGI) is a composite index that consolidates multiple HR data points to provide a holistic score of gender equality within an institution, throughout the employee lifecycle. It is not a standardized indicator. It can be defined as a weighted score that measures a financial institution's gender equality across key HR areas, including representation, remuneration, recruitment, promotion, and retention, going way beyond headcount. Potential indicator components include: representation score (gender diversity at different corporate levels), pay equality score (mean and median pay gap), gender gap in performance-based bonuses, progression score (promotion rate gender gap, recruitment score (% of women among new hires, especially at senior levels), retention score (gender gap in turnover rate).  This indicator can be used to monitor implementaton of gender equality targets and national policies, but also by prudential and conduct supervisors, to compare performance in other metrics, such as basic consumer risk indicators and prudential risk indicators, with the level of gender diversity of the customer base, with the purpose of finding any possible correlation. https://www.elibrary.imf.org/view/journals/001/2023/091/article-A001-en.xml
 .</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
+      <c r="H223" t="inlineStr">
         <is>
           <t>How do FSPs compare in their HRGI scores across dimensions of representation, pay equity, recruitment, promotion, and retention? Do FSPs with higher HRGI scores tend to perform better on key financial indicators (capital adequacy, profitability, NPL rates, consumer protection outcomes)? How do HRGI scores vary by FSP type and region?</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
+      <c r="L223" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Sustainability (ESG)</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Diversity and inclusion</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D216">
-        <v>13</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>Success rate of license applications by diverse FSPs</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>% of all license applications by diverse FSPs that are issued</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>This indicator is a measure of potential gender biases in licensing decisions by the financial authority. It helps authorities analyze the success rate of license pplications by segmenting applications by their final oucome (rejection/approval), and the gender of the lead sponsor of the application (e.g., the majority individual shareholder). The definition of lead sponsor will vary across countries and the indicator should align with local practices.</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Do applications by FSPs with greater gender diversity in their management or board show different probably of being approved? This indicator can be analyzed alongside new licenses granted to diverse FSPs to explore whether the overall volume of licenses granted to gender-diverse FSPs reflects a higher application success rate, or simply more applications. Variations in this indicator may be explored across FSP type.</t>
-        </is>
-      </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Capital markets development</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Investments</t>
-        </is>
-      </c>
-      <c r="D217">
-        <v>45</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>Crowdfunding - Differential rate of return (equity)</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>Difference between the advertised/promised rate of return and the actual rate of return of equity in crowdfunding projects</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>Measures the gap between the projected or advertised rate of return presented to investors before a project is funded and the actual rate of return realized after the project is completed. This is a critical conduct indicator that measures the accuracy of a project's promises versus its real-world performance. For investors, this metric is a tool for due diligence. For conduct supervisors, it can be used to detect mis-selling and fraud. A large and persistent negative differential (where actual returns are consistently far below promised returns) is a red flag. it could flag issues such as inadequate risk disclosure and fraud. When gender disaggregated by the gender of the main sponsor or lead executive, the indicator can provide additional information. If projects led by women consistently show a smaller negative "reality gap" (meaning their actual returns are closer to their promised returns), it could suggest they are more conservative or accurate in their financial projections. This would be a crucial data point in assessing risk and investor protection. Using this indicator together with the indicator on rejected crowddfunding projects could strenghten the identification of gender bias inside the securities authority. Return Differential (%) = Actual Rate of Return - Advertised/Promised Rate of Return.</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in crowdfunding differential rate of return (equity)? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, and product type. Do crowdfunding platforms with more gender-diverse management show more equitable outcomes for female campaign sponsors?</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>Uptake (account ownership)</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Capital markets development</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Investments</t>
-        </is>
-      </c>
-      <c r="D218">
-        <v>44</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>Crowdfunding - Authorization rejection rate</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>% of all crowfunding applications that are rejected (not authorized by the securities authority)</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>Measures the percentage of all crowdfunding applications submitted to a securities authority that are denied or not authorized to proceed with fundraising. This is a key regulatory indicator that reflects the quality of applications being submitted and the stringency of the regulator's vetting process, which is designed to protect investors from fraud and non-viable projects. When disaggregated by the gender of the main sponsor, the lead executive of the company, it could draw insights into potential gender biases working within the securities authority.</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in crowdfunding authorization rejection rate? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, and product type. Do crowdfunding platforms with more gender-diverse management show more equitable outcomes for female campaign sponsors?This indicator can be analyzed alongside crowdfunding – success rate to explore whether customer groups facing higher authorization rejection rates also show lower overall success rates.</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Capital markets development</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Investments</t>
-        </is>
-      </c>
-      <c r="D219">
-        <v>43</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>Crowdfunding - Success rate</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>% of all crowfunding projects that are successful in raising the asked amount</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>The indicator is a metric that measures the proportion of projects on a crowdfunding platform (or the sum of all crowdfunding platforms) that successfully reach their predetermined funding goal within a specified timeframe. This indicator is a vital sign of a platform's effectiveness, credibility, and the overall health of its ecosystem. It helps gauge the ability of a platform to connect viable projects with interested backers. For MSMEs, crowdfunding can be a viable and less onerous funding source, so the indicator provids important information for monitoring development of MSME finance markets. From a market conduct perspective, while a high success rate is generally positive, an unusually high or artificially inflated rate could be a red flag for misconduct. Platforms could be setting trivially low funding goals to boost statistics,  failing to conduct proper due diligence on projects, or not being transparent about how the success rate is calculated. Successful projects is the number of projects that met or exceeded their funding target during a specific period (e.g., a month, quarter, or year).</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in crowdfunding success rate, and do women-led ventures face different rates or outcomes compared to men? Variations in this indicator may be explored across customer type, gender, income, age, location, FSP type, and product type. Do crowdfunding platforms with more gender-diverse management show more equitable outcomes for female campaign sponsors?</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Capital markets development</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Investments</t>
-        </is>
-      </c>
-      <c r="D220">
-        <v>42</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>Crowdfunding - Transactions</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>Volume (number of offerings) and value (amount raised) of crowdfunding transactions</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>Metric that measures the total volume of individual investments or pledges made across all projects on a crowdfunding platform or in the entire market (across multiple platforms) over a specific period. This indicator is a direct measure of market activity and investor engagement with crowdfunding, which is increasingly important for MSME finance.</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in crowdfunding transactions, and do women-led ventures face different rates or outcomes compared to men? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, and product type. Do crowdfunding platforms with more gender-diverse management show more equitable outcomes for female campaign sponsors? This indicator can be analyzed alongside crowdfunding – success rate to explore whether socio-demographic disparities in the volume of crowdfunding campaigns are compounded by disparities in success rates.</t>
-        </is>
-      </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Capital markets development</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Investments</t>
-        </is>
-      </c>
-      <c r="D221">
-        <v>46</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>P2P - Investors</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>Number of P2P investors</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>This indicator counts the number of investors registered in P2P lending platforms, as a measure of development of digital finance, and specifically P2P lending, which can potentially benefit MSMEs. It is a key metric to monitor market development in platform lending. It helps assess the effectiveness of marketing campaigns, measure market reach, and forecast potential loan demand or the ability of platforms to meet demand. A growing investor base indicates increased trust and interest, enabling the business to scale and optimize revenue generation. The indicator should be segmented by type of investor (e.g., retail investor, institutional investor), according to local regulatory definitions.</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Are there gender disparities across P2P investors? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside P2P – credit operations to explore whether socio-demographic disparities on the investor side of P2P markets are mirrored by disparities on the borrower side.</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Capital markets development</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Investments</t>
-        </is>
-      </c>
-      <c r="D222">
-        <v>9</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>Total investment fund shares</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>Number of investment fund shares held by retail investors in the system</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>Market-wide metric that quantifies the volume of investment fund shares owned by individual, non-professional investors within a financial system. This market develoment indicator serves as a crucial gauge of retail investor participation in the capital markets, and their overall exposure to market risks. Companion indicators include the share of investment fund shares held by retail investors as percentage of total investment fund shares, and the average holding size by retail investors.</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in the ownership of investment fund shares? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? This indicator can be analyzed alongside investment accounts (outstanding balance) to explore whether socio-demographic disparities in fund share ownership are proportional to disparities in total investment account balances.</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>Uptake (account ownership)</t>
-        </is>
-      </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Savings, Credit</t>
-        </is>
-      </c>
-      <c r="D223">
-        <v>267</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>Interest rate spreads (loans)</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>Difference between the average lending rate and a reference rate (e.g. deposit rate or external reference rate)</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>The interest-rate spread on loans captures the margin between the average contractual rate a lender charges borrowers and an external reference rate—typically the policy rate. It is a concise gauge of (i) lenders’ credit-risk pricing, (ii) competitive conditions in the lending market, and (iii) monetary-policy transmission. Wider spreads may reflect higher perceived borrower risk, limited competition, or funding-cost pressures; persistently narrow spreads can point to aggressive underwriting or excess liquidity that may undermine future asset quality. Tracked over time and across peer institutions, interest-rate spreads provide insights into credit-cycle turning points, profitability dynamics, and the effectiveness of monetary-policy signals reaching the real economy. !- Definitions and concepts:  Loan interest rate spread (simple): Average contractual loan rate minus Reference rate measured for new originations or for the stock of loans. Net lending spread: average loan rate minus average deposit rate, often used when policy benchmarks are volatile. Segmented spreads: calculated by product (e.g., mortgages, MSMEs, credit cards). Non-interest charges: fees and cross-selling income are excluded; the true all-in lending margin may be higher.</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in the interest rate spreads faced by borrowers? Variations in this indicator may be explored across customer gender, customer type, age, income, location, FSP type, credit type, loan size, and loan term. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside annual percentage rate (APR) for retail credit to explore whether customer groups facing higher APRs are concentrated in loan types or FSPs that also show wider spreads over reference rates.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>Quality, Fair treatment</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Market development</t>
+          <t>Sustainability (ESG)</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Diversity and inclusion</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -12391,46 +12470,31 @@
         </is>
       </c>
       <c r="D224">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Open finance - % of customers that have given data sharing consent to FSPs</t>
+          <t>Success rate of license applications by diverse FSPs</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>% of all customers that have given consent to participate in the open finance scheme</t>
+          <t>% of all license applications by diverse FSPs that are issued</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>The indicator shows how many customers have actively opted in to share their data via the open finance rails (e.g., with account information service providers or payment initiation service providers). A higher share signals trust, clear value propositions, and mature consent customer interfaces (mobile apps); a low or falling rate may reflect friction in UX or Strong Customer Authentication (SCA), poor messaging, or privacy concerns. It’s a headline adoption KPI for open finance schemes. !- Definitions and concepts: Explicit consent: a clear, affirmative action tied to a specific purpose with the ability to manage and withdraw. Active consent: valid as of the reference date (not expired/withdrawn). Open finance consenting customers (%) = [# unique customers with at least 1 open finance consent / # eligible customers] x 100%. Denominator options: all active retail/MSME customers (preferred) or customers with eligible accounts (state choice). Segment by purpose of consent, scope (accounts included), and channel (mobile/web). Duplication &amp; scope: a customer may hold multiple consents across TPPs; count unique customers, and compare with total count of consents. Lawful-basis nuance: exclude sharing done under contractual necessity or legal obligation (e.g., consultation to credit bureaus for a loan application)—this metric is about explicit consent only.</t>
+          <t>This indicator is a measure of potential gender biases in licensing decisions by the financial authority. It helps authorities analyze the success rate of license pplications by segmenting applications by their final oucome (rejection/approval), and the gender of the lead sponsor of the application (e.g., the majority individual shareholder). The definition of lead sponsor will vary across countries and the indicator should align with local practices.</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Are there gender disparities in data sharing consent rates for open finance? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside consents for sharing data with third parties to explore whether customer groups consenting to data sharing within open finance schemes are also more likely to share data with third parties.</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>Consumer protection; Stability, safety and soundness; Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>Data privacy and protection, Operational risk, Quality</t>
+          <t>Do applications by FSPs with greater gender diversity in their management or board show different probably of being approved? This indicator can be analyzed alongside new licenses granted to diverse FSPs to explore whether the overall volume of licenses granted to gender-diverse FSPs reflects a higher application success rate, or simply more applications. Variations in this indicator may be explored across FSP type.</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -12442,55 +12506,50 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D225">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Open finance - API availability</t>
+          <t>Crowdfunding - Differential rate of return (equity)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Average % of time APIs are available</t>
+          <t>Difference between the advertised/promised rate of return and the actual rate of return of equity in crowdfunding projects</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Shows the proportion of clock time that open finance endpoints can successfully serve requests. High availability is critical for data users such as third-party providers (TPPs) to deliver reliable account information and payment initiation; poor uptime breaks customer journeys, breaches SLAs/SLOs, and can trigger regulatory scrutiny in open finance schemes. !- Definitions and concepts: Availability (uptime):  time-weighted share of intervals in which an endpoint meets both reachability and success criteria. Scope — include account information service, payment initiation service, consent/token endpoints, and webhooks if they’re required for completion. Planned vs. unplanned:  exclude planned maintenance time; report maintenance windows separately. SLO period: availability is usually measured monthly/quarterly (e.g., 99.9% per calendar month), but preferably in shorter periods (e.g., weekly, daily). Granularity: overall availability, by endpoint family, region/zone, and time of day. Example indicator: Availability = 1 - [Downtime / Total scheduled time] where Downtime aggregates intervals failing the success criterion (5xx gateway/network timeouts, auth outages, or latency breaches). !- Limitations and considerations: Including latency SLOs will lower availability vs. status-only measurements. Publish thresholds.</t>
+          <t>Measures the gap between the projected or advertised rate of return presented to investors before a project is funded and the actual rate of return realized after the project is completed. This is a critical conduct indicator that measures the accuracy of a project's promises versus its real-world performance. For investors, this metric is a tool for due diligence. For conduct supervisors, it can be used to detect mis-selling and fraud. A large and persistent negative differential (where actual returns are consistently far below promised returns) is a red flag. it could flag issues such as inadequate risk disclosure and fraud. When gender disaggregated by the gender of the main sponsor or lead executive, the indicator can provide additional information. If projects led by women consistently show a smaller negative "reality gap" (meaning their actual returns are closer to their promised returns), it could suggest they are more conservative or accurate in their financial projections. This would be a crucial data point in assessing risk and investor protection. Using this indicator together with the indicator on rejected crowddfunding projects could strenghten the identification of gender bias inside the securities authority. Return Differential (%) = Actual Rate of Return - Advertised/Promised Rate of Return.</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Does API infrastructure for open finance show performance differences across FSPs that could disproportionately affect digital-first FSPs serving gender-diverse or underserved customer bases? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside open finance – API error rate and open finance – API response time to explore whether FSPs with lower API availability also show higher error rates and slower response times. Variations in this indicator may be explored across FSP type and API type.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Are there gender disparities in crowdfunding differential rate of return (equity)? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, and product type. Do crowdfunding platforms with more gender-diverse management show more equitable outcomes for female campaign sponsors?</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Financial inclusion; Stability, safety and soundness; Consumer protection</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Quality, Operational risk, Fair treatment</t>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -12502,55 +12561,40 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D226">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Open finance - API error rate</t>
+          <t>Crowdfunding - Authorization rejection rate</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>% of all API calls that are unsuccessful</t>
+          <t>% of all crowfunding applications that are rejected (not authorized by the securities authority)</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>This indicator tracks the reliability of open-finance interfaces by showing what share of API requests do not complete successfully due to errors. It is a key API performance indicator monitored by financial authorities implementing open finance. High failure rates degrade customer journeys (consent, data retrieval, payment initiation), inflate support costs, and can breach SLA/SLO commitments. !- Definitions and concepts: API call (request): one HTTP request to a documented endpoint, for example: Account Information Services (AIS) data, Payment Initiatiion Services (PIS) payment, consent, token, webhook, etc. Unsuccessful call: define as per local regulation. This indicator can be collected segmented by types of errors, to be defined as per local regulation (e.g., gateway/network timeouts, invalid/expired token/consent, error in validation, authentication failures. It should also be segmented by type of endpoint, as per local categorization (e.g., account information request, payment initiation request, other). Example indicator: [# of errors  /  # total API calls] x 100%.</t>
+          <t>Measures the percentage of all crowdfunding applications submitted to a securities authority that are denied or not authorized to proceed with fundraising. This is a key regulatory indicator that reflects the quality of applications being submitted and the stringency of the regulator's vetting process, which is designed to protect investors from fraud and non-viable projects. When disaggregated by the gender of the main sponsor, the lead executive of the company, it could draw insights into potential gender biases working within the securities authority.</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Does API error rate show performance differences that could disproportionately affect digital-first FSPs serving gender-diverse and underserved customer bases? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type and API type.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>Quality, Operational risk</t>
+          <t>Are there gender disparities in crowdfunding authorization rejection rate? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, and product type. Do crowdfunding platforms with more gender-diverse management show more equitable outcomes for female campaign sponsors?This indicator can be analyzed alongside crowdfunding – success rate to explore whether customer groups facing higher authorization rejection rates also show lower overall success rates.</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -12562,55 +12606,50 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D227">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Open finance - API response time</t>
+          <t>Crowdfunding - Success rate</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Average API response time</t>
+          <t>% of all crowfunding projects that are successful in raising the asked amount</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Shows how quickly open-finance endpoints answer requests. Faster responses improve user experience during consent, account-information retrieval, and payment initiation, reducing frictions and drop-offs. Response time is a core performance KPI that complements availability and error rate. !- Definitions and concepts: Response time (latency): elapsed time between request start and final byte received (client-observed) or gateway in → gateway out (server-observed). Track both when possible. Averages vs. tails: report p50/median, p95, p99, and the mean; tails (p95/p99) best reflect user pain. Track both. Granularity: report by endpoint family (types of APIs), potentially segmented into priority levels (see https://www.cdr.gov.au/performance). Units &amp; window: milliseconds, by calendar month (preferably shorter SLO period, such as weekly or daily).</t>
+          <t>The indicator is a metric that measures the proportion of projects on a crowdfunding platform (or the sum of all crowdfunding platforms) that successfully reach their predetermined funding goal within a specified timeframe. This indicator is a vital sign of a platform's effectiveness, credibility, and the overall health of its ecosystem. It helps gauge the ability of a platform to connect viable projects with interested backers. For MSMEs, crowdfunding can be a viable and less onerous funding source, so the indicator provids important information for monitoring development of MSME finance markets. From a market conduct perspective, while a high success rate is generally positive, an unusually high or artificially inflated rate could be a red flag for misconduct. Platforms could be setting trivially low funding goals to boost statistics,  failing to conduct proper due diligence on projects, or not being transparent about how the success rate is calculated. Successful projects is the number of projects that met or exceeded their funding target during a specific period (e.g., a month, quarter, or year).</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Does API call response time show performance differences that could disproportionately affect digital-first FSPs serving gender-diverse or underserved customer bases? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type, and API type.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Are there gender disparities in crowdfunding success rate, and do women-led ventures face different rates or outcomes compared to men? Variations in this indicator may be explored across customer type, gender, income, age, location, FSP type, and product type. Do crowdfunding platforms with more gender-diverse management show more equitable outcomes for female campaign sponsors?</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Financial inclusion; Stability, safety and soundness; Consumer protection</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Quality, Operational risk, Fair treatment</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -12622,45 +12661,40 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D228">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Open finance - Payment initiation transactions</t>
+          <t>Crowdfunding - Transactions</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Number of payment initiation transactions conducted in the open finance scheme</t>
+          <t>Volume (number of offerings) and value (amount raised) of crowdfunding transactions</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Counts how many account-to-account (A2A) payment orders were successfully initiated via open-finance rails in the period. It’s a core adoption and usage KPI for Payment Initiation Services (PIS): more transactions imply growing merchant and P2P acceptance of openb finance, customer trust, and TPP–bank interoperability. !- Definitions and concepts: Payment initiation transaction (PIT): a payment order created via an authorized PISP/TPP and accepted by the ASPSP (account holder) for processing. Companion counts: Failed payment initiation transactions. Refunds/returns/chargebacks tracked separately. Sub-types: single immediate payments, scheduled payments, recurring/VRP (variable recurring payments), instant vs. ACH/batch. !- Data requirements: Total number of successful payment initiation transactions. !- Limitations and considerations: Duplicates: avoid double counting by using operation IDs.</t>
+          <t>Metric that measures the total volume of individual investments or pledges made across all projects on a crowdfunding platform or in the entire market (across multiple platforms) over a specific period. This indicator is a direct measure of market activity and investor engagement with crowdfunding, which is increasingly important for MSME finance.</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the use of payment initiation services through open finance channels? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside access to the instant/fast payment system to explore whether socio-demographic gaps in payment initiation through open finance channels are related to gaps in registration in the instant payment system.</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Are there gender disparities in crowdfunding transactions, and do women-led ventures face different rates or outcomes compared to men? Variations in this indicator may be explored across customer type, gender, age, income, location, FSP type, and product type. Do crowdfunding platforms with more gender-diverse management show more equitable outcomes for female campaign sponsors? This indicator can be analyzed alongside crowdfunding – success rate to explore whether socio-demographic disparities in the volume of crowdfunding campaigns are compounded by disparities in success rates.</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -12672,174 +12706,624 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
+          <t>Capital markets development</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="D229">
+        <v>46</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>P2P - Investors</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Number of P2P investors</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>This indicator counts the number of investors registered in P2P lending platforms, as a measure of development of digital finance, and specifically P2P lending, which can potentially benefit MSMEs. It is a key metric to monitor market development in platform lending. It helps assess the effectiveness of marketing campaigns, measure market reach, and forecast potential loan demand or the ability of platforms to meet demand. A growing investor base indicates increased trust and interest, enabling the business to scale and optimize revenue generation. The indicator should be segmented by type of investor (e.g., retail investor, institutional investor), according to local regulatory definitions.</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Are there gender disparities across P2P investors? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside P2P – credit operations to explore whether socio-demographic disparities on the investor side of P2P markets are mirrored by disparities on the borrower side.</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Capital markets development</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="D230">
+        <v>9</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Total investment fund shares</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Number of investment fund shares held by retail investors in the system</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Market-wide metric that quantifies the volume of investment fund shares owned by individual, non-professional investors within a financial system. This market develoment indicator serves as a crucial gauge of retail investor participation in the capital markets, and their overall exposure to market risks. Companion indicators include the share of investment fund shares held by retail investors as percentage of total investment fund shares, and the average holding size by retail investors.</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Are there disparities in the ownership of investment fund shares associated with customer type, gender, age, income, location, or FSP type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? This indicator can be analyzed alongside investment accounts (outstanding balance) to explore whether socio-demographic disparities in fund share ownership are proportional to disparities in total investment account balances.</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Uptake (account ownership)</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Savings, Credit</t>
+        </is>
+      </c>
+      <c r="D231">
+        <v>267</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Interest rate spreads (loans)</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Difference between the average lending rate and a reference rate (e.g. deposit rate or external reference rate)</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>The interest-rate spread on loans captures the margin between the average contractual rate a lender charges borrowers and an external reference rate—typically the policy rate. It is a concise gauge of (i) lenders’ credit-risk pricing, (ii) competitive conditions in the lending market, and (iii) monetary-policy transmission. Wider spreads may reflect higher perceived borrower risk, limited competition, or funding-cost pressures; persistently narrow spreads can point to aggressive underwriting or excess liquidity that may undermine future asset quality. Tracked over time and across peer institutions, interest-rate spreads provide insights into credit-cycle turning points, profitability dynamics, and the effectiveness of monetary-policy signals reaching the real economy. !- Definitions and concepts:  Loan interest rate spread (simple): Average contractual loan rate minus Reference rate measured for new originations or for the stock of loans. Net lending spread: average loan rate minus average deposit rate, often used when policy benchmarks are volatile. Segmented spreads: calculated by product (e.g., mortgages, MSMEs, credit cards). Non-interest charges: fees and cross-selling income are excluded; the true all-in lending margin may be higher.</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Are there disparities in the interest rate spreads faced by borrowers associated with customer gender, customer type, age, income, location, FSP type, credit type, loan size, or loan term? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside annual percentage rate (APR) for retail credit to explore whether customer groups facing higher APRs are concentrated in loan types or FSPs that also show wider spreads over reference rates.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Quality, Fair treatment</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
         <is>
           <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D229">
+      <c r="D232">
+        <v>35</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Open finance - % of customers that have given data sharing consent to FSPs</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>% of all customers that have given consent to participate in the open finance scheme</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>The indicator shows how many customers have actively opted in to share their data via the open finance rails (e.g., with account information service providers or payment initiation service providers). A higher share signals trust, clear value propositions, and mature consent customer interfaces (mobile apps); a low or falling rate may reflect friction in UX or Strong Customer Authentication (SCA), poor messaging, or privacy concerns. It’s a headline adoption KPI for open finance schemes. !- Definitions and concepts: Explicit consent: a clear, affirmative action tied to a specific purpose with the ability to manage and withdraw. Active consent: valid as of the reference date (not expired/withdrawn). Open finance consenting customers (%) = [# unique customers with at least 1 open finance consent / # eligible customers] x 100%. Denominator options: all active retail/MSME customers (preferred) or customers with eligible accounts (state choice). Segment by purpose of consent, scope (accounts included), and channel (mobile/web). Duplication &amp; scope: a customer may hold multiple consents across TPPs; count unique customers, and compare with total count of consents. Lawful-basis nuance: exclude sharing done under contractual necessity or legal obligation (e.g., consultation to credit bureaus for a loan application)—this metric is about explicit consent only.</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in data sharing consent rates for open finance? Variations in this indicator may be explored across customer type, gender, age, income, location, and FSP type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside consents for sharing data with third parties to explore whether customer groups consenting to data sharing within open finance schemes are also more likely to share data with third parties.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Consumer protection; Stability, safety and soundness; Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Data privacy and protection, Operational risk, Quality</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D233">
+        <v>36</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Open finance - API availability</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Average % of time APIs are available</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Shows the proportion of clock time that open finance endpoints can successfully serve requests. High availability is critical for data users such as third-party providers (TPPs) to deliver reliable account information and payment initiation; poor uptime breaks customer journeys, breaches SLAs/SLOs, and can trigger regulatory scrutiny in open finance schemes. !- Definitions and concepts: Availability (uptime):  time-weighted share of intervals in which an endpoint meets both reachability and success criteria. Scope — include account information service, payment initiation service, consent/token endpoints, and webhooks if they’re required for completion. Planned vs. unplanned:  exclude planned maintenance time; report maintenance windows separately. SLO period: availability is usually measured monthly/quarterly (e.g., 99.9% per calendar month), but preferably in shorter periods (e.g., weekly, daily). Granularity: overall availability, by endpoint family, region/zone, and time of day. Example indicator: Availability = 1 - [Downtime / Total scheduled time] where Downtime aggregates intervals failing the success criterion (5xx gateway/network timeouts, auth outages, or latency breaches). !- Limitations and considerations: Including latency SLOs will lower availability vs. status-only measurements. Publish thresholds.</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Does API infrastructure for open finance show performance differences across FSPs that could disproportionately affect digital-first FSPs serving gender-diverse or underserved customer bases? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside open finance – API error rate and open finance – API response time to explore whether FSPs with lower API availability also show higher error rates and slower response times. Variations in this indicator may be explored across FSP type and API type.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Quality, Operational risk, Fair treatment</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D234">
+        <v>37</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Open finance - API error rate</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>% of all API calls that are unsuccessful</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>This indicator tracks the reliability of open-finance interfaces by showing what share of API requests do not complete successfully due to errors. It is a key API performance indicator monitored by financial authorities implementing open finance. High failure rates degrade customer journeys (consent, data retrieval, payment initiation), inflate support costs, and can breach SLA/SLO commitments. !- Definitions and concepts: API call (request): one HTTP request to a documented endpoint, for example: Account Information Services (AIS) data, Payment Initiatiion Services (PIS) payment, consent, token, webhook, etc. Unsuccessful call: define as per local regulation. This indicator can be collected segmented by types of errors, to be defined as per local regulation (e.g., gateway/network timeouts, invalid/expired token/consent, error in validation, authentication failures. It should also be segmented by type of endpoint, as per local categorization (e.g., account information request, payment initiation request, other). Example indicator: [# of errors  /  # total API calls] x 100%.</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Does API error rate show performance differences that could disproportionately affect digital-first FSPs serving gender-diverse and underserved customer bases? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type and API type.</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Quality, Operational risk</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D235">
+        <v>69</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Open finance - API response time</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Average API response time</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Shows how quickly open-finance endpoints answer requests. Faster responses improve user experience during consent, account-information retrieval, and payment initiation, reducing frictions and drop-offs. Response time is a core performance KPI that complements availability and error rate. !- Definitions and concepts: Response time (latency): elapsed time between request start and final byte received (client-observed) or gateway in → gateway out (server-observed). Track both when possible. Averages vs. tails: report p50/median, p95, p99, and the mean; tails (p95/p99) best reflect user pain. Track both. Granularity: report by endpoint family (types of APIs), potentially segmented into priority levels (see https://www.cdr.gov.au/performance). Units &amp; window: milliseconds, by calendar month (preferably shorter SLO period, such as weekly or daily).</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Does API call response time show performance differences that could disproportionately affect digital-first FSPs serving gender-diverse or underserved customer bases? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? Variations in this indicator may be explored across FSP type, and API type.</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Quality, Operational risk, Fair treatment</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D236">
+        <v>68</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Open finance - Payment initiation transactions</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Number of payment initiation transactions conducted in the open finance scheme</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Counts how many account-to-account (A2A) payment orders were successfully initiated via open-finance rails in the period. It’s a core adoption and usage KPI for Payment Initiation Services (PIS): more transactions imply growing merchant and P2P acceptance of openb finance, customer trust, and TPP–bank interoperability. !- Definitions and concepts: Payment initiation transaction (PIT): a payment order created via an authorized PISP/TPP and accepted by the ASPSP (account holder) for processing. Companion counts: Failed payment initiation transactions. Refunds/returns/chargebacks tracked separately. Sub-types: single immediate payments, scheduled payments, recurring/VRP (variable recurring payments), instant vs. ACH/batch. !- Data requirements: Total number of successful payment initiation transactions. !- Limitations and considerations: Duplicates: avoid double counting by using operation IDs.</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Are there disparities in the use of payment initiation services through open finance channels associated with customer type, gender, age, income, location, or FSP type? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside access to the instant/fast payment system to explore whether socio-demographic gaps in payment initiation through open finance channels are related to gaps in registration in the instant payment system.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D237">
         <v>150</v>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E237" t="inlineStr">
         <is>
           <t>Bundled product uptake rate</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
+      <c r="F237" t="inlineStr">
         <is>
           <t>% of customers taking up additional products during onboarding</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
+      <c r="G237" t="inlineStr">
         <is>
           <t>Measures the percentage of customers who acquire one or more additional financial products or services at the time of onboarding (i.e., when opening their primary account or initiating a new relationship with a financial service provider). These additional products may include insurance, savings, credit, or investment add-ons linked to the initial product. Captures the prevalence of product bundling and cross-selling practices during customer onboarding. It provides insight into market behavior, product integration, and the extent to which customers are being offered or encouraged to take multiple products simultaneously. Monitoring product bundling helps regulators and providers:
 Assess consumer choice and informed consent during onboarding; Identify potential coercive or mis-selling practices; Evaluate financial literacy and customer understanding of product combinations; Analyze the integration of complementary services (e.g., savings plus micro-insurance); Support efforts to ensure responsible cross-selling and transparent disclosure. Bundling can enhance value and convenience when responsibly designed, but may also raise conduct or affordability risks if customers are not well-informed. High bundling rates may reflect integrated product offerings or effective cross-selling, but warrant review for consent and suitability. Low rates may indicate limited product integration or narrow customer engagement at onboarding. Trends can reveal shifts in market strategy, regulatory compliance, or consumer protection outcomes. !- Definitions and concepts: Bundled product: A package of two or more financial services offered together at onboarding (e.g., transaction account + insurance or credit line). Onboarding: The process of establishing a new customer relationship, including account opening and KYC verification. Cross-selling: Offering additional, often related, financial products to a new or existing customer. Informed consent: The customer’s clear understanding and voluntary acceptance of each product taken. !- Data requirements: Bundled product uptake rate (%)=Number of customers who acquired ≥1 additional product at onboarding​/Total number of new customers onboarded. Administrative or CRM data from financial institutions on new customer onboarding and product uptake. Disaggregation by institution type, customer segment (individual, MSMEs), region, and product category. !- Derivable indicators: Average number of products per new customer; Distribution of additional products (e.g., % taking insurance, credit, savings add-ons)</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in the average number of products taken up during onboarding? Variations in this indicator may be explored across customer gender, age, income, location, customer type, product type and FSP type. this indicator can be analyzed alongisde the active usage of products taken up during onboarding. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside product take-up ratio to explore whether disparities in bundled product uptake at onboarding persist into actual product activation and usage.</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr">
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Are there disparities in the average number of products taken up during onboarding associated with customer gender, age, income, location, customer type, product type or FSP type? this indicator can be analyzed alongisde the active usage of products taken up during onboarding. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside product take-up ratio to explore whether disparities in bundled product uptake at onboarding persist into actual product activation and usage.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
         <is>
           <t>Uptake (account ownership)</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr">
+      <c r="L237" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
+    <row r="238">
+      <c r="A238" t="inlineStr">
         <is>
           <t>Market development</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B238" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
+      <c r="C238" t="inlineStr">
         <is>
           <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D230">
+      <c r="D238">
         <v>32</v>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E238" t="inlineStr">
         <is>
           <t>Product portability requests</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
+      <c r="F238" t="inlineStr">
         <is>
           <t>Number of product portability requests</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
+      <c r="G238" t="inlineStr">
         <is>
           <t>Measures the volume of formal requests initiated by customers to transfer their financial product or relationship from one provider to another within a specific period. This includes activities like switching a mortgage, transferring a loan to a new lender, or moving a current account to a new bank. This indicator is a gauge of market competition, consumer empowerment, and potential frictions or risks within the financial system. Very low switching rates can indicate significant barriers to entry or anti-competitive behavior, suggesting that customers are "trapped" with their current providers due to high exit fees, complex processes, or a lack of clear alternatives. This indicator is even more important in countries where product switching platforms or open finance exist and whose effectiveness should be monitored. A companion indicator to the total number of product switch requests is the total number of switches effected in the period, in comparison to the total number of requests. Another companion indicator is the total number of requests (or successful requests) relative to the number of active customers. The central bank of Brazil has calculated the number of loan portability requests relative to the number of loans with an interest rate above the market average rates, using the number of loans with above-market interest rates as a proxy for the untapped potential of the portability system. https://www.bcb.gov.br/content/publicacoes/Documents/reb/boxesreb2020/boxe_2_evolucao_portabilidade_credito_brasil.pdf</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
+      <c r="H238" t="inlineStr">
         <is>
           <t>Are there gender disparities in account and loan portability or FSP switching requests? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, and product type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator? This indicator can be analyzed alongside rejected product portability requests to explore whether customer groups submitting more portability requests also face higher rejection rates.</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
+      <c r="K238" t="inlineStr">
         <is>
           <t>Quality, Suitability</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr">
+      <c r="L238" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
+    <row r="239">
+      <c r="A239" t="inlineStr">
         <is>
           <t>Market development</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B239" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
+      <c r="C239" t="inlineStr">
         <is>
           <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D231">
+      <c r="D239">
         <v>33</v>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="E239" t="inlineStr">
         <is>
           <t>Rejected product portability requests</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
+      <c r="F239" t="inlineStr">
         <is>
           <t>% of all product portability requests that are rejected</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
+      <c r="G239" t="inlineStr">
         <is>
           <t>Measures the volume of formal portability requests initiated by customers to transfer their financial product or relationship from one provider to another within a specific period, which are rejected by the financial service provider. Product portability includes activities like switching a mortgage, transferring a loan to a new lender, or moving a current account to a new bank. This indicator is a gauge of market competition, consumer empowerment, and potential frictions or risks within the financial system. Very low switching rates can indicate significant barriers to entry or anti-competitive behavior, suggesting that customers are "trapped" with their current providers due to high exit fees, complex processes, or a lack of clear alternatives. This indicator is even more important in countries where product switching platforms or open finance exist and whose effectiveness should be monitored. When providers reject too many portability requests, this could be a sign of anti-competitive practices. This indicator should be analyzed together with the indicator on the total number of portability requests.</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in the rate of rejected portability requests? Variations in this indicator may be explored across customer gender, age, income, location, customer type, FSP type, and product type. Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Are there disparities in the rate of rejected portability requests associated with customer gender, age, income, location, customer type, FSP type, or product type? Do FSPs with greater gender diversity in their workforce, management, or board, show different performance in this indicator? Do FSPs with different levels of gender balance in their customer base, show different performance in this indicator?</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
+      <c r="K239" t="inlineStr">
         <is>
           <t>Quality, Suitability</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr">
+      <c r="L239" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
         </is>

--- a/www/LENS_INDICATORS_DB.xlsx
+++ b/www/LENS_INDICATORS_DB.xlsx
@@ -993,7 +993,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Number of individual (retail) deposit accounts</t>
+          <t>Number of individual deposit accounts</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Investment account holders (retail investors)</t>
+          <t>Investment account holders (individual investors)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Number of retail investors (including crowdfunding investors and P2P investors)</t>
+          <t>Number of individual investors (including crowdfunding and P2P investors)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>% of retail borrowers who have more than one outstanding credit operation (as a proxy for over-indebtedness)</t>
+          <t>% of borrowers who have more than one outstanding credit operation (as a proxy for over-indebtedness)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Outstanding balance in the secured retail loan portfolio</t>
+          <t>Outstanding balance in the secured loan portfolio</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Value of principal disbursed on secured retail loans</t>
+          <t>Value of principal disbursed on secured loans</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Number (and %) of retail borrowers required to provide collateral on outstanding loans</t>
+          <t>Number (and %) of borrowers required to provide collateral on outstanding loans</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Average retail account opening costs for the financial service provider (FSP), considering all fees and charges</t>
+          <t>Average account opening costs for the financial service provider (FSP), considering all fees and charges</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>% of retail depositors who actively closed a deposit account</t>
+          <t>% of depositors who actively closed a deposit account</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Annual percentage rate (APR) for retail credit</t>
+          <t>Annual percentage rate (APR) on credit</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Late penalty charges/fees on retail credit</t>
+          <t>Late payment penalty charges or fees</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Average topline revenue earned from unsecured retail credit operations (as percentage of the average outstanding unsecured credit)</t>
+          <t>Average topline revenue earned from unsecured credit operations (as a percentage of average outstanding unsecured credit)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>% of income allocated to retail credit debt repayment</t>
+          <t>% of income allocated to credit debt repayment</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gender composition of guarantors in the retail loan portfolio</t>
+          <t>Gender composition of guarantors in the loan portfolio</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Volume and value of delinquent retail loans as a proportion of total retail portfolio</t>
+          <t>Volume and value of delinquent loans as a proportion of the total loan portfolio</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Non performing loans rate in the retail loan portfolio</t>
+          <t>Non-performing loan rate in the loan portfolio</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Volume and value of restructured loans as a proportion of total retail/MSME portfolio</t>
+          <t>Volume and value of restructured loans as a proportion of the total loan portfolio</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Volume and value of written off retail loans as a proportion of retail/MSME portfolio</t>
+          <t>Volume and value of written-off loans as a proportion of the total loan portfolio</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Stability/volatility of retail deposits (deposit stickness, deposit stability, deposit flows)</t>
+          <t>Stability/volatility of deposits (deposit stickiness, deposit flows)</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Number of loans in the retail loan portfolio designated as rural credit</t>
+          <t>Number of loans in the loan portfolio designated as rural credit</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>% of the total retail loan portfolio that is rural credit based on outstanding balance</t>
+          <t>% of the total loan portfolio that is rural credit, based on outstanding balance</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>% of the total retail loan portfolio that is rural credit based on principal disbursed</t>
+          <t>% of the total loan portfolio that is rural credit, based on principal disbursed</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Number of investment fund shares held by retail investors in the system</t>
+          <t>Number of investment fund shares held by individual investors in the system</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
